--- a/HTML/0 Excel SRC Files/Other E.xlsx
+++ b/HTML/0 Excel SRC Files/Other E.xlsx
@@ -1,34 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Me\QuickAccessv2\HTML\0 Excel SRC Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F555F1-D9D4-422E-8930-F5258D9237B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A992883B-DD26-4AC5-A54C-B483FB9C8530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="899" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0" sheetId="1" r:id="rId1"/>
-    <sheet name="AI" sheetId="37" r:id="rId2"/>
-    <sheet name="Marketing" sheetId="5" r:id="rId3"/>
-    <sheet name="Repair" sheetId="4" r:id="rId4"/>
-    <sheet name="EG" sheetId="12" r:id="rId5"/>
-    <sheet name="$$" sheetId="14" r:id="rId6"/>
-    <sheet name="Food" sheetId="18" r:id="rId7"/>
-    <sheet name="Freelaning" sheetId="32" r:id="rId8"/>
-    <sheet name="Advise" sheetId="19" r:id="rId9"/>
-    <sheet name="Clothes" sheetId="22" r:id="rId10"/>
-    <sheet name="Sports" sheetId="24" r:id="rId11"/>
-    <sheet name="Home" sheetId="25" r:id="rId12"/>
-    <sheet name="Law" sheetId="30" r:id="rId13"/>
-    <sheet name="Jobs" sheetId="33" r:id="rId14"/>
-    <sheet name="Post" sheetId="34" r:id="rId15"/>
-    <sheet name="Search" sheetId="36" r:id="rId16"/>
+    <sheet name="Marketing" sheetId="5" r:id="rId2"/>
+    <sheet name="Repair" sheetId="4" r:id="rId3"/>
+    <sheet name="$$" sheetId="14" r:id="rId4"/>
+    <sheet name="Food" sheetId="18" r:id="rId5"/>
+    <sheet name="Freelaning" sheetId="32" r:id="rId6"/>
+    <sheet name="Advise" sheetId="19" r:id="rId7"/>
+    <sheet name="Clothes" sheetId="22" r:id="rId8"/>
+    <sheet name="Sports" sheetId="24" r:id="rId9"/>
+    <sheet name="Home" sheetId="25" r:id="rId10"/>
+    <sheet name="Law" sheetId="30" r:id="rId11"/>
+    <sheet name="Jobs" sheetId="33" r:id="rId12"/>
+    <sheet name="Post" sheetId="34" r:id="rId13"/>
+    <sheet name="Search" sheetId="36" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="732">
   <si>
     <t>البيت الكبير</t>
   </si>
@@ -179,39 +177,9 @@
     <t>MOZ</t>
   </si>
   <si>
-    <t>الدرر السنية</t>
-  </si>
-  <si>
-    <t>مكملين</t>
-  </si>
-  <si>
     <t>زاد</t>
   </si>
   <si>
-    <t>بيت الاسلام</t>
-  </si>
-  <si>
-    <t>العلم يؤكد الدين</t>
-  </si>
-  <si>
-    <t>محمد هداية</t>
-  </si>
-  <si>
-    <t>اسلاميات</t>
-  </si>
-  <si>
-    <t>الاسلام س و ج</t>
-  </si>
-  <si>
-    <t>اسلام ويب</t>
-  </si>
-  <si>
-    <t>جسور</t>
-  </si>
-  <si>
-    <t>مصطفى البدري</t>
-  </si>
-  <si>
     <t>البينة</t>
   </si>
   <si>
@@ -221,24 +189,9 @@
     <t>الدفاع العقدي</t>
   </si>
   <si>
-    <t>هيثم طلعت</t>
-  </si>
-  <si>
     <t>جهاد حافظ</t>
   </si>
   <si>
-    <t>تبيان</t>
-  </si>
-  <si>
-    <t>عمر العودة</t>
-  </si>
-  <si>
-    <t>سامح الجنداوي</t>
-  </si>
-  <si>
-    <t>علاء حامد</t>
-  </si>
-  <si>
     <t>عبد الله بن فهد</t>
   </si>
   <si>
@@ -248,12 +201,6 @@
     <t>سمير مصطفي</t>
   </si>
   <si>
-    <t>طارق السويدان</t>
-  </si>
-  <si>
-    <t>علوي الكافي</t>
-  </si>
-  <si>
     <t>عبد الرزاق البدر</t>
   </si>
   <si>
@@ -266,15 +213,6 @@
     <t>Back</t>
   </si>
   <si>
-    <t>سعيد الكملي</t>
-  </si>
-  <si>
-    <t>بالعقل مع حسام</t>
-  </si>
-  <si>
-    <t>احمد السيد</t>
-  </si>
-  <si>
     <t>سنحيا كراما</t>
   </si>
   <si>
@@ -284,9 +222,6 @@
     <t>فقه النفس/مكاني</t>
   </si>
   <si>
-    <t>اياد قنيبي</t>
-  </si>
-  <si>
     <t>English test store</t>
   </si>
   <si>
@@ -449,12 +384,6 @@
     <t>محمود خالد</t>
   </si>
   <si>
-    <t>ميسم مجدي</t>
-  </si>
-  <si>
-    <t>أشجان يحيى</t>
-  </si>
-  <si>
     <t>bassem elgarhi</t>
   </si>
   <si>
@@ -476,48 +405,6 @@
     <t>Jumia</t>
   </si>
   <si>
-    <t>التعليم العالي والبحث العلمي</t>
-  </si>
-  <si>
-    <t>المركزي للتعبئة العامة والاحصاء</t>
-  </si>
-  <si>
-    <t>المشروعات الصغيرة</t>
-  </si>
-  <si>
-    <t>مصر الرقمية</t>
-  </si>
-  <si>
-    <t>حماية المستهلك</t>
-  </si>
-  <si>
-    <t>الاتصالات و تكنولوجيا المعلومات</t>
-  </si>
-  <si>
-    <t>الدراسات العليا للبحوث الاحصائية</t>
-  </si>
-  <si>
-    <t>المركزي للمحاسبات</t>
-  </si>
-  <si>
-    <t>مصلحة الجمارك</t>
-  </si>
-  <si>
-    <t>منظومة الشكاوي الموحدة</t>
-  </si>
-  <si>
-    <t>المالية</t>
-  </si>
-  <si>
-    <t>شركة المياه</t>
-  </si>
-  <si>
-    <t>الشهر العقاري</t>
-  </si>
-  <si>
-    <t>القومية للتأمين</t>
-  </si>
-  <si>
     <t>Body</t>
   </si>
   <si>
@@ -533,39 +420,9 @@
     <t>مصطفى شاهين</t>
   </si>
   <si>
-    <t>هاني سليمان</t>
-  </si>
-  <si>
-    <t>كلمه السر</t>
-  </si>
-  <si>
-    <t>Grow Up Mind</t>
-  </si>
-  <si>
-    <t>الوزير المالي</t>
-  </si>
-  <si>
-    <t>محمد عبدالفتاح</t>
-  </si>
-  <si>
-    <t>خمسينة اقتصاد</t>
-  </si>
-  <si>
-    <t>استثمر مع محمود</t>
-  </si>
-  <si>
-    <t>اخبار البنوك</t>
-  </si>
-  <si>
     <t>Shark Tank</t>
   </si>
   <si>
-    <t>المستثمر الذكي</t>
-  </si>
-  <si>
-    <t>market watch</t>
-  </si>
-  <si>
     <t>استثمار بلا انهيار</t>
   </si>
   <si>
@@ -575,12 +432,6 @@
     <t>مباشر</t>
   </si>
   <si>
-    <t>Mo Abo Ali</t>
-  </si>
-  <si>
-    <t>Keyser Soze</t>
-  </si>
-  <si>
     <t>Fin Bee</t>
   </si>
   <si>
@@ -611,9 +462,6 @@
     <t>كتب تجارة2</t>
   </si>
   <si>
-    <t>مُجٓمَع شَبَاب البنوك</t>
-  </si>
-  <si>
     <t>عبدالله جلال SAP, CMA</t>
   </si>
   <si>
@@ -626,112 +474,25 @@
     <t>EBI</t>
   </si>
   <si>
-    <t>EGY TAX1</t>
-  </si>
-  <si>
-    <t>EGY TAX2</t>
-  </si>
-  <si>
-    <t>PayPal</t>
-  </si>
-  <si>
-    <t>EGY POST</t>
-  </si>
-  <si>
     <t>Gold Price</t>
   </si>
   <si>
     <t>I Sagha</t>
   </si>
   <si>
-    <t>BTC Egypt Gold</t>
-  </si>
-  <si>
-    <t>Selema Gold</t>
-  </si>
-  <si>
-    <t>Lazurde</t>
-  </si>
-  <si>
     <t>Egypt Gold</t>
   </si>
   <si>
-    <t>kirmena</t>
-  </si>
-  <si>
-    <t>Bajocchi</t>
-  </si>
-  <si>
     <t>Swiss Gold</t>
   </si>
   <si>
-    <t>EGX</t>
-  </si>
-  <si>
-    <t>EGX FB</t>
-  </si>
-  <si>
-    <t>ازيموت مصر</t>
-  </si>
-  <si>
-    <t>Hermes One</t>
-  </si>
-  <si>
-    <t>Thndr APP</t>
-  </si>
-  <si>
-    <t>تحليل أسهم البورصة</t>
-  </si>
-  <si>
-    <t>بورصجي مصر</t>
-  </si>
-  <si>
-    <t>المضارب العربي</t>
-  </si>
-  <si>
-    <t>البورصه مع فاروق</t>
-  </si>
-  <si>
-    <t>صندوق حماية المستثمر</t>
-  </si>
-  <si>
-    <t>البورصجية</t>
-  </si>
-  <si>
-    <t>افهم بورصة</t>
-  </si>
-  <si>
-    <t>هاني جنينة</t>
-  </si>
-  <si>
     <t>هاني توفيق</t>
   </si>
   <si>
-    <t>محمود وهبه</t>
-  </si>
-  <si>
-    <t>ممدوح حمزة</t>
-  </si>
-  <si>
     <t>خضر و بزنس</t>
   </si>
   <si>
     <t>محمد خضر</t>
-  </si>
-  <si>
-    <t>تامر فاروق</t>
-  </si>
-  <si>
-    <t>كريم دوغيم</t>
-  </si>
-  <si>
-    <t>مجتمع ثاندر</t>
-  </si>
-  <si>
-    <t>I-Score</t>
-  </si>
-  <si>
-    <t>صندوق النقد الدولي</t>
   </si>
   <si>
     <t>الفطار | العشاء</t>
@@ -1502,9 +1263,6 @@
     <t>CS</t>
   </si>
   <si>
-    <t>Egy Official</t>
-  </si>
-  <si>
     <t>القانون</t>
   </si>
   <si>
@@ -1647,9 +1405,6 @@
   </si>
   <si>
     <t>Elgalla Gold</t>
-  </si>
-  <si>
-    <t>Advcash</t>
   </si>
   <si>
     <t>Gold Era</t>
@@ -2772,39 +2527,9 @@
     <t>بن سامي</t>
   </si>
   <si>
-    <t>الشيخ حسن أيوب</t>
-  </si>
-  <si>
     <t xml:space="preserve">د. محمد خير الشعّال </t>
   </si>
   <si>
-    <t>Omar El-Shenety</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>Stack AI</t>
-  </si>
-  <si>
-    <t>.NET AI</t>
-  </si>
-  <si>
-    <t>Hugging Face</t>
-  </si>
-  <si>
-    <t>Open AI</t>
-  </si>
-  <si>
-    <t>شيماء خضير</t>
-  </si>
-  <si>
-    <t>luma labs</t>
-  </si>
-  <si>
-    <t>ML .NET</t>
-  </si>
-  <si>
     <t>onlinesim</t>
   </si>
   <si>
@@ -2823,9 +2548,6 @@
     <t>Printige</t>
   </si>
   <si>
-    <t>Hailuoai</t>
-  </si>
-  <si>
     <t>InnovEgypt</t>
   </si>
   <si>
@@ -2841,7 +2563,7 @@
     <t>هل بتحطلي roadmap او planing أل next step</t>
   </si>
   <si>
-    <t>إنت أي رأيك عامة في الخطوة دي ؟ إني اجي اتوس ؟
+    <t>إنت أي رأيك عامة في الخطوة دي ؟ إني اجي xxx ؟
 هل الشغل هيبرد و لا رموتلي او احتمال قدام يبقي رموتلي
 اي التحديات اللي هواجها او اتعلمها
 اي ال main rules بتاعتي
@@ -2853,7 +2575,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="53" x14ac:knownFonts="1">
+  <fonts count="50" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3103,21 +2825,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <color theme="0" tint="-4.9989318521683403E-2"/>
@@ -3159,13 +2866,6 @@
       <b/>
       <sz val="20"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -4024,7 +3724,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="265">
+  <cellXfs count="258">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4053,10 +3753,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4382,10 +4078,6 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4485,60 +4177,57 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4580,7 +4269,7 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4589,7 +4278,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4598,53 +4287,50 @@
     <xf numFmtId="0" fontId="6" fillId="23" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4712,7 +4398,7 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4799,13 +4485,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5509,7 +5192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="18.5703125" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" style="2" customWidth="1"/>
@@ -5524,512 +5207,389 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="119">
+      <c r="A1" s="117">
         <v>1</v>
       </c>
-      <c r="B1" s="200">
+      <c r="B1" s="195">
         <v>2</v>
       </c>
-      <c r="C1" s="119" t="s">
-        <v>462</v>
-      </c>
-      <c r="D1" s="200" t="s">
-        <v>461</v>
-      </c>
-      <c r="E1" s="119" t="s">
-        <v>155</v>
-      </c>
-      <c r="F1" s="200" t="s">
-        <v>508</v>
-      </c>
-      <c r="G1" s="119" t="s">
-        <v>487</v>
-      </c>
-      <c r="H1" s="200" t="s">
-        <v>509</v>
-      </c>
-      <c r="I1" s="119" t="s">
-        <v>463</v>
+      <c r="C1" s="117" t="s">
+        <v>383</v>
+      </c>
+      <c r="D1" s="195" t="s">
+        <v>382</v>
+      </c>
+      <c r="E1" s="117" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" s="195" t="s">
+        <v>428</v>
+      </c>
+      <c r="G1" s="117" t="s">
+        <v>407</v>
+      </c>
+      <c r="H1" s="195" t="s">
+        <v>429</v>
+      </c>
+      <c r="I1" s="117" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="120" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" s="120" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2" s="120" t="s">
-        <v>799</v>
-      </c>
-      <c r="D2" s="120" t="s">
-        <v>128</v>
-      </c>
-      <c r="E2" s="120" t="s">
-        <v>802</v>
-      </c>
-      <c r="F2" s="205" t="s">
-        <v>815</v>
-      </c>
-      <c r="G2" s="205" t="s">
-        <v>814</v>
-      </c>
-      <c r="H2" s="120" t="s">
-        <v>813</v>
-      </c>
-      <c r="I2" s="200" t="s">
-        <v>507</v>
+      <c r="A2" s="118" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="118" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="118" t="s">
+        <v>718</v>
+      </c>
+      <c r="D2" s="118" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="200" t="s">
+        <v>724</v>
+      </c>
+      <c r="F2" s="118" t="s">
+        <v>722</v>
+      </c>
+      <c r="G2" s="118" t="s">
+        <v>107</v>
+      </c>
+      <c r="H2" s="200" t="s">
+        <v>727</v>
+      </c>
+      <c r="I2" s="195" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="120" t="s">
-        <v>130</v>
-      </c>
-      <c r="B3" s="205" t="s">
-        <v>818</v>
-      </c>
-      <c r="C3" s="205" t="s">
-        <v>819</v>
-      </c>
-      <c r="D3" s="120" t="s">
-        <v>816</v>
-      </c>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="119" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="120"/>
-      <c r="B4" s="120"/>
+      <c r="A3" s="200" t="s">
+        <v>726</v>
+      </c>
+      <c r="B3" s="201" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="200" t="s">
+        <v>723</v>
+      </c>
+      <c r="F3" s="200" t="s">
+        <v>720</v>
+      </c>
+      <c r="G3" s="118" t="s">
+        <v>728</v>
+      </c>
+      <c r="H3" s="118" t="s">
+        <v>725</v>
+      </c>
+      <c r="I3" s="117" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="205" t="s">
+        <v>430</v>
+      </c>
+      <c r="B4" s="205"/>
       <c r="C4" s="205"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="200" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="120"/>
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120" t="s">
-        <v>820</v>
-      </c>
-      <c r="I5" s="119" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="211" t="s">
-        <v>510</v>
-      </c>
-      <c r="B6" s="211"/>
-      <c r="C6" s="211"/>
-      <c r="D6" s="211"/>
-      <c r="E6" s="211"/>
-      <c r="F6" s="211"/>
-      <c r="G6" s="211"/>
-      <c r="H6" s="211"/>
-      <c r="I6" s="211"/>
-    </row>
-    <row r="7" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="123" t="s">
+      <c r="D4" s="205"/>
+      <c r="E4" s="205"/>
+      <c r="F4" s="205"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="205"/>
+    </row>
+    <row r="5" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="119" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="119" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="119" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="119" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="119" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="119" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="119" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="118" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="119" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="119" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="119" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="119" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="119" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="119" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+    </row>
+    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="205" t="s">
+        <v>679</v>
+      </c>
+      <c r="B7" s="205"/>
+      <c r="C7" s="205"/>
+      <c r="D7" s="205"/>
+      <c r="E7" s="205"/>
+      <c r="F7" s="205"/>
+      <c r="G7" s="205"/>
+      <c r="H7" s="205"/>
+      <c r="I7" s="205"/>
+    </row>
+    <row r="8" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="118" t="s">
+        <v>410</v>
+      </c>
+      <c r="B8" s="118" t="s">
+        <v>411</v>
+      </c>
+      <c r="C8" s="118" t="s">
+        <v>412</v>
+      </c>
+      <c r="D8" s="118" t="s">
+        <v>413</v>
+      </c>
+      <c r="E8" s="118" t="s">
+        <v>414</v>
+      </c>
+      <c r="F8" s="118" t="s">
+        <v>415</v>
+      </c>
+      <c r="G8" s="118" t="s">
+        <v>416</v>
+      </c>
+      <c r="H8" s="118" t="s">
+        <v>417</v>
+      </c>
+      <c r="I8" s="118" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="118" t="s">
+        <v>418</v>
+      </c>
+      <c r="B9" s="118" t="s">
+        <v>419</v>
+      </c>
+      <c r="C9" s="118" t="s">
+        <v>420</v>
+      </c>
+      <c r="D9" s="118" t="s">
+        <v>421</v>
+      </c>
+      <c r="E9" s="118" t="s">
+        <v>422</v>
+      </c>
+      <c r="F9" s="118" t="s">
+        <v>423</v>
+      </c>
+      <c r="G9" s="118" t="s">
+        <v>424</v>
+      </c>
+      <c r="H9" s="118" t="s">
+        <v>426</v>
+      </c>
+      <c r="I9" s="118" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="205" t="s">
+        <v>680</v>
+      </c>
+      <c r="B10" s="205"/>
+      <c r="C10" s="205"/>
+      <c r="D10" s="205"/>
+      <c r="E10" s="205"/>
+      <c r="F10" s="205"/>
+      <c r="G10" s="205"/>
+      <c r="H10" s="205"/>
+      <c r="I10" s="205"/>
+    </row>
+    <row r="11" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="200" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="200" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="200" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="200" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="200" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="200" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="200" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="200" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="202" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="200" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="200" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="200" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="200" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="200" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="200" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="200" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="200" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="200" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="200" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="200" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="200" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="200" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="200" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="123" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="123" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="123" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="123" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="123" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="123" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" s="123" t="s">
-        <v>71</v>
-      </c>
-      <c r="I7" s="123" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="123" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="123" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="123" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" s="123" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="123" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8" s="123" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="123" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="123" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="123" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="123" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="123" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="123" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="123" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="123" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="123" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="123" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="123" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="123" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="123" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="123" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="123" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="123" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="123" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="123" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="123" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="120" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="211" t="s">
-        <v>760</v>
-      </c>
-      <c r="B11" s="211"/>
-      <c r="C11" s="211"/>
-      <c r="D11" s="211"/>
-      <c r="E11" s="211"/>
-      <c r="F11" s="211"/>
-      <c r="G11" s="211"/>
-      <c r="H11" s="211"/>
-      <c r="I11" s="211"/>
-    </row>
-    <row r="12" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="120" t="s">
-        <v>490</v>
-      </c>
-      <c r="B12" s="120" t="s">
-        <v>491</v>
-      </c>
-      <c r="C12" s="120" t="s">
-        <v>492</v>
-      </c>
-      <c r="D12" s="120" t="s">
-        <v>493</v>
-      </c>
-      <c r="E12" s="120" t="s">
-        <v>494</v>
-      </c>
-      <c r="F12" s="120" t="s">
-        <v>495</v>
-      </c>
-      <c r="G12" s="120" t="s">
-        <v>496</v>
-      </c>
-      <c r="H12" s="120" t="s">
-        <v>497</v>
-      </c>
-      <c r="I12" s="120" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="120" t="s">
-        <v>498</v>
-      </c>
-      <c r="B13" s="120" t="s">
-        <v>499</v>
-      </c>
-      <c r="C13" s="120" t="s">
-        <v>500</v>
-      </c>
-      <c r="D13" s="120" t="s">
-        <v>501</v>
-      </c>
-      <c r="E13" s="120" t="s">
-        <v>502</v>
-      </c>
-      <c r="F13" s="120" t="s">
-        <v>503</v>
-      </c>
-      <c r="G13" s="120" t="s">
-        <v>504</v>
-      </c>
-      <c r="H13" s="120" t="s">
-        <v>506</v>
-      </c>
-      <c r="I13" s="120" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="211" t="s">
-        <v>761</v>
-      </c>
-      <c r="B14" s="211"/>
-      <c r="C14" s="211"/>
-      <c r="D14" s="211"/>
-      <c r="E14" s="211"/>
-      <c r="F14" s="211"/>
-      <c r="G14" s="211"/>
-      <c r="H14" s="211"/>
-      <c r="I14" s="211"/>
-    </row>
-    <row r="15" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="205" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="205" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="205" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" s="205" t="s">
+      <c r="H13" s="200" t="s">
+        <v>87</v>
+      </c>
+      <c r="I13" s="200" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="200" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="205" t="s">
+      <c r="B14" s="200" t="s">
         <v>82</v>
       </c>
-      <c r="F15" s="205" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="205" t="s">
+      <c r="C14" s="200" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="200" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="200" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="200" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="205" t="s">
-        <v>99</v>
-      </c>
-      <c r="I15" s="206" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="205" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="205" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="205" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="205" t="s">
+      <c r="G14" s="200" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="E16" s="205" t="s">
+      <c r="I14" s="200" t="s">
         <v>93</v>
       </c>
-      <c r="F16" s="205" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="205" t="s">
-        <v>91</v>
-      </c>
-      <c r="H16" s="205" t="s">
-        <v>109</v>
-      </c>
-      <c r="I16" s="207" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="205" t="s">
-        <v>95</v>
-      </c>
-      <c r="B17" s="205" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="205" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="205" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="205" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" s="205" t="s">
-        <v>97</v>
-      </c>
-      <c r="G17" s="205" t="s">
-        <v>98</v>
-      </c>
-      <c r="H17" s="205" t="s">
-        <v>108</v>
-      </c>
-      <c r="I17" s="208"/>
-    </row>
-    <row r="18" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="205" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="205" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="205" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="205" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" s="205" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" s="205" t="s">
-        <v>107</v>
-      </c>
-      <c r="G18" s="205" t="s">
-        <v>110</v>
-      </c>
-      <c r="H18" s="205" t="s">
-        <v>111</v>
-      </c>
-      <c r="I18" s="208"/>
-    </row>
-    <row r="19" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="205" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="205" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="205" t="s">
-        <v>114</v>
-      </c>
-      <c r="D19" s="208"/>
-      <c r="E19" s="208"/>
-      <c r="F19" s="209"/>
-      <c r="G19" s="209"/>
-      <c r="H19" s="209"/>
-      <c r="I19" s="208"/>
-    </row>
-    <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="211"/>
-      <c r="B20" s="211"/>
-      <c r="C20" s="211"/>
-      <c r="D20" s="211"/>
-      <c r="E20" s="211"/>
-      <c r="F20" s="211"/>
-      <c r="G20" s="211"/>
-      <c r="H20" s="211"/>
-      <c r="I20" s="211"/>
-    </row>
-    <row r="21" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="205" t="s">
-        <v>811</v>
-      </c>
-      <c r="B21" s="120" t="s">
-        <v>133</v>
-      </c>
-      <c r="C21" s="120" t="s">
-        <v>132</v>
-      </c>
-      <c r="D21" s="120" t="s">
-        <v>808</v>
-      </c>
-      <c r="E21" s="120" t="s">
-        <v>800</v>
-      </c>
-      <c r="F21" s="210"/>
-      <c r="G21" s="205"/>
-      <c r="H21" s="205"/>
-      <c r="I21" s="205"/>
-    </row>
-    <row r="23" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="264" t="s">
-        <v>822</v>
-      </c>
-      <c r="B24" s="264" t="s">
-        <v>823</v>
+    </row>
+    <row r="15" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="205"/>
+      <c r="B15" s="205"/>
+      <c r="C15" s="205"/>
+      <c r="D15" s="205"/>
+      <c r="E15" s="205"/>
+      <c r="F15" s="205"/>
+      <c r="G15" s="205"/>
+      <c r="H15" s="205"/>
+      <c r="I15" s="205"/>
+    </row>
+    <row r="16" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B16" s="203" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="203" t="s">
+        <v>730</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F1" location="Repair!A1" display="[صيانة]" xr:uid="{CB7C93AC-CAE0-4257-8918-2B9D24101A69}"/>
     <hyperlink ref="G1" location="Jobs!A1" display="Jobs" xr:uid="{76A456D3-FA32-4765-AED9-E883E86A1CED}"/>
-    <hyperlink ref="I1" location="EG!A1" display="[Egy Official]" xr:uid="{6C97A8A7-80E1-4075-BE65-238E19B621B1}"/>
     <hyperlink ref="A2" r:id="rId1" display="https://www.youtube.com/@dwdocarabia/videos" xr:uid="{3D08B856-FE3C-4DB0-8693-4D8AA801EC5D}"/>
-    <hyperlink ref="D2" r:id="rId2" display="https://mcit.gov.eg/" xr:uid="{13083B6B-62C6-4508-977C-252D35DE35D8}"/>
+    <hyperlink ref="G2" r:id="rId2" display="https://mcit.gov.eg/" xr:uid="{13083B6B-62C6-4508-977C-252D35DE35D8}"/>
     <hyperlink ref="B1:D1" location="'$$'!A1" display="'$$'!A1" xr:uid="{36CA0706-DD86-4B1D-A60E-4D98853504F5}"/>
     <hyperlink ref="C1" r:id="rId3" xr:uid="{F7BC58C6-4D7F-46A5-B0B6-E4E00776BBAC}"/>
     <hyperlink ref="A1" r:id="rId4" display="..\1.html" xr:uid="{10F17F0F-B58E-460E-A563-CB5410414046}"/>
@@ -6037,769 +5597,94 @@
     <hyperlink ref="E1" location="Food!A1" display="Body" xr:uid="{93D3B2A3-E9BA-49D3-B3E5-952B4074149D}"/>
     <hyperlink ref="H1" location="Marketing!A1" display="Marketing" xr:uid="{6BF12EBD-4D0A-4E55-A0D3-CC02663B48AC}"/>
     <hyperlink ref="I2" location="Law!A1" display="[Law]" xr:uid="{0C0AE0C9-22E6-439D-8683-807AF6C40C13}"/>
-    <hyperlink ref="I3" location="Freelaning!A1" display="Freelancing" xr:uid="{00F80706-582F-4B8C-B85C-742129B840A5}"/>
-    <hyperlink ref="A16" r:id="rId5" display="https://learnenglish.britishcouncil.org/online-english-level-test" xr:uid="{490249CD-69D6-4F5C-B5D9-F9B22E5531F8}"/>
-    <hyperlink ref="B16" r:id="rId6" display="https://www.abaenglish.com/en/english-level-test" xr:uid="{C522A13A-66DB-489D-900A-6B52CE61F427}"/>
-    <hyperlink ref="C16" r:id="rId7" display="https://www.facebook.com/BerlitzEgypt" xr:uid="{9A5C3573-1496-4F3A-AC2E-401DDF1DE2CE}"/>
-    <hyperlink ref="C17" r:id="rId8" display="https://www.e2english.com/Home/PlacementTest?gclid=Cj0KCQjwhqaVBhCxARIsAHK1tiMYX2k6u4GzYTpUkafFVpF4BUV_bgOumu6I4thoubdtYzqd9k5NKwoaApt3EALw_wcB" xr:uid="{2E842923-A1CC-4A5D-B40B-DFD523EB31B4}"/>
-    <hyperlink ref="F16" r:id="rId9" display="https://www.languagelevel.com/english/index.php" xr:uid="{6EFB8D37-425E-4F6F-AD3C-219F60B70DFA}"/>
-    <hyperlink ref="G16" r:id="rId10" display="https://www.busuu.com/" xr:uid="{3765DD28-651E-4ABF-98DA-8A09FEBA3C9E}"/>
-    <hyperlink ref="D16" r:id="rId11" display="https://www.bbc.co.uk/learningenglish" xr:uid="{54EB8998-62E4-41FC-84CA-28D8E96E427E}"/>
-    <hyperlink ref="E16" r:id="rId12" display="https://www.espressoenglish.net/english-tips-blog" xr:uid="{3FA836B7-1028-48AE-8951-8C2766989504}"/>
-    <hyperlink ref="A17" r:id="rId13" display="https://www.espressoenglish.net/how-to-learn-english-for-free-50-websites-for-free-english-lessons" xr:uid="{57197D10-C848-4C02-AC29-7E1C3E3E53C8}"/>
-    <hyperlink ref="I16" r:id="rId14" display="https://www.duolingo.com/learn" xr:uid="{FFC13E6E-BCC9-4E40-8811-7AB8A2F09ECB}"/>
-    <hyperlink ref="F17" r:id="rId15" display="https://www.youtube.com/c/ZAmericanEnglish/videos" xr:uid="{7643E7D0-9780-4DA5-AFF2-9ABFC505990B}"/>
-    <hyperlink ref="G17" r:id="rId16" display="https://www.youtube.com/c/VeronikaMark" xr:uid="{482FECE1-83C4-45FC-B270-D2DE2E503994}"/>
-    <hyperlink ref="A18" r:id="rId17" display="https://www.youtube.com/c/LearnEnglishwithBobtheCanadian/videos" xr:uid="{320FB9C0-08FD-49D8-9BA6-49D2314F64B6}"/>
-    <hyperlink ref="B18" r:id="rId18" display="https://www.youtube.com/c/MasterEnglish/videos" xr:uid="{10FCE5BE-82DA-4E1C-9BB1-542F1309E879}"/>
-    <hyperlink ref="E17" r:id="rId19" display="https://www.youtube.com/c/GoNaturalEnglish/videos" xr:uid="{DBE65AC5-86BA-480A-9D64-15A49991CECD}"/>
-    <hyperlink ref="E18" r:id="rId20" display="https://www.youtube.com/c/englishforyoutv" xr:uid="{6FFC4B5D-0D78-4AC1-9CA7-CC90A8AB6CB4}"/>
-    <hyperlink ref="F18" r:id="rId21" display="https://www.youtube.com/user/EnglishAnyone" xr:uid="{29DAA25A-6ABD-403A-A90D-654AED8B66B5}"/>
-    <hyperlink ref="C18" r:id="rId22" display="https://www.youtube.com/c/rachelsenglish" xr:uid="{850BA37C-D43A-47C1-8F0B-3950FCC6A227}"/>
-    <hyperlink ref="D18" r:id="rId23" display="https://www.youtube.com/c/mmmEnglish_Emma" xr:uid="{97CA62D5-C3C6-4137-9685-0968A587D3CD}"/>
-    <hyperlink ref="H17" r:id="rId24" display="https://www.youtube.com/c/AmigosIngleses/videos" xr:uid="{9BD15DB6-75AF-444E-BB8F-4E80131B7199}"/>
-    <hyperlink ref="H16" r:id="rId25" display="Single Step English" xr:uid="{89EC801F-7A89-4271-9961-FEE438084B14}"/>
-    <hyperlink ref="B19" r:id="rId26" display="https://www.youtube.com/c/OneMinuteEnglish/videos" xr:uid="{39A0FD1C-A0F1-493D-BCA4-66D8345DB928}"/>
-    <hyperlink ref="D17" r:id="rId27" xr:uid="{C144C009-46AA-423D-ADDB-A8B36273830F}"/>
-    <hyperlink ref="C19" r:id="rId28" xr:uid="{ACE42FCC-AAD7-4632-B2D8-8EFFCA4B5BA1}"/>
-    <hyperlink ref="B17" r:id="rId29" xr:uid="{13D5419E-228F-4DA1-A26A-3BC212A3A7A9}"/>
-    <hyperlink ref="A19" r:id="rId30" display="EdMo Tests and Quizzes " xr:uid="{5AE54B23-DDD8-4A58-9D7D-459206AB2EEB}"/>
-    <hyperlink ref="H18" r:id="rId31" display="Culips " xr:uid="{3784E8EE-E16C-459E-9B59-47B6ED00BCAA}"/>
-    <hyperlink ref="G18" r:id="rId32" display="https://www.youtube.com/c/EnglishwithLucy/videos" xr:uid="{E6ECFE11-8A70-4700-A357-B0B1516B8954}"/>
-    <hyperlink ref="H15" r:id="rId33" display="https://www.youtube.com/c/EnglishClass101/videos" xr:uid="{677F7135-2D2E-4D83-B9A9-CF5C49A9FC41}"/>
-    <hyperlink ref="I15" r:id="rId34" xr:uid="{BFF4F3ED-2E98-4610-8C03-5273DF52C8DC}"/>
-    <hyperlink ref="E15" r:id="rId35" display="https://learningenglish.voanews.com/" xr:uid="{2B47E0B5-3EB5-443C-8F99-08E3DEDAB1D4}"/>
-    <hyperlink ref="F15" r:id="rId36" display="https://www.cambly.com/english?lang=en" xr:uid="{DC5DBA3B-121D-4C50-A347-1E99DB4C82A0}"/>
-    <hyperlink ref="G15" r:id="rId37" display="https://www.aucegypt.edu/ar" xr:uid="{D09BB70C-8FD6-4368-94E0-9285BC36CC71}"/>
-    <hyperlink ref="B15" r:id="rId38" display="https://www.cambridgeenglish.org/" xr:uid="{80219548-CF0A-464B-B939-323B5009D1F6}"/>
-    <hyperlink ref="A15" r:id="rId39" display="https://englishteststore.net/" xr:uid="{C2EFF72A-A901-4792-833C-7B67D27C9B84}"/>
-    <hyperlink ref="H13" r:id="rId40" display="https://www.youtube.com/channel/UCyQw44YqPM0kDCHYQmGPVeQ/videos" xr:uid="{B70DB9EB-D354-4021-BB8A-DF8D540DA65D}"/>
-    <hyperlink ref="I12" r:id="rId41" display="https://www.youtube.com/c/SamiAlbatati/videos" xr:uid="{E2E2A3F4-4E0F-4CAE-BFC5-FF02DDB056FB}"/>
-    <hyperlink ref="G13" r:id="rId42" display="https://www.youtube.com/c/AliMuhammadAli/videos" xr:uid="{C90F45A7-B0CA-4D80-9F3E-15047C7DD643}"/>
-    <hyperlink ref="F13" r:id="rId43" display="https://www.youtube.com/@a5drcom/videos" xr:uid="{4F602CCB-E90B-41A8-8D77-92CEC2E4FA50}"/>
-    <hyperlink ref="E13" r:id="rId44" display="https://www.youtube.com/channel/UCPnXSD5IUw3YdhUy5emn_qg/videos" xr:uid="{684A01B0-CBF4-4D19-938B-289CADA6AFD2}"/>
-    <hyperlink ref="D13" r:id="rId45" display="http://dar.bibalex.org/webpages/dar.jsf" xr:uid="{8FBD0710-CF66-4060-8DB8-8733691038D6}"/>
-    <hyperlink ref="C13" r:id="rId46" display="https://link.springer.com/" xr:uid="{50BDCAE8-282A-4606-A900-6AA33C0FB243}"/>
-    <hyperlink ref="B13" r:id="rId47" display="https://www.pdfdrive.com/" xr:uid="{6E568A8D-934C-4016-A2AF-C73752C5F9BF}"/>
-    <hyperlink ref="A13" r:id="rId48" display="https://zlibrary.to/" xr:uid="{A3A84337-0CFD-46C1-A9E8-9D3116513A81}"/>
-    <hyperlink ref="H12" r:id="rId49" display="https://www.aseeralkotb.com/" xr:uid="{B48D1149-2882-4796-9423-0319D4C56B36}"/>
-    <hyperlink ref="G12" r:id="rId50" display="https://www.ktaab.com/sections" xr:uid="{DBFE8FA3-FBD0-414D-BAAD-75DFEF8F9981}"/>
-    <hyperlink ref="F12" r:id="rId51" display="https://www.hindawi.org/" xr:uid="{FEC92C61-F3C9-4001-A92F-C51CB4C2B64B}"/>
-    <hyperlink ref="E12" r:id="rId52" display="https://waqfeya.net/index.php" xr:uid="{6A730B5F-A499-4FCB-BA2B-73B5E028B1E2}"/>
-    <hyperlink ref="D12" r:id="rId53" display="https://www.noor-book.com/" xr:uid="{F21F0608-62CE-482D-A266-9F09A9CB6D51}"/>
-    <hyperlink ref="C12" r:id="rId54" display="https://arxiv.org/archive/cs" xr:uid="{A24A4C94-E6C2-4674-8489-71746340F2F1}"/>
-    <hyperlink ref="B12" r:id="rId55" display="https://arxiv.org/archive/math" xr:uid="{DB281A6E-38B9-4C3E-8CA0-E59CBFA03DD2}"/>
-    <hyperlink ref="A12" r:id="rId56" display="https://openstax.org/" xr:uid="{A991F212-3D3E-41B2-A50F-17DBA15BB561}"/>
-    <hyperlink ref="H10" r:id="rId57" display="https://islamhouse.com/ar/favorites/ar/1" xr:uid="{139EC5EC-86E4-4ED8-A5DE-77D728A63F67}"/>
-    <hyperlink ref="G10" r:id="rId58" display="https://www.facebook.com/Islam.anti.atheism" xr:uid="{7CA107BB-12D0-40F1-B227-EECA5EDA3C9D}"/>
-    <hyperlink ref="I9" r:id="rId59" display="https://www.youtube.com/c/Uslameyat1/videos" xr:uid="{D68F1E5D-7FC2-4245-A668-B22AB0BA4D1D}"/>
-    <hyperlink ref="F10" r:id="rId60" display="https://islamqa.info/ar" xr:uid="{9CC82866-8189-48AB-8574-1F9947976B53}"/>
-    <hyperlink ref="C10" r:id="rId61" display="https://www.youtube.com/c/Shuounislamiya/videos" xr:uid="{EBE73D93-A083-48DF-A076-C41368BFD3C2}"/>
-    <hyperlink ref="E10" r:id="rId62" display="https://www.youtube.com/channel/UCMr8VnDU1gojDgzlgkDisxA/videos" xr:uid="{7765CC63-34B1-4A80-97AD-5E82997C8FA1}"/>
-    <hyperlink ref="D10" r:id="rId63" display="https://www.youtube.com/user/Albyyinah/videos" xr:uid="{BB97F436-79C2-4B1D-96AB-FA91EAB37F50}"/>
-    <hyperlink ref="B10" r:id="rId64" display="https://www.youtube.com/channel/UCnc4DP-ohpBFg51ogObyMeQ/videos" xr:uid="{1B054AE7-7906-434B-B29D-A8B2DE30A3E9}"/>
-    <hyperlink ref="A10" r:id="rId65" display="https://www.youtube.com/channel/UCLj8UFOcdFrvlh24Lw7jrgA/videos" xr:uid="{4724DCEE-47D5-4835-98FB-C1E7FC67F74B}"/>
-    <hyperlink ref="I5" location="Post!A1" display="Posts" xr:uid="{E2990330-7D2A-4854-A8B7-29BD2711693F}"/>
-    <hyperlink ref="F9" r:id="rId66" display="https://dorar.net/" xr:uid="{5C263283-4D18-46F9-BA83-A31D6A5E56D1}"/>
-    <hyperlink ref="D9" r:id="rId67" display="https://www.youtube.com/@mekameleen/playlists" xr:uid="{51261E04-35A9-4E94-90C4-1855B85E3A3E}"/>
-    <hyperlink ref="E9" r:id="rId68" display="https://www.facebook.com/AcademyZAD" xr:uid="{18076CB2-D37A-4E6C-B0FF-63A45481BA72}"/>
-    <hyperlink ref="G9" r:id="rId69" display="https://www.youtube.com/@DRMohamedHedayah/videos" xr:uid="{BC00AC04-4BFC-446F-88A6-AAE4039BCE1A}"/>
-    <hyperlink ref="H9" r:id="rId70" display="https://www.islamweb.net/ar" xr:uid="{C60F5FED-8955-4431-8E67-C83830E8F334}"/>
-    <hyperlink ref="A9" r:id="rId71" display="https://www.youtube.com/@SamehElgendawey/videos" xr:uid="{E8F9123C-B974-49BF-8EF1-3301D25DCAE2}"/>
-    <hyperlink ref="B9" r:id="rId72" display="https://www.youtube.com/@osamaoa24/videos" xr:uid="{5AE429ED-AD32-43CB-9F85-15DF00582C06}"/>
-    <hyperlink ref="C9" r:id="rId73" display="https://www.youtube.com/c/BridgesfoundationOrgun/videos" xr:uid="{BD93C02D-6219-45AE-A7E8-E54AD79E6B2F}"/>
-    <hyperlink ref="C7" r:id="rId74" display="https://www.youtube.com/@Archive_Makany_World/videos" xr:uid="{EF71FB90-0CA3-4064-919B-CC073FE46870}"/>
-    <hyperlink ref="I8" r:id="rId75" display="https://www.youtube.com/channel/UCAN2kEVfIk0EC4w4hqhiQUw/videos" xr:uid="{759DCF15-70B5-47D4-A149-173802F53626}"/>
-    <hyperlink ref="G7" r:id="rId76" display="https://www.youtube.com/@Sha5bata/videos" xr:uid="{C17148A2-EB32-45B5-B06B-B0A8F4239BBB}"/>
-    <hyperlink ref="F8" r:id="rId77" display="https://www.youtube.com/@samirmoustafa/videos" xr:uid="{6822F3B1-BEC2-490B-B408-2DA83A89C2F8}"/>
-    <hyperlink ref="E8" r:id="rId78" display="https://www.youtube.com/@DrAlSuwaidan/videos" xr:uid="{29BAC375-1C3A-43C4-BEA8-15E99109F1EB}"/>
-    <hyperlink ref="D8" r:id="rId79" display="https://www.youtube.com/user/FiqhShaf3i/videos" xr:uid="{252E0DCC-C302-4866-9B8A-F0A58CC25BBD}"/>
-    <hyperlink ref="G8" r:id="rId80" display="https://www.youtube.com/@Alkulify1/videos" xr:uid="{793D43BE-7408-439E-995B-2F4BE34C6CD1}"/>
-    <hyperlink ref="C8" r:id="rId81" display="https://www.youtube.com/c/AbdulRazapAlbadr2345/videos" xr:uid="{CE8ED2CC-4E69-40A1-965E-9F5541346BA3}"/>
-    <hyperlink ref="A8" r:id="rId82" display="https://www.youtube.com/user/YasserHozaimy/videos" xr:uid="{0499C3A8-A23B-4BE8-9712-482E670336ED}"/>
-    <hyperlink ref="B8" r:id="rId83" display="https://www.youtube.com/channel/UCScQCjryYxfCeLFdmmMm1EA" xr:uid="{40863D37-1106-4AFA-BADE-261CEED63668}"/>
-    <hyperlink ref="E7" r:id="rId84" display="https://www.youtube.com/user/alsayedtvch1/videos" xr:uid="{2A6AADBD-9487-4FBA-87BD-09D7BAA42AC8}"/>
-    <hyperlink ref="I7" r:id="rId85" display="https://www.facebook.com/3laaHamed" xr:uid="{81B23A21-B187-41D0-A0AE-A59E52F15006}"/>
-    <hyperlink ref="H8" r:id="rId86" display="https://www.youtube.com/channel/UC-GsjCkUB5ndNryHMDdYfTA/videos" xr:uid="{031EB79A-6FDA-49BB-A13A-AB0CC7801A4E}"/>
-    <hyperlink ref="B7" r:id="rId87" display="https://www.youtube.com/c/MakanyWorld/videos" xr:uid="{A826D7B2-004B-4B5D-BCDC-ECABF41494AB}"/>
-    <hyperlink ref="H7" r:id="rId88" display="https://www.youtube.com/channel/UCASAOTD6fMPEg8jmO4nPblQ/videos" xr:uid="{B50BFE26-BAA2-46C4-BB2F-D1894EB7B1BA}"/>
-    <hyperlink ref="D7" r:id="rId89" display="https://www.youtube.com/channel/UCWt3O9HfHs8-LqBFnRj1wZw/videos" xr:uid="{C4545AEB-FFD3-4827-A511-EB25ECC59D0F}"/>
-    <hyperlink ref="F7" r:id="rId90" display="https://www.youtube.com/c/Belaqltube/videos" xr:uid="{C07F1275-C635-416E-AB7E-4E1EB1F702E5}"/>
-    <hyperlink ref="A7" r:id="rId91" display="https://www.youtube.com/c/eyadqunaibi/videos" xr:uid="{43B8E2DC-F96C-4340-8F6C-746048EB98D5}"/>
-    <hyperlink ref="A3" r:id="rId92" display="https://www.facebook.com/mohamedsayedalyhassan" xr:uid="{A0590324-D380-402F-BB13-F20E61254BDA}"/>
-    <hyperlink ref="B2" r:id="rId93" display="https://www.facebook.com/bashmohandesx" xr:uid="{D7762E36-E8AA-428C-9F32-1E7EDED3C576}"/>
-    <hyperlink ref="C2" r:id="rId94" xr:uid="{6300804B-651F-43E0-81FA-1D218C607A69}"/>
-    <hyperlink ref="E21" r:id="rId95" xr:uid="{EA9B63C3-6488-439A-A13C-5838A1D00CA7}"/>
-    <hyperlink ref="I10" r:id="rId96" xr:uid="{F77C77EF-E846-4340-AB3B-35AF20F0D120}"/>
-    <hyperlink ref="E2" r:id="rId97" xr:uid="{F89CF9A0-874B-43BD-BF08-97B343DAC9CD}"/>
-    <hyperlink ref="I4" location="AI!A1" display="AI" xr:uid="{CDA5366C-C760-44C5-ABC5-3700B9EE8122}"/>
-    <hyperlink ref="D21" r:id="rId98" xr:uid="{EBAF2699-8967-4F26-BFA1-A3AEFB61D7E6}"/>
-    <hyperlink ref="A21" r:id="rId99" xr:uid="{E0395C6C-FD09-4709-87D7-67AAC26B3C64}"/>
-    <hyperlink ref="I13" r:id="rId100" xr:uid="{32FBE17A-58AA-43A6-95F3-413C1CF07B71}"/>
-    <hyperlink ref="H2" r:id="rId101" xr:uid="{50514D8B-AA71-45AE-BE0A-C906FCD3CA5F}"/>
-    <hyperlink ref="F2" r:id="rId102" display="PersonalFinanceEgypt" xr:uid="{24D8FE4B-0847-4064-92BD-2597098598FC}"/>
-    <hyperlink ref="G2" r:id="rId103" display="sri_hash_generator" xr:uid="{6B783BD2-2E9F-4F5A-9EF0-557DE66841FC}"/>
-    <hyperlink ref="D3" r:id="rId104" xr:uid="{45C16977-7BCA-47B9-ADD3-84D73D43F510}"/>
-    <hyperlink ref="B3" r:id="rId105" xr:uid="{277FBAA6-1E44-4092-B37E-11C8208136A6}"/>
-    <hyperlink ref="C3" r:id="rId106" xr:uid="{969AC396-5B59-481C-A83A-7CF2FB12E437}"/>
-    <hyperlink ref="H5" r:id="rId107" display="Quran" xr:uid="{1A09DF84-C826-4E70-AF94-16C57942C718}"/>
+    <hyperlink ref="I1" location="Freelaning!A1" display="Freelancing" xr:uid="{00F80706-582F-4B8C-B85C-742129B840A5}"/>
+    <hyperlink ref="A12" r:id="rId5" display="https://learnenglish.britishcouncil.org/online-english-level-test" xr:uid="{490249CD-69D6-4F5C-B5D9-F9B22E5531F8}"/>
+    <hyperlink ref="B12" r:id="rId6" display="https://www.abaenglish.com/en/english-level-test" xr:uid="{C522A13A-66DB-489D-900A-6B52CE61F427}"/>
+    <hyperlink ref="C12" r:id="rId7" display="https://www.facebook.com/BerlitzEgypt" xr:uid="{9A5C3573-1496-4F3A-AC2E-401DDF1DE2CE}"/>
+    <hyperlink ref="C13" r:id="rId8" display="https://www.e2english.com/Home/PlacementTest?gclid=Cj0KCQjwhqaVBhCxARIsAHK1tiMYX2k6u4GzYTpUkafFVpF4BUV_bgOumu6I4thoubdtYzqd9k5NKwoaApt3EALw_wcB" xr:uid="{2E842923-A1CC-4A5D-B40B-DFD523EB31B4}"/>
+    <hyperlink ref="F12" r:id="rId9" display="https://www.languagelevel.com/english/index.php" xr:uid="{6EFB8D37-425E-4F6F-AD3C-219F60B70DFA}"/>
+    <hyperlink ref="G12" r:id="rId10" display="https://www.busuu.com/" xr:uid="{3765DD28-651E-4ABF-98DA-8A09FEBA3C9E}"/>
+    <hyperlink ref="D12" r:id="rId11" display="https://www.bbc.co.uk/learningenglish" xr:uid="{54EB8998-62E4-41FC-84CA-28D8E96E427E}"/>
+    <hyperlink ref="E12" r:id="rId12" display="https://www.espressoenglish.net/english-tips-blog" xr:uid="{3FA836B7-1028-48AE-8951-8C2766989504}"/>
+    <hyperlink ref="A13" r:id="rId13" display="https://www.espressoenglish.net/how-to-learn-english-for-free-50-websites-for-free-english-lessons" xr:uid="{57197D10-C848-4C02-AC29-7E1C3E3E53C8}"/>
+    <hyperlink ref="I11" r:id="rId14" display="https://www.duolingo.com/learn" xr:uid="{FFC13E6E-BCC9-4E40-8811-7AB8A2F09ECB}"/>
+    <hyperlink ref="F13" r:id="rId15" display="https://www.youtube.com/c/ZAmericanEnglish/videos" xr:uid="{7643E7D0-9780-4DA5-AFF2-9ABFC505990B}"/>
+    <hyperlink ref="G13" r:id="rId16" display="https://www.youtube.com/c/VeronikaMark" xr:uid="{482FECE1-83C4-45FC-B270-D2DE2E503994}"/>
+    <hyperlink ref="A14" r:id="rId17" display="https://www.youtube.com/c/LearnEnglishwithBobtheCanadian/videos" xr:uid="{320FB9C0-08FD-49D8-9BA6-49D2314F64B6}"/>
+    <hyperlink ref="B14" r:id="rId18" display="https://www.youtube.com/c/MasterEnglish/videos" xr:uid="{10FCE5BE-82DA-4E1C-9BB1-542F1309E879}"/>
+    <hyperlink ref="E13" r:id="rId19" display="https://www.youtube.com/c/GoNaturalEnglish/videos" xr:uid="{DBE65AC5-86BA-480A-9D64-15A49991CECD}"/>
+    <hyperlink ref="E14" r:id="rId20" display="https://www.youtube.com/c/englishforyoutv" xr:uid="{6FFC4B5D-0D78-4AC1-9CA7-CC90A8AB6CB4}"/>
+    <hyperlink ref="F14" r:id="rId21" display="https://www.youtube.com/user/EnglishAnyone" xr:uid="{29DAA25A-6ABD-403A-A90D-654AED8B66B5}"/>
+    <hyperlink ref="C14" r:id="rId22" display="https://www.youtube.com/c/rachelsenglish" xr:uid="{850BA37C-D43A-47C1-8F0B-3950FCC6A227}"/>
+    <hyperlink ref="D14" r:id="rId23" display="https://www.youtube.com/c/mmmEnglish_Emma" xr:uid="{97CA62D5-C3C6-4137-9685-0968A587D3CD}"/>
+    <hyperlink ref="H13" r:id="rId24" display="https://www.youtube.com/c/AmigosIngleses/videos" xr:uid="{9BD15DB6-75AF-444E-BB8F-4E80131B7199}"/>
+    <hyperlink ref="H12" r:id="rId25" display="Single Step English" xr:uid="{89EC801F-7A89-4271-9961-FEE438084B14}"/>
+    <hyperlink ref="H14" r:id="rId26" display="https://www.youtube.com/c/OneMinuteEnglish/videos" xr:uid="{39A0FD1C-A0F1-493D-BCA4-66D8345DB928}"/>
+    <hyperlink ref="D13" r:id="rId27" xr:uid="{C144C009-46AA-423D-ADDB-A8B36273830F}"/>
+    <hyperlink ref="I14" r:id="rId28" xr:uid="{ACE42FCC-AAD7-4632-B2D8-8EFFCA4B5BA1}"/>
+    <hyperlink ref="B13" r:id="rId29" xr:uid="{13D5419E-228F-4DA1-A26A-3BC212A3A7A9}"/>
+    <hyperlink ref="G14" r:id="rId30" display="EdMo Tests and Quizzes " xr:uid="{5AE54B23-DDD8-4A58-9D7D-459206AB2EEB}"/>
+    <hyperlink ref="I12" r:id="rId31" display="Culips " xr:uid="{3784E8EE-E16C-459E-9B59-47B6ED00BCAA}"/>
+    <hyperlink ref="I13" r:id="rId32" display="https://www.youtube.com/c/EnglishwithLucy/videos" xr:uid="{E6ECFE11-8A70-4700-A357-B0B1516B8954}"/>
+    <hyperlink ref="H11" r:id="rId33" display="https://www.youtube.com/c/EnglishClass101/videos" xr:uid="{677F7135-2D2E-4D83-B9A9-CF5C49A9FC41}"/>
+    <hyperlink ref="B3" r:id="rId34" xr:uid="{BFF4F3ED-2E98-4610-8C03-5273DF52C8DC}"/>
+    <hyperlink ref="E11" r:id="rId35" display="https://learningenglish.voanews.com/" xr:uid="{2B47E0B5-3EB5-443C-8F99-08E3DEDAB1D4}"/>
+    <hyperlink ref="F11" r:id="rId36" display="https://www.cambly.com/english?lang=en" xr:uid="{DC5DBA3B-121D-4C50-A347-1E99DB4C82A0}"/>
+    <hyperlink ref="G11" r:id="rId37" display="https://www.aucegypt.edu/ar" xr:uid="{D09BB70C-8FD6-4368-94E0-9285BC36CC71}"/>
+    <hyperlink ref="B11" r:id="rId38" display="https://www.cambridgeenglish.org/" xr:uid="{80219548-CF0A-464B-B939-323B5009D1F6}"/>
+    <hyperlink ref="A11" r:id="rId39" display="https://englishteststore.net/" xr:uid="{C2EFF72A-A901-4792-833C-7B67D27C9B84}"/>
+    <hyperlink ref="H9" r:id="rId40" display="https://www.youtube.com/channel/UCyQw44YqPM0kDCHYQmGPVeQ/videos" xr:uid="{B70DB9EB-D354-4021-BB8A-DF8D540DA65D}"/>
+    <hyperlink ref="I8" r:id="rId41" display="https://www.youtube.com/c/SamiAlbatati/videos" xr:uid="{E2E2A3F4-4E0F-4CAE-BFC5-FF02DDB056FB}"/>
+    <hyperlink ref="G9" r:id="rId42" display="https://www.youtube.com/c/AliMuhammadAli/videos" xr:uid="{C90F45A7-B0CA-4D80-9F3E-15047C7DD643}"/>
+    <hyperlink ref="F9" r:id="rId43" display="https://www.youtube.com/@a5drcom/videos" xr:uid="{4F602CCB-E90B-41A8-8D77-92CEC2E4FA50}"/>
+    <hyperlink ref="E9" r:id="rId44" display="https://www.youtube.com/channel/UCPnXSD5IUw3YdhUy5emn_qg/videos" xr:uid="{684A01B0-CBF4-4D19-938B-289CADA6AFD2}"/>
+    <hyperlink ref="D9" r:id="rId45" display="http://dar.bibalex.org/webpages/dar.jsf" xr:uid="{8FBD0710-CF66-4060-8DB8-8733691038D6}"/>
+    <hyperlink ref="C9" r:id="rId46" display="https://link.springer.com/" xr:uid="{50BDCAE8-282A-4606-A900-6AA33C0FB243}"/>
+    <hyperlink ref="B9" r:id="rId47" display="https://www.pdfdrive.com/" xr:uid="{6E568A8D-934C-4016-A2AF-C73752C5F9BF}"/>
+    <hyperlink ref="A9" r:id="rId48" display="https://zlibrary.to/" xr:uid="{A3A84337-0CFD-46C1-A9E8-9D3116513A81}"/>
+    <hyperlink ref="H8" r:id="rId49" display="https://www.aseeralkotb.com/" xr:uid="{B48D1149-2882-4796-9423-0319D4C56B36}"/>
+    <hyperlink ref="G8" r:id="rId50" display="https://www.ktaab.com/sections" xr:uid="{DBFE8FA3-FBD0-414D-BAAD-75DFEF8F9981}"/>
+    <hyperlink ref="F8" r:id="rId51" display="https://www.hindawi.org/" xr:uid="{FEC92C61-F3C9-4001-A92F-C51CB4C2B64B}"/>
+    <hyperlink ref="E8" r:id="rId52" display="https://waqfeya.net/index.php" xr:uid="{6A730B5F-A499-4FCB-BA2B-73B5E028B1E2}"/>
+    <hyperlink ref="D8" r:id="rId53" display="https://www.noor-book.com/" xr:uid="{F21F0608-62CE-482D-A266-9F09A9CB6D51}"/>
+    <hyperlink ref="C8" r:id="rId54" display="https://arxiv.org/archive/cs" xr:uid="{A24A4C94-E6C2-4674-8489-71746340F2F1}"/>
+    <hyperlink ref="B8" r:id="rId55" display="https://arxiv.org/archive/math" xr:uid="{DB281A6E-38B9-4C3E-8CA0-E59CBFA03DD2}"/>
+    <hyperlink ref="A8" r:id="rId56" display="https://openstax.org/" xr:uid="{A991F212-3D3E-41B2-A50F-17DBA15BB561}"/>
+    <hyperlink ref="E6" r:id="rId57" display="https://www.youtube.com/c/Shuounislamiya/videos" xr:uid="{EBE73D93-A083-48DF-A076-C41368BFD3C2}"/>
+    <hyperlink ref="F6" r:id="rId58" display="https://www.youtube.com/user/Albyyinah/videos" xr:uid="{BB97F436-79C2-4B1D-96AB-FA91EAB37F50}"/>
+    <hyperlink ref="D6" r:id="rId59" display="https://www.youtube.com/channel/UCnc4DP-ohpBFg51ogObyMeQ/videos" xr:uid="{1B054AE7-7906-434B-B29D-A8B2DE30A3E9}"/>
+    <hyperlink ref="I3" location="Post!A1" display="Posts" xr:uid="{E2990330-7D2A-4854-A8B7-29BD2711693F}"/>
+    <hyperlink ref="C6" r:id="rId60" display="https://www.facebook.com/AcademyZAD" xr:uid="{18076CB2-D37A-4E6C-B0FF-63A45481BA72}"/>
+    <hyperlink ref="B5" r:id="rId61" display="https://www.youtube.com/@Archive_Makany_World/videos" xr:uid="{EF71FB90-0CA3-4064-919B-CC073FE46870}"/>
+    <hyperlink ref="D5" r:id="rId62" display="https://www.youtube.com/@Sha5bata/videos" xr:uid="{C17148A2-EB32-45B5-B06B-B0A8F4239BBB}"/>
+    <hyperlink ref="E5" r:id="rId63" display="https://www.youtube.com/@samirmoustafa/videos" xr:uid="{6822F3B1-BEC2-490B-B408-2DA83A89C2F8}"/>
+    <hyperlink ref="A6" r:id="rId64" display="https://www.youtube.com/@Alkulify1/videos" xr:uid="{793D43BE-7408-439E-995B-2F4BE34C6CD1}"/>
+    <hyperlink ref="H5" r:id="rId65" display="https://www.youtube.com/c/AbdulRazapAlbadr2345/videos" xr:uid="{CE8ED2CC-4E69-40A1-965E-9F5541346BA3}"/>
+    <hyperlink ref="F5" r:id="rId66" display="https://www.youtube.com/user/YasserHozaimy/videos" xr:uid="{0499C3A8-A23B-4BE8-9712-482E670336ED}"/>
+    <hyperlink ref="G5" r:id="rId67" display="https://www.youtube.com/channel/UCScQCjryYxfCeLFdmmMm1EA" xr:uid="{40863D37-1106-4AFA-BADE-261CEED63668}"/>
+    <hyperlink ref="B6" r:id="rId68" display="https://www.youtube.com/channel/UC-GsjCkUB5ndNryHMDdYfTA/videos" xr:uid="{031EB79A-6FDA-49BB-A13A-AB0CC7801A4E}"/>
+    <hyperlink ref="A5" r:id="rId69" display="https://www.youtube.com/c/MakanyWorld/videos" xr:uid="{A826D7B2-004B-4B5D-BCDC-ECABF41494AB}"/>
+    <hyperlink ref="C5" r:id="rId70" display="https://www.youtube.com/channel/UCWt3O9HfHs8-LqBFnRj1wZw/videos" xr:uid="{C4545AEB-FFD3-4827-A511-EB25ECC59D0F}"/>
+    <hyperlink ref="D2" r:id="rId71" display="https://www.facebook.com/mohamedsayedalyhassan" xr:uid="{A0590324-D380-402F-BB13-F20E61254BDA}"/>
+    <hyperlink ref="B2" r:id="rId72" display="https://www.facebook.com/bashmohandesx" xr:uid="{D7762E36-E8AA-428C-9F32-1E7EDED3C576}"/>
+    <hyperlink ref="C2" r:id="rId73" xr:uid="{6300804B-651F-43E0-81FA-1D218C607A69}"/>
+    <hyperlink ref="F3" r:id="rId74" xr:uid="{E0395C6C-FD09-4709-87D7-67AAC26B3C64}"/>
+    <hyperlink ref="I9" r:id="rId75" xr:uid="{32FBE17A-58AA-43A6-95F3-413C1CF07B71}"/>
+    <hyperlink ref="F2" r:id="rId76" xr:uid="{50514D8B-AA71-45AE-BE0A-C906FCD3CA5F}"/>
+    <hyperlink ref="E2" r:id="rId77" display="PersonalFinanceEgypt" xr:uid="{24D8FE4B-0847-4064-92BD-2597098598FC}"/>
+    <hyperlink ref="E3" r:id="rId78" display="sri_hash_generator" xr:uid="{6B783BD2-2E9F-4F5A-9EF0-557DE66841FC}"/>
+    <hyperlink ref="H3" r:id="rId79" xr:uid="{45C16977-7BCA-47B9-ADD3-84D73D43F510}"/>
+    <hyperlink ref="A3" r:id="rId80" xr:uid="{277FBAA6-1E44-4092-B37E-11C8208136A6}"/>
+    <hyperlink ref="H2" r:id="rId81" xr:uid="{969AC396-5B59-481C-A83A-7CF2FB12E437}"/>
+    <hyperlink ref="G3" r:id="rId82" display="Quran" xr:uid="{1A09DF84-C826-4E70-AF94-16C57942C718}"/>
+    <hyperlink ref="I5" r:id="rId83" xr:uid="{AE6A0070-D481-4725-8D96-23887A6B2F88}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId108"/>
+  <pageSetup orientation="portrait" r:id="rId84"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73EAC2E5-A839-4CFE-81CB-B3D389005C51}">
-  <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="17.140625" style="44" customWidth="1"/>
-    <col min="2" max="2" width="25" style="44" customWidth="1"/>
-    <col min="3" max="3" width="46.42578125" style="44" customWidth="1"/>
-    <col min="4" max="4" width="1.85546875" style="44" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="44" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="44" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" style="44" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" style="44" customWidth="1"/>
-    <col min="9" max="9" width="24" style="44" customWidth="1"/>
-    <col min="10" max="10" width="1.5703125" style="44" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="44" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="44"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="93" t="s">
-        <v>380</v>
-      </c>
-      <c r="B1" s="92" t="s">
-        <v>379</v>
-      </c>
-      <c r="C1" s="91" t="s">
-        <v>378</v>
-      </c>
-      <c r="E1" s="90" t="s">
-        <v>377</v>
-      </c>
-      <c r="F1" s="89" t="s">
-        <v>376</v>
-      </c>
-      <c r="G1" s="88" t="s">
-        <v>375</v>
-      </c>
-      <c r="H1" s="88" t="s">
-        <v>374</v>
-      </c>
-      <c r="I1" s="87" t="s">
-        <v>373</v>
-      </c>
-      <c r="K1" s="234" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="241" t="s">
-        <v>372</v>
-      </c>
-      <c r="B2" s="86" t="s">
-        <v>371</v>
-      </c>
-      <c r="C2" s="53" t="s">
-        <v>370</v>
-      </c>
-      <c r="E2" s="255" t="s">
-        <v>369</v>
-      </c>
-      <c r="F2" s="85" t="s">
-        <v>368</v>
-      </c>
-      <c r="G2" s="84" t="s">
-        <v>367</v>
-      </c>
-      <c r="H2" s="84" t="s">
-        <v>366</v>
-      </c>
-      <c r="I2" s="83"/>
-      <c r="K2" s="235"/>
-    </row>
-    <row r="3" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="241"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="53" t="s">
-        <v>365</v>
-      </c>
-      <c r="E3" s="256"/>
-      <c r="F3" s="82" t="s">
-        <v>364</v>
-      </c>
-      <c r="G3" s="81" t="s">
-        <v>363</v>
-      </c>
-      <c r="H3" s="81"/>
-      <c r="I3" s="80"/>
-    </row>
-    <row r="4" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="241"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="53"/>
-      <c r="E4" s="257"/>
-      <c r="F4" s="79" t="s">
-        <v>362</v>
-      </c>
-      <c r="G4" s="78">
-        <v>44</v>
-      </c>
-      <c r="H4" s="78" t="s">
-        <v>361</v>
-      </c>
-      <c r="I4" s="77" t="s">
-        <v>330</v>
-      </c>
-      <c r="K4" s="243" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="241"/>
-      <c r="B5" s="73"/>
-      <c r="C5" s="53"/>
-      <c r="E5" s="246" t="s">
-        <v>359</v>
-      </c>
-      <c r="F5" s="76" t="s">
-        <v>355</v>
-      </c>
-      <c r="G5" s="75" t="s">
-        <v>358</v>
-      </c>
-      <c r="H5" s="75"/>
-      <c r="I5" s="74" t="s">
-        <v>357</v>
-      </c>
-      <c r="K5" s="244"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="241"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="53"/>
-      <c r="E6" s="247"/>
-      <c r="F6" s="72" t="s">
-        <v>356</v>
-      </c>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="70"/>
-    </row>
-    <row r="7" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="241" t="s">
-        <v>355</v>
-      </c>
-      <c r="B7" s="54" t="s">
-        <v>354</v>
-      </c>
-      <c r="C7" s="53" t="s">
-        <v>353</v>
-      </c>
-      <c r="E7" s="248"/>
-      <c r="F7" s="69" t="s">
-        <v>352</v>
-      </c>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="67"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="241"/>
-      <c r="B8" s="252" t="s">
-        <v>351</v>
-      </c>
-      <c r="C8" s="53" t="s">
-        <v>350</v>
-      </c>
-      <c r="E8" s="249" t="s">
-        <v>349</v>
-      </c>
-      <c r="F8" s="66" t="s">
-        <v>348</v>
-      </c>
-      <c r="G8" s="253">
-        <v>1.8229166666666667</v>
-      </c>
-      <c r="H8" s="65"/>
-      <c r="I8" s="64"/>
-    </row>
-    <row r="9" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="241"/>
-      <c r="B9" s="252"/>
-      <c r="C9" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="E9" s="250"/>
-      <c r="F9" s="63" t="s">
-        <v>346</v>
-      </c>
-      <c r="G9" s="254"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="61"/>
-    </row>
-    <row r="10" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="241"/>
-      <c r="B10" s="43" t="s">
-        <v>345</v>
-      </c>
-      <c r="C10" s="53"/>
-    </row>
-    <row r="11" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="241" t="s">
-        <v>344</v>
-      </c>
-      <c r="B11" s="60" t="s">
-        <v>343</v>
-      </c>
-      <c r="C11" s="53"/>
-      <c r="E11" s="251" t="s">
-        <v>342</v>
-      </c>
-      <c r="F11" s="59" t="s">
-        <v>341</v>
-      </c>
-      <c r="I11" s="242" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="241"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="53"/>
-      <c r="E12" s="241"/>
-      <c r="F12" s="58" t="s">
-        <v>339</v>
-      </c>
-      <c r="I12" s="242"/>
-    </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="241"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="53"/>
-      <c r="E13" s="241"/>
-      <c r="F13" s="57"/>
-      <c r="I13" s="242"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="241"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="53"/>
-      <c r="E14" s="241"/>
-      <c r="F14" s="57"/>
-      <c r="I14" s="55" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="241"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="53"/>
-      <c r="E15" s="245"/>
-      <c r="F15" s="56"/>
-      <c r="I15" s="55" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="241"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="53"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="241" t="s">
-        <v>336</v>
-      </c>
-      <c r="B17" s="54" t="s">
-        <v>335</v>
-      </c>
-      <c r="C17" s="53"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="241"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="53"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="241"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="53"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="245"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="51"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="238" t="s">
-        <v>334</v>
-      </c>
-      <c r="B22" s="239"/>
-      <c r="C22" s="240"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="50" t="s">
-        <v>332</v>
-      </c>
-      <c r="B23" s="49" t="s">
-        <v>333</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="47" t="s">
-        <v>332</v>
-      </c>
-      <c r="B24" s="46" t="s">
-        <v>331</v>
-      </c>
-      <c r="C24" s="45" t="s">
-        <v>330</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E11:E15"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="E2:E4"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{B988A63C-7553-41F6-967C-BC88E6F5E3DD}"/>
-    <hyperlink ref="B8:B9" r:id="rId2" display="الحفاظ علي البنطلون الجينس" xr:uid="{880237D1-1B91-4C64-A6CC-22BC2270CA94}"/>
-    <hyperlink ref="B11" r:id="rId3" display="انواع الريحة لازم في الخطوبة" xr:uid="{B7F74BA0-EC89-4678-95F7-816C16AFC981}"/>
-    <hyperlink ref="B17" r:id="rId4" xr:uid="{31AFDD69-1797-4DAD-8122-5ED1B8D405D5}"/>
-    <hyperlink ref="K1" location="Food!A1" display="رجوع" xr:uid="{6CB8AB43-919C-4D43-A984-3DA84D1F460C}"/>
-    <hyperlink ref="B2" r:id="rId5" xr:uid="{6B4AFA1A-2287-47DD-875E-678BCED22632}"/>
-    <hyperlink ref="F12" r:id="rId6" xr:uid="{698456EB-C81D-445D-9CE2-1B1D1C262E82}"/>
-    <hyperlink ref="F11" r:id="rId7" xr:uid="{C73669CA-12C8-4426-9434-BBBFFBC26F01}"/>
-    <hyperlink ref="K4:K5" location="Suit!A1" display="Good Suit" xr:uid="{7F379537-317A-44E4-8081-EAD6202FE71E}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId8"/>
-  <drawing r:id="rId9"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E6618AA-AE09-4C49-A204-1817CC12D7FC}">
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
-        <v>402</v>
-      </c>
-      <c r="B1" s="98" t="s">
-        <v>401</v>
-      </c>
-      <c r="C1" s="98" t="s">
-        <v>400</v>
-      </c>
-      <c r="D1" s="98" t="s">
-        <v>399</v>
-      </c>
-      <c r="E1" s="98" t="s">
-        <v>398</v>
-      </c>
-      <c r="F1" s="98" t="s">
-        <v>397</v>
-      </c>
-      <c r="H1" s="234" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="96" t="s">
-        <v>396</v>
-      </c>
-      <c r="B2" s="43" t="s">
-        <v>395</v>
-      </c>
-      <c r="C2" s="43" t="s">
-        <v>395</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="E2" s="43">
-        <v>2</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="H2" s="235"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="96" t="s">
-        <v>394</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="D3" s="43">
-        <v>15</v>
-      </c>
-      <c r="E3" s="43">
-        <v>3</v>
-      </c>
-      <c r="F3" s="97" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="96" t="s">
-        <v>393</v>
-      </c>
-      <c r="B4" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="D4" s="43">
-        <v>15</v>
-      </c>
-      <c r="E4" s="43">
-        <v>3</v>
-      </c>
-      <c r="F4" s="97" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="96" t="s">
-        <v>391</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>390</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>390</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="96" t="s">
-        <v>389</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="D6" s="43">
-        <v>15</v>
-      </c>
-      <c r="E6" s="43">
-        <v>3</v>
-      </c>
-      <c r="F6" s="43" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="96" t="s">
-        <v>388</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="D7" s="43">
-        <v>15</v>
-      </c>
-      <c r="E7" s="43">
-        <v>3</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="96" t="s">
-        <v>387</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="D8" s="43">
-        <v>50</v>
-      </c>
-      <c r="E8" s="43">
-        <v>2</v>
-      </c>
-      <c r="F8" s="43" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="96"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="96"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="96"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="96"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="96"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="96"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="96"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="96"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="96"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="96"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="95" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="95" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="95" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="95" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="94" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="94"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:H2"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="H1" location="Food!A1" display="رجوع" xr:uid="{B51BC1D8-BE8F-4685-B797-B33661E6AC7E}"/>
-    <hyperlink ref="B20" r:id="rId1" xr:uid="{D0CD5B75-8B58-4EF0-A785-5AD62082792B}"/>
-    <hyperlink ref="B22" r:id="rId2" xr:uid="{C5E299F2-4960-4620-AB15-17E8CAB7DD92}"/>
-    <hyperlink ref="B23" r:id="rId3" xr:uid="{CF66D09A-5242-470B-A8B0-98F885522A00}"/>
-    <hyperlink ref="B21" r:id="rId4" xr:uid="{BBD8B956-1626-45FB-96C8-F75C27E7B01C}"/>
-    <hyperlink ref="B24" r:id="rId5" xr:uid="{75EA1F4B-79B3-48D3-8124-7958DF345360}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938CE309-CBD9-4E7B-AEF7-6480C043974A}">
   <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6811,328 +5696,328 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="102" t="s">
-        <v>427</v>
-      </c>
-      <c r="B1" s="100" t="s">
-        <v>426</v>
-      </c>
-      <c r="C1" s="102" t="s">
-        <v>425</v>
-      </c>
-      <c r="D1" s="101"/>
+      <c r="A1" s="100" t="s">
+        <v>348</v>
+      </c>
+      <c r="B1" s="98" t="s">
+        <v>347</v>
+      </c>
+      <c r="C1" s="100" t="s">
+        <v>346</v>
+      </c>
+      <c r="D1" s="99"/>
     </row>
     <row r="2" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="102" t="s">
-        <v>424</v>
-      </c>
-      <c r="B2" s="102" t="s">
-        <v>423</v>
-      </c>
-      <c r="C2" s="102" t="s">
-        <v>422</v>
-      </c>
-      <c r="D2" s="101"/>
+      <c r="A2" s="100" t="s">
+        <v>345</v>
+      </c>
+      <c r="B2" s="100" t="s">
+        <v>344</v>
+      </c>
+      <c r="C2" s="100" t="s">
+        <v>343</v>
+      </c>
+      <c r="D2" s="99"/>
     </row>
     <row r="3" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="102" t="s">
-        <v>421</v>
-      </c>
-      <c r="B3" s="102" t="s">
-        <v>420</v>
-      </c>
-      <c r="C3" s="102" t="s">
-        <v>419</v>
-      </c>
-      <c r="D3" s="104"/>
+      <c r="A3" s="100" t="s">
+        <v>342</v>
+      </c>
+      <c r="B3" s="100" t="s">
+        <v>341</v>
+      </c>
+      <c r="C3" s="100" t="s">
+        <v>340</v>
+      </c>
+      <c r="D3" s="102"/>
     </row>
     <row r="4" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="102" t="s">
-        <v>484</v>
-      </c>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="104"/>
+      <c r="A4" s="100" t="s">
+        <v>404</v>
+      </c>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="102"/>
     </row>
     <row r="5" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="101"/>
-      <c r="B5" s="100" t="s">
-        <v>418</v>
-      </c>
-      <c r="C5" s="102" t="s">
-        <v>417</v>
-      </c>
-      <c r="D5" s="103"/>
+      <c r="A5" s="99"/>
+      <c r="B5" s="98" t="s">
+        <v>339</v>
+      </c>
+      <c r="C5" s="100" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" s="101"/>
     </row>
     <row r="6" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="102" t="s">
-        <v>416</v>
-      </c>
-      <c r="B6" s="102" t="s">
-        <v>415</v>
-      </c>
-      <c r="C6" s="102" t="s">
-        <v>414</v>
-      </c>
-      <c r="D6" s="103"/>
+      <c r="A6" s="100" t="s">
+        <v>337</v>
+      </c>
+      <c r="B6" s="100" t="s">
+        <v>336</v>
+      </c>
+      <c r="C6" s="100" t="s">
+        <v>335</v>
+      </c>
+      <c r="D6" s="101"/>
     </row>
     <row r="7" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="102" t="s">
-        <v>413</v>
-      </c>
-      <c r="B7" s="101"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="101"/>
+      <c r="A7" s="100" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" s="99"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99"/>
     </row>
     <row r="8" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="101"/>
-      <c r="B8" s="100" t="s">
-        <v>412</v>
-      </c>
-      <c r="C8" s="100" t="s">
-        <v>411</v>
-      </c>
-      <c r="D8" s="100" t="s">
-        <v>410</v>
+      <c r="A8" s="99"/>
+      <c r="B8" s="98" t="s">
+        <v>333</v>
+      </c>
+      <c r="C8" s="98" t="s">
+        <v>332</v>
+      </c>
+      <c r="D8" s="98" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="100" t="s">
-        <v>409</v>
-      </c>
-      <c r="B9" s="100" t="s">
-        <v>408</v>
-      </c>
-      <c r="C9" s="100" t="s">
-        <v>407</v>
-      </c>
-      <c r="D9" s="100" t="s">
-        <v>406</v>
+      <c r="A9" s="98" t="s">
+        <v>330</v>
+      </c>
+      <c r="B9" s="98" t="s">
+        <v>329</v>
+      </c>
+      <c r="C9" s="98" t="s">
+        <v>328</v>
+      </c>
+      <c r="D9" s="98" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="100" t="s">
-        <v>405</v>
-      </c>
-      <c r="B10" s="100" t="s">
-        <v>404</v>
-      </c>
-      <c r="C10" s="100" t="s">
-        <v>403</v>
-      </c>
-      <c r="D10" s="99"/>
+      <c r="A10" s="98" t="s">
+        <v>326</v>
+      </c>
+      <c r="B10" s="98" t="s">
+        <v>325</v>
+      </c>
+      <c r="C10" s="98" t="s">
+        <v>324</v>
+      </c>
+      <c r="D10" s="97"/>
     </row>
     <row r="11" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="99"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
+      <c r="A11" s="97"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
     </row>
     <row r="13" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="106" t="s">
-        <v>438</v>
-      </c>
-      <c r="B13" s="106" t="s">
-        <v>437</v>
-      </c>
-      <c r="C13" s="106" t="s">
-        <v>436</v>
-      </c>
-      <c r="D13" s="106" t="s">
-        <v>435</v>
+      <c r="A13" s="104" t="s">
+        <v>359</v>
+      </c>
+      <c r="B13" s="104" t="s">
+        <v>358</v>
+      </c>
+      <c r="C13" s="104" t="s">
+        <v>357</v>
+      </c>
+      <c r="D13" s="104" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="105" t="s">
-        <v>434</v>
-      </c>
-      <c r="B14" s="105"/>
-      <c r="C14" s="105"/>
-      <c r="D14" s="105"/>
+      <c r="A14" s="103" t="s">
+        <v>355</v>
+      </c>
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
     </row>
     <row r="15" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="105" t="s">
-        <v>433</v>
-      </c>
-      <c r="B15" s="105"/>
-      <c r="C15" s="105"/>
-      <c r="D15" s="105"/>
+      <c r="A15" s="103" t="s">
+        <v>354</v>
+      </c>
+      <c r="B15" s="103"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
     </row>
     <row r="16" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="105" t="s">
-        <v>432</v>
-      </c>
-      <c r="B16" s="105"/>
-      <c r="C16" s="105"/>
-      <c r="D16" s="105"/>
+      <c r="A16" s="103" t="s">
+        <v>353</v>
+      </c>
+      <c r="B16" s="103"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
     </row>
     <row r="17" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="105" t="s">
-        <v>431</v>
-      </c>
-      <c r="B17" s="105"/>
-      <c r="C17" s="105"/>
-      <c r="D17" s="105"/>
+      <c r="A17" s="103" t="s">
+        <v>352</v>
+      </c>
+      <c r="B17" s="103"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
     </row>
     <row r="18" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="105" t="s">
-        <v>430</v>
-      </c>
-      <c r="B18" s="105"/>
-      <c r="C18" s="105"/>
-      <c r="D18" s="105"/>
+      <c r="A18" s="103" t="s">
+        <v>351</v>
+      </c>
+      <c r="B18" s="103"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
     </row>
     <row r="19" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="105" t="s">
-        <v>429</v>
-      </c>
-      <c r="B19" s="105"/>
-      <c r="C19" s="105"/>
-      <c r="D19" s="105"/>
+      <c r="A19" s="103" t="s">
+        <v>350</v>
+      </c>
+      <c r="B19" s="103"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="103"/>
     </row>
     <row r="20" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="105" t="s">
-        <v>428</v>
-      </c>
-      <c r="B20" s="105"/>
-      <c r="C20" s="105"/>
-      <c r="D20" s="105"/>
+      <c r="A20" s="103" t="s">
+        <v>349</v>
+      </c>
+      <c r="B20" s="103"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="103"/>
     </row>
     <row r="27" spans="1:5" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="112" t="s">
-        <v>447</v>
-      </c>
-      <c r="B27" s="112" t="s">
-        <v>446</v>
-      </c>
-      <c r="C27" s="112" t="s">
-        <v>445</v>
-      </c>
-      <c r="D27" s="112" t="s">
-        <v>444</v>
-      </c>
-      <c r="E27" s="112" t="s">
-        <v>443</v>
+      <c r="A27" s="110" t="s">
+        <v>368</v>
+      </c>
+      <c r="B27" s="110" t="s">
+        <v>367</v>
+      </c>
+      <c r="C27" s="110" t="s">
+        <v>366</v>
+      </c>
+      <c r="D27" s="110" t="s">
+        <v>365</v>
+      </c>
+      <c r="E27" s="110" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="108" t="s">
-        <v>442</v>
-      </c>
-      <c r="B28" s="110" t="s">
-        <v>441</v>
-      </c>
-      <c r="C28" s="110">
+      <c r="A28" s="106" t="s">
+        <v>363</v>
+      </c>
+      <c r="B28" s="108" t="s">
+        <v>362</v>
+      </c>
+      <c r="C28" s="108">
         <v>1227504373</v>
       </c>
-      <c r="D28" s="110">
+      <c r="D28" s="108">
         <v>1023409495</v>
       </c>
-      <c r="E28" s="110">
+      <c r="E28" s="108">
         <v>1115204079</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="108" t="s">
-        <v>442</v>
-      </c>
-      <c r="B29" s="110" t="s">
-        <v>441</v>
-      </c>
-      <c r="C29" s="110">
+      <c r="A29" s="106" t="s">
+        <v>363</v>
+      </c>
+      <c r="B29" s="108" t="s">
+        <v>362</v>
+      </c>
+      <c r="C29" s="108">
         <v>1028358685</v>
       </c>
-      <c r="D29" s="110">
+      <c r="D29" s="108">
         <v>1221416005</v>
       </c>
-      <c r="E29" s="108"/>
+      <c r="E29" s="106"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="109" t="s">
-        <v>440</v>
-      </c>
-      <c r="B30" s="108" t="s">
-        <v>439</v>
-      </c>
-      <c r="C30" s="108">
+      <c r="A30" s="107" t="s">
+        <v>361</v>
+      </c>
+      <c r="B30" s="106" t="s">
+        <v>360</v>
+      </c>
+      <c r="C30" s="106">
         <v>1125519116</v>
       </c>
-      <c r="D30" s="108"/>
-      <c r="E30" s="108"/>
+      <c r="D30" s="106"/>
+      <c r="E30" s="106"/>
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="108"/>
-      <c r="B31" s="108"/>
-      <c r="C31" s="108"/>
-      <c r="D31" s="108"/>
-      <c r="E31" s="108"/>
+      <c r="A31" s="106"/>
+      <c r="B31" s="106"/>
+      <c r="C31" s="106"/>
+      <c r="D31" s="106"/>
+      <c r="E31" s="106"/>
     </row>
     <row r="35" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="116" t="s">
-        <v>460</v>
+      <c r="A35" s="114" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="115" t="s">
-        <v>459</v>
+      <c r="A36" s="113" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="115" t="s">
-        <v>458</v>
+      <c r="A37" s="113" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="115" t="s">
-        <v>457</v>
+      <c r="A38" s="113" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="115" t="s">
-        <v>456</v>
+      <c r="A39" s="113" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="115" t="s">
-        <v>455</v>
+      <c r="A40" s="113" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="115" t="s">
-        <v>454</v>
+      <c r="A41" s="113" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
-        <v>453</v>
+      <c r="A42" s="113" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="115" t="s">
-        <v>452</v>
+      <c r="A43" s="113" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="115" t="s">
-        <v>451</v>
+      <c r="A44" s="113" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="115" t="s">
-        <v>450</v>
+      <c r="A45" s="113" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="115" t="s">
-        <v>449</v>
+      <c r="A46" s="113" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="114"/>
+      <c r="A47" s="112"/>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="113" t="s">
-        <v>448</v>
+      <c r="A48" s="111" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -7172,53 +6057,53 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC843F6-2887-4BE1-A36B-BE9F1EA31AD0}">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="24.28515625" defaultRowHeight="69.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>464</v>
+        <v>384</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>465</v>
+        <v>385</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>466</v>
+        <v>386</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>467</v>
+        <v>387</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>468</v>
+        <v>388</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>469</v>
+        <v>389</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>470</v>
+        <v>390</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>471</v>
+        <v>391</v>
       </c>
       <c r="I1" s="4"/>
     </row>
     <row r="2" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>472</v>
+        <v>392</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>473</v>
+        <v>393</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>473</v>
+        <v>393</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>473</v>
+        <v>393</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>474</v>
+        <v>394</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -7300,7 +6185,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B540495-B4AD-4CA9-A206-F86AB5A39250}">
   <dimension ref="A1:I75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7315,944 +6200,944 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="165" t="s">
-        <v>584</v>
-      </c>
-      <c r="B1" s="165" t="s">
-        <v>585</v>
-      </c>
-      <c r="C1" s="165" t="s">
-        <v>586</v>
+      <c r="A1" s="161" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1" s="161" t="s">
+        <v>504</v>
+      </c>
+      <c r="C1" s="161" t="s">
+        <v>505</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="E1" s="166" t="s">
-        <v>588</v>
+        <v>506</v>
+      </c>
+      <c r="E1" s="162" t="s">
+        <v>507</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>589</v>
+        <v>508</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="H1" s="167"/>
-      <c r="I1" s="168" t="s">
-        <v>70</v>
+        <v>509</v>
+      </c>
+      <c r="H1" s="163"/>
+      <c r="I1" s="204" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>591</v>
+        <v>510</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="C2" s="166" t="s">
-        <v>593</v>
+        <v>511</v>
+      </c>
+      <c r="C2" s="162" t="s">
+        <v>512</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>594</v>
+        <v>513</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>595</v>
+        <v>514</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>596</v>
+        <v>515</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="H2" s="167"/>
-      <c r="I2" s="201" t="s">
-        <v>763</v>
+        <v>516</v>
+      </c>
+      <c r="H2" s="163"/>
+      <c r="I2" s="196" t="s">
+        <v>682</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>598</v>
+        <v>517</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>599</v>
+        <v>518</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>600</v>
+        <v>519</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>601</v>
+        <v>520</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>602</v>
+        <v>521</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>603</v>
+        <v>522</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="H3" s="167"/>
-      <c r="I3" s="201" t="s">
-        <v>764</v>
+        <v>523</v>
+      </c>
+      <c r="H3" s="163"/>
+      <c r="I3" s="196" t="s">
+        <v>683</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>605</v>
+        <v>524</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>606</v>
+        <v>525</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>607</v>
+        <v>526</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>608</v>
+        <v>527</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>609</v>
+        <v>528</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="G4" s="166" t="s">
-        <v>611</v>
-      </c>
-      <c r="H4" s="167"/>
-      <c r="I4" s="167"/>
+        <v>529</v>
+      </c>
+      <c r="G4" s="162" t="s">
+        <v>530</v>
+      </c>
+      <c r="H4" s="163"/>
+      <c r="I4" s="163"/>
     </row>
     <row r="5" spans="1:9" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>612</v>
+        <v>531</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>613</v>
+        <v>532</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>614</v>
+        <v>533</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>615</v>
-      </c>
-      <c r="E5" s="166" t="s">
-        <v>616</v>
+        <v>534</v>
+      </c>
+      <c r="E5" s="162" t="s">
+        <v>535</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="G5" s="167" t="s">
-        <v>618</v>
-      </c>
-      <c r="H5" s="167"/>
-      <c r="I5" s="167"/>
+        <v>536</v>
+      </c>
+      <c r="G5" s="163" t="s">
+        <v>537</v>
+      </c>
+      <c r="H5" s="163"/>
+      <c r="I5" s="163"/>
     </row>
     <row r="6" spans="1:9" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>619</v>
+        <v>538</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>620</v>
+        <v>539</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="D6" s="169" t="s">
-        <v>622</v>
-      </c>
-      <c r="E6" s="169" t="s">
-        <v>623</v>
-      </c>
-      <c r="F6" s="169" t="s">
-        <v>624</v>
-      </c>
-      <c r="G6" s="169" t="s">
-        <v>625</v>
-      </c>
-      <c r="H6" s="167"/>
-      <c r="I6" s="167"/>
+        <v>540</v>
+      </c>
+      <c r="D6" s="164" t="s">
+        <v>541</v>
+      </c>
+      <c r="E6" s="164" t="s">
+        <v>542</v>
+      </c>
+      <c r="F6" s="164" t="s">
+        <v>543</v>
+      </c>
+      <c r="G6" s="164" t="s">
+        <v>544</v>
+      </c>
+      <c r="H6" s="163"/>
+      <c r="I6" s="163"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="170" t="s">
-        <v>438</v>
-      </c>
-      <c r="B9" s="184" t="s">
-        <v>688</v>
-      </c>
-      <c r="C9" s="184" t="s">
-        <v>687</v>
-      </c>
-      <c r="D9" s="184" t="s">
-        <v>686</v>
-      </c>
-      <c r="E9" s="186" t="s">
-        <v>685</v>
-      </c>
-      <c r="F9" s="185" t="s">
-        <v>684</v>
-      </c>
-      <c r="G9" s="184" t="s">
-        <v>683</v>
-      </c>
-      <c r="H9" s="183" t="s">
-        <v>682</v>
+      <c r="A9" s="165" t="s">
+        <v>359</v>
+      </c>
+      <c r="B9" s="179" t="s">
+        <v>607</v>
+      </c>
+      <c r="C9" s="179" t="s">
+        <v>606</v>
+      </c>
+      <c r="D9" s="179" t="s">
+        <v>605</v>
+      </c>
+      <c r="E9" s="181" t="s">
+        <v>604</v>
+      </c>
+      <c r="F9" s="180" t="s">
+        <v>603</v>
+      </c>
+      <c r="G9" s="179" t="s">
+        <v>602</v>
+      </c>
+      <c r="H9" s="178" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="258" t="s">
+      <c r="A10" s="252" t="s">
+        <v>600</v>
+      </c>
+      <c r="B10" s="253"/>
+      <c r="C10" s="253"/>
+      <c r="D10" s="253"/>
+      <c r="E10" s="253"/>
+      <c r="F10" s="253"/>
+      <c r="G10" s="253"/>
+      <c r="H10" s="254"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="177" t="s">
+        <v>599</v>
+      </c>
+      <c r="B11" s="53" t="s">
+        <v>598</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>597</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>570</v>
+      </c>
+      <c r="E11" s="173" t="s">
+        <v>596</v>
+      </c>
+      <c r="F11" s="173" t="s">
+        <v>595</v>
+      </c>
+      <c r="G11" s="53"/>
+      <c r="H11" s="176"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="177"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="173"/>
+      <c r="F12" s="173"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="176"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="177"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="173"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="176"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="177"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="173"/>
+      <c r="F14" s="173"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="176"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="177"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="173"/>
+      <c r="F15" s="173"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="176"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="177"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="173"/>
+      <c r="F16" s="173"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="176"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="177"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="173"/>
+      <c r="F17" s="173"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="176"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="177"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="173"/>
+      <c r="F18" s="173"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="176"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="252" t="s">
+        <v>594</v>
+      </c>
+      <c r="B19" s="253"/>
+      <c r="C19" s="253"/>
+      <c r="D19" s="253"/>
+      <c r="E19" s="253"/>
+      <c r="F19" s="253"/>
+      <c r="G19" s="253"/>
+      <c r="H19" s="254"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="175" t="s">
+        <v>593</v>
+      </c>
+      <c r="B20" s="41" t="s">
+        <v>592</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>591</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>583</v>
+      </c>
+      <c r="E20" s="173" t="s">
+        <v>590</v>
+      </c>
+      <c r="F20" s="172">
+        <v>25898039</v>
+      </c>
+      <c r="G20" s="255" t="s">
+        <v>589</v>
+      </c>
+      <c r="H20" s="171" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="174" t="s">
+        <v>588</v>
+      </c>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41" t="s">
+        <v>587</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>570</v>
+      </c>
+      <c r="E21" s="173"/>
+      <c r="F21" s="172"/>
+      <c r="G21" s="255"/>
+      <c r="H21" s="171" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="174" t="s">
+        <v>586</v>
+      </c>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41" t="s">
+        <v>583</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>583</v>
+      </c>
+      <c r="E22" s="173"/>
+      <c r="F22" s="172"/>
+      <c r="G22" s="41" t="s">
+        <v>585</v>
+      </c>
+      <c r="H22" s="171" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="174" t="s">
+        <v>584</v>
+      </c>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41" t="s">
+        <v>583</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>583</v>
+      </c>
+      <c r="E23" s="173" t="s">
+        <v>582</v>
+      </c>
+      <c r="F23" s="172" t="s">
+        <v>581</v>
+      </c>
+      <c r="G23" s="41" t="s">
+        <v>580</v>
+      </c>
+      <c r="H23" s="171" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="174"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="173"/>
+      <c r="F24" s="172"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="171"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="174"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="173"/>
+      <c r="F25" s="172"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="171"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="174"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="173"/>
+      <c r="F26" s="172"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="171"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="174" t="s">
+        <v>578</v>
+      </c>
+      <c r="B27" s="41" t="s">
+        <v>577</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>576</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>570</v>
+      </c>
+      <c r="E27" s="173" t="s">
+        <v>575</v>
+      </c>
+      <c r="F27" s="172" t="s">
+        <v>574</v>
+      </c>
+      <c r="G27" s="41"/>
+      <c r="H27" s="171"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="175" t="s">
+        <v>573</v>
+      </c>
+      <c r="B28" s="41" t="s">
+        <v>572</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>571</v>
+      </c>
+      <c r="D28" s="41" t="s">
+        <v>570</v>
+      </c>
+      <c r="E28" s="173" t="s">
+        <v>569</v>
+      </c>
+      <c r="F28" s="173" t="s">
+        <v>568</v>
+      </c>
+      <c r="G28" s="41"/>
+      <c r="H28" s="171"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="174"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="173"/>
+      <c r="F29" s="172"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="171"/>
+    </row>
+    <row r="32" spans="1:8" ht="58.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="98" t="s">
+        <v>622</v>
+      </c>
+      <c r="B32" s="98" t="s">
+        <v>621</v>
+      </c>
+      <c r="C32" s="98" t="s">
+        <v>620</v>
+      </c>
+      <c r="D32" s="98" t="s">
+        <v>619</v>
+      </c>
+      <c r="E32" s="98" t="s">
+        <v>618</v>
+      </c>
+      <c r="F32" s="101" t="s">
+        <v>613</v>
+      </c>
+      <c r="G32" s="101" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="98" t="s">
+        <v>617</v>
+      </c>
+      <c r="B33" s="182" t="s">
+        <v>616</v>
+      </c>
+      <c r="C33" s="98" t="s">
+        <v>615</v>
+      </c>
+      <c r="D33" s="98" t="s">
+        <v>611</v>
+      </c>
+      <c r="E33" s="98" t="s">
+        <v>614</v>
+      </c>
+      <c r="F33" s="98" t="s">
+        <v>610</v>
+      </c>
+      <c r="G33" s="98" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="98" t="s">
+        <v>612</v>
+      </c>
+      <c r="B34" s="98" t="s">
+        <v>611</v>
+      </c>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="98"/>
+    </row>
+    <row r="36" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="F36" s="183" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="187" t="s">
+        <v>359</v>
+      </c>
+      <c r="B38" s="187" t="s">
+        <v>647</v>
+      </c>
+      <c r="C38" s="187" t="s">
+        <v>646</v>
+      </c>
+      <c r="D38" s="187" t="s">
+        <v>645</v>
+      </c>
+      <c r="E38" s="187" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="186" t="s">
+        <v>643</v>
+      </c>
+      <c r="B39" s="184" t="s">
+        <v>642</v>
+      </c>
+      <c r="C39" s="186" t="s">
+        <v>641</v>
+      </c>
+      <c r="D39" s="184">
+        <v>1153332210</v>
+      </c>
+      <c r="E39" s="184"/>
+      <c r="G39" s="118" t="s">
+        <v>112</v>
+      </c>
+      <c r="H39" s="118" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="186" t="s">
+        <v>640</v>
+      </c>
+      <c r="B40" s="184" t="s">
+        <v>639</v>
+      </c>
+      <c r="C40" s="184"/>
+      <c r="D40" s="184"/>
+      <c r="E40" s="184"/>
+      <c r="G40" s="118" t="s">
+        <v>114</v>
+      </c>
+      <c r="H40" s="118" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="186" t="s">
+        <v>638</v>
+      </c>
+      <c r="B41" s="184"/>
+      <c r="C41" s="184"/>
+      <c r="D41" s="184"/>
+      <c r="E41" s="184"/>
+      <c r="G41" s="118" t="s">
+        <v>116</v>
+      </c>
+      <c r="H41" s="118" t="s">
         <v>681</v>
       </c>
-      <c r="B10" s="259"/>
-      <c r="C10" s="259"/>
-      <c r="D10" s="259"/>
-      <c r="E10" s="259"/>
-      <c r="F10" s="259"/>
-      <c r="G10" s="259"/>
-      <c r="H10" s="260"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="182" t="s">
-        <v>680</v>
-      </c>
-      <c r="B11" s="55" t="s">
-        <v>679</v>
-      </c>
-      <c r="C11" s="55" t="s">
+    </row>
+    <row r="42" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="186" t="s">
+        <v>637</v>
+      </c>
+      <c r="B42" s="184" t="s">
+        <v>636</v>
+      </c>
+      <c r="C42" s="184"/>
+      <c r="D42" s="184"/>
+      <c r="E42" s="184"/>
+      <c r="G42" s="118" t="s">
+        <v>117</v>
+      </c>
+      <c r="H42" s="197"/>
+    </row>
+    <row r="43" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="186" t="s">
+        <v>635</v>
+      </c>
+      <c r="B43" s="184"/>
+      <c r="C43" s="184"/>
+      <c r="D43" s="184"/>
+      <c r="E43" s="184" t="s">
+        <v>630</v>
+      </c>
+      <c r="G43" s="197"/>
+      <c r="H43" s="197"/>
+    </row>
+    <row r="44" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="186" t="s">
+        <v>634</v>
+      </c>
+      <c r="B44" s="184"/>
+      <c r="C44" s="184"/>
+      <c r="D44" s="184"/>
+      <c r="E44" s="184" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="186" t="s">
+        <v>633</v>
+      </c>
+      <c r="B45" s="184"/>
+      <c r="C45" s="184"/>
+      <c r="D45" s="184"/>
+      <c r="E45" s="184" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="186" t="s">
+        <v>632</v>
+      </c>
+      <c r="B46" s="184"/>
+      <c r="C46" s="184"/>
+      <c r="D46" s="184"/>
+      <c r="E46" s="184" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="186" t="s">
+        <v>631</v>
+      </c>
+      <c r="B47" s="184"/>
+      <c r="C47" s="184"/>
+      <c r="D47" s="184"/>
+      <c r="E47" s="184" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="184"/>
+      <c r="B48" s="184"/>
+      <c r="C48" s="184"/>
+      <c r="D48" s="184"/>
+      <c r="E48" s="184"/>
+    </row>
+    <row r="49" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="184"/>
+      <c r="B49" s="184"/>
+      <c r="C49" s="184"/>
+      <c r="D49" s="184"/>
+      <c r="E49" s="184"/>
+    </row>
+    <row r="50" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="184"/>
+      <c r="B50" s="184"/>
+      <c r="C50" s="184"/>
+      <c r="D50" s="184"/>
+      <c r="E50" s="184"/>
+    </row>
+    <row r="51" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="184"/>
+      <c r="B51" s="184"/>
+      <c r="C51" s="184"/>
+      <c r="D51" s="184"/>
+      <c r="E51" s="184"/>
+    </row>
+    <row r="52" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="186" t="s">
+        <v>629</v>
+      </c>
+      <c r="B52" s="184"/>
+      <c r="C52" s="184"/>
+      <c r="D52" s="184"/>
+      <c r="E52" s="184" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="184"/>
+      <c r="B53" s="184"/>
+      <c r="C53" s="184"/>
+      <c r="D53" s="184"/>
+      <c r="E53" s="184"/>
+    </row>
+    <row r="54" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="185" t="s">
+        <v>627</v>
+      </c>
+      <c r="B54" s="184"/>
+      <c r="C54" s="184"/>
+      <c r="D54" s="184"/>
+      <c r="E54" s="184"/>
+    </row>
+    <row r="55" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="184" t="s">
+        <v>626</v>
+      </c>
+      <c r="B55" s="184"/>
+      <c r="C55" s="184"/>
+      <c r="D55" s="184"/>
+      <c r="E55" s="184"/>
+    </row>
+    <row r="56" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="184" t="s">
+        <v>625</v>
+      </c>
+      <c r="B56" s="184"/>
+      <c r="C56" s="184"/>
+      <c r="D56" s="184"/>
+      <c r="E56" s="184"/>
+    </row>
+    <row r="57" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="184" t="s">
+        <v>624</v>
+      </c>
+      <c r="B57" s="184"/>
+      <c r="C57" s="184"/>
+      <c r="D57" s="184"/>
+      <c r="E57" s="184"/>
+    </row>
+    <row r="60" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A60" s="98" t="s">
+        <v>665</v>
+      </c>
+      <c r="B60" s="188" t="s">
+        <v>664</v>
+      </c>
+      <c r="C60" s="98" t="s">
+        <v>663</v>
+      </c>
+      <c r="D60" s="188"/>
+      <c r="E60" s="188"/>
+      <c r="F60" s="188"/>
+      <c r="G60" s="191" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="98" t="s">
+        <v>662</v>
+      </c>
+      <c r="B61" s="98" t="s">
+        <v>661</v>
+      </c>
+      <c r="C61" s="188"/>
+      <c r="D61" s="188"/>
+      <c r="E61" s="188"/>
+      <c r="F61" s="188"/>
+      <c r="G61" s="188"/>
+    </row>
+    <row r="62" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A62" s="188"/>
+      <c r="B62" s="188"/>
+      <c r="C62" s="188"/>
+      <c r="D62" s="188"/>
+      <c r="E62" s="188"/>
+      <c r="F62" s="188"/>
+      <c r="G62" s="190" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="188"/>
+      <c r="B63" s="188"/>
+      <c r="C63" s="188"/>
+      <c r="D63" s="188"/>
+      <c r="E63" s="188"/>
+      <c r="F63" s="188"/>
+      <c r="G63" s="188"/>
+    </row>
+    <row r="64" spans="1:7" ht="58.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="189" t="s">
+        <v>659</v>
+      </c>
+      <c r="B64" s="188" t="s">
+        <v>658</v>
+      </c>
+      <c r="C64" s="98" t="s">
+        <v>657</v>
+      </c>
+      <c r="D64" s="98" t="s">
+        <v>656</v>
+      </c>
+      <c r="E64" s="98" t="s">
+        <v>655</v>
+      </c>
+      <c r="F64" s="188"/>
+      <c r="G64" s="188"/>
+    </row>
+    <row r="65" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="98" t="s">
+        <v>654</v>
+      </c>
+      <c r="B65" s="188"/>
+      <c r="C65" s="188"/>
+      <c r="D65" s="188"/>
+      <c r="E65" s="188"/>
+      <c r="F65" s="188"/>
+      <c r="G65" s="188"/>
+    </row>
+    <row r="66" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="188"/>
+      <c r="B66" s="188"/>
+      <c r="C66" s="188"/>
+      <c r="D66" s="188"/>
+      <c r="E66" s="188"/>
+      <c r="F66" s="188"/>
+      <c r="G66" s="188"/>
+    </row>
+    <row r="67" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="188"/>
+      <c r="B67" s="188"/>
+      <c r="C67" s="188"/>
+      <c r="D67" s="188"/>
+      <c r="E67" s="188"/>
+      <c r="F67" s="188"/>
+      <c r="G67" s="188"/>
+    </row>
+    <row r="68" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="189" t="s">
+        <v>653</v>
+      </c>
+      <c r="B68" s="188" t="s">
+        <v>652</v>
+      </c>
+      <c r="C68" s="188" t="s">
+        <v>651</v>
+      </c>
+      <c r="D68" s="188" t="s">
+        <v>650</v>
+      </c>
+      <c r="E68" s="188" t="s">
+        <v>649</v>
+      </c>
+      <c r="F68" s="188"/>
+      <c r="G68" s="188"/>
+    </row>
+    <row r="69" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="188" t="s">
+        <v>648</v>
+      </c>
+      <c r="B69" s="188"/>
+      <c r="C69" s="188"/>
+      <c r="D69" s="188"/>
+      <c r="E69" s="188"/>
+      <c r="F69" s="188"/>
+      <c r="G69" s="188"/>
+    </row>
+    <row r="73" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A73" s="193" t="s">
         <v>678</v>
       </c>
-      <c r="D11" s="55" t="s">
-        <v>651</v>
-      </c>
-      <c r="E11" s="178" t="s">
+      <c r="B73" s="194" t="s">
         <v>677</v>
       </c>
-      <c r="F11" s="178" t="s">
+      <c r="C73" s="194" t="s">
         <v>676</v>
       </c>
-      <c r="G11" s="55"/>
-      <c r="H11" s="181"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="182"/>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="178"/>
-      <c r="F12" s="178"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="181"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="182"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="178"/>
-      <c r="F13" s="178"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="181"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="182"/>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="178"/>
-      <c r="F14" s="178"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="181"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="182"/>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="178"/>
-      <c r="F15" s="178"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="181"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="182"/>
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="178"/>
-      <c r="F16" s="178"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="181"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="182"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="178"/>
-      <c r="F17" s="178"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="181"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="182"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="178"/>
-      <c r="F18" s="178"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="181"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="258" t="s">
+      <c r="D73" s="193" t="s">
         <v>675</v>
       </c>
-      <c r="B19" s="259"/>
-      <c r="C19" s="259"/>
-      <c r="D19" s="259"/>
-      <c r="E19" s="259"/>
-      <c r="F19" s="259"/>
-      <c r="G19" s="259"/>
-      <c r="H19" s="260"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="180" t="s">
+      <c r="E73" s="194" t="s">
         <v>674</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="F73" s="194" t="s">
         <v>673</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="G73" s="192"/>
+    </row>
+    <row r="74" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A74" s="193" t="s">
         <v>672</v>
       </c>
-      <c r="D20" s="43" t="s">
-        <v>664</v>
-      </c>
-      <c r="E20" s="178" t="s">
+      <c r="B74" s="193" t="s">
         <v>671</v>
       </c>
-      <c r="F20" s="177">
-        <v>25898039</v>
-      </c>
-      <c r="G20" s="261" t="s">
+      <c r="C74" s="194" t="s">
         <v>670</v>
       </c>
-      <c r="H20" s="176" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="179" t="s">
+      <c r="D74" s="193" t="s">
         <v>669</v>
       </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43" t="s">
+      <c r="E74" s="193" t="s">
         <v>668</v>
       </c>
-      <c r="D21" s="43" t="s">
-        <v>651</v>
-      </c>
-      <c r="E21" s="178"/>
-      <c r="F21" s="177"/>
-      <c r="G21" s="261"/>
-      <c r="H21" s="176" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="179" t="s">
+      <c r="F74" s="193" t="s">
         <v>667</v>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43" t="s">
-        <v>664</v>
-      </c>
-      <c r="D22" s="43" t="s">
-        <v>664</v>
-      </c>
-      <c r="E22" s="178"/>
-      <c r="F22" s="177"/>
-      <c r="G22" s="43" t="s">
+      <c r="G74" s="192"/>
+    </row>
+    <row r="75" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A75" s="193" t="s">
         <v>666</v>
       </c>
-      <c r="H22" s="176" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="179" t="s">
-        <v>665</v>
-      </c>
-      <c r="B23" s="43"/>
-      <c r="C23" s="43" t="s">
-        <v>664</v>
-      </c>
-      <c r="D23" s="43" t="s">
-        <v>664</v>
-      </c>
-      <c r="E23" s="178" t="s">
-        <v>663</v>
-      </c>
-      <c r="F23" s="177" t="s">
-        <v>662</v>
-      </c>
-      <c r="G23" s="43" t="s">
-        <v>661</v>
-      </c>
-      <c r="H23" s="176" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="179"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="178"/>
-      <c r="F24" s="177"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="176"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="179"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="178"/>
-      <c r="F25" s="177"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="176"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="179"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="178"/>
-      <c r="F26" s="177"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="176"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="179" t="s">
-        <v>659</v>
-      </c>
-      <c r="B27" s="43" t="s">
-        <v>658</v>
-      </c>
-      <c r="C27" s="43" t="s">
-        <v>657</v>
-      </c>
-      <c r="D27" s="43" t="s">
-        <v>651</v>
-      </c>
-      <c r="E27" s="178" t="s">
-        <v>656</v>
-      </c>
-      <c r="F27" s="177" t="s">
-        <v>655</v>
-      </c>
-      <c r="G27" s="43"/>
-      <c r="H27" s="176"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="180" t="s">
-        <v>654</v>
-      </c>
-      <c r="B28" s="43" t="s">
-        <v>653</v>
-      </c>
-      <c r="C28" s="43" t="s">
-        <v>652</v>
-      </c>
-      <c r="D28" s="43" t="s">
-        <v>651</v>
-      </c>
-      <c r="E28" s="178" t="s">
-        <v>650</v>
-      </c>
-      <c r="F28" s="178" t="s">
-        <v>649</v>
-      </c>
-      <c r="G28" s="43"/>
-      <c r="H28" s="176"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="179"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="178"/>
-      <c r="F29" s="177"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="176"/>
-    </row>
-    <row r="32" spans="1:8" ht="58.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="100" t="s">
-        <v>703</v>
-      </c>
-      <c r="B32" s="100" t="s">
-        <v>702</v>
-      </c>
-      <c r="C32" s="100" t="s">
-        <v>701</v>
-      </c>
-      <c r="D32" s="100" t="s">
-        <v>700</v>
-      </c>
-      <c r="E32" s="100" t="s">
-        <v>699</v>
-      </c>
-      <c r="F32" s="103" t="s">
-        <v>694</v>
-      </c>
-      <c r="G32" s="103" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="100" t="s">
-        <v>698</v>
-      </c>
-      <c r="B33" s="187" t="s">
-        <v>697</v>
-      </c>
-      <c r="C33" s="100" t="s">
-        <v>696</v>
-      </c>
-      <c r="D33" s="100" t="s">
-        <v>692</v>
-      </c>
-      <c r="E33" s="100" t="s">
-        <v>695</v>
-      </c>
-      <c r="F33" s="100" t="s">
-        <v>691</v>
-      </c>
-      <c r="G33" s="100" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="100" t="s">
-        <v>693</v>
-      </c>
-      <c r="B34" s="100" t="s">
-        <v>692</v>
-      </c>
-      <c r="C34" s="100"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="100"/>
-      <c r="G34" s="100"/>
-    </row>
-    <row r="36" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="F36" s="188" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="192" t="s">
-        <v>438</v>
-      </c>
-      <c r="B38" s="192" t="s">
-        <v>728</v>
-      </c>
-      <c r="C38" s="192" t="s">
-        <v>727</v>
-      </c>
-      <c r="D38" s="192" t="s">
-        <v>726</v>
-      </c>
-      <c r="E38" s="192" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="191" t="s">
-        <v>724</v>
-      </c>
-      <c r="B39" s="189" t="s">
-        <v>723</v>
-      </c>
-      <c r="C39" s="191" t="s">
-        <v>722</v>
-      </c>
-      <c r="D39" s="189">
-        <v>1153332210</v>
-      </c>
-      <c r="E39" s="189"/>
-      <c r="G39" s="120" t="s">
-        <v>135</v>
-      </c>
-      <c r="H39" s="120" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="191" t="s">
-        <v>721</v>
-      </c>
-      <c r="B40" s="189" t="s">
-        <v>720</v>
-      </c>
-      <c r="C40" s="189"/>
-      <c r="D40" s="189"/>
-      <c r="E40" s="189"/>
-      <c r="G40" s="120" t="s">
-        <v>137</v>
-      </c>
-      <c r="H40" s="120" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="191" t="s">
-        <v>719</v>
-      </c>
-      <c r="B41" s="189"/>
-      <c r="C41" s="189"/>
-      <c r="D41" s="189"/>
-      <c r="E41" s="189"/>
-      <c r="G41" s="120" t="s">
-        <v>139</v>
-      </c>
-      <c r="H41" s="120" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="191" t="s">
-        <v>718</v>
-      </c>
-      <c r="B42" s="189" t="s">
-        <v>717</v>
-      </c>
-      <c r="C42" s="189"/>
-      <c r="D42" s="189"/>
-      <c r="E42" s="189"/>
-      <c r="G42" s="120" t="s">
-        <v>140</v>
-      </c>
-      <c r="H42" s="202"/>
-    </row>
-    <row r="43" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="191" t="s">
-        <v>716</v>
-      </c>
-      <c r="B43" s="189"/>
-      <c r="C43" s="189"/>
-      <c r="D43" s="189"/>
-      <c r="E43" s="189" t="s">
-        <v>711</v>
-      </c>
-      <c r="G43" s="202"/>
-      <c r="H43" s="202"/>
-    </row>
-    <row r="44" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="191" t="s">
-        <v>715</v>
-      </c>
-      <c r="B44" s="189"/>
-      <c r="C44" s="189"/>
-      <c r="D44" s="189"/>
-      <c r="E44" s="189" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="191" t="s">
-        <v>714</v>
-      </c>
-      <c r="B45" s="189"/>
-      <c r="C45" s="189"/>
-      <c r="D45" s="189"/>
-      <c r="E45" s="189" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="191" t="s">
-        <v>713</v>
-      </c>
-      <c r="B46" s="189"/>
-      <c r="C46" s="189"/>
-      <c r="D46" s="189"/>
-      <c r="E46" s="189" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="191" t="s">
-        <v>712</v>
-      </c>
-      <c r="B47" s="189"/>
-      <c r="C47" s="189"/>
-      <c r="D47" s="189"/>
-      <c r="E47" s="189" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="189"/>
-      <c r="B48" s="189"/>
-      <c r="C48" s="189"/>
-      <c r="D48" s="189"/>
-      <c r="E48" s="189"/>
-    </row>
-    <row r="49" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="189"/>
-      <c r="B49" s="189"/>
-      <c r="C49" s="189"/>
-      <c r="D49" s="189"/>
-      <c r="E49" s="189"/>
-    </row>
-    <row r="50" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="189"/>
-      <c r="B50" s="189"/>
-      <c r="C50" s="189"/>
-      <c r="D50" s="189"/>
-      <c r="E50" s="189"/>
-    </row>
-    <row r="51" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="189"/>
-      <c r="B51" s="189"/>
-      <c r="C51" s="189"/>
-      <c r="D51" s="189"/>
-      <c r="E51" s="189"/>
-    </row>
-    <row r="52" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="191" t="s">
-        <v>710</v>
-      </c>
-      <c r="B52" s="189"/>
-      <c r="C52" s="189"/>
-      <c r="D52" s="189"/>
-      <c r="E52" s="189" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="189"/>
-      <c r="B53" s="189"/>
-      <c r="C53" s="189"/>
-      <c r="D53" s="189"/>
-      <c r="E53" s="189"/>
-    </row>
-    <row r="54" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="190" t="s">
-        <v>708</v>
-      </c>
-      <c r="B54" s="189"/>
-      <c r="C54" s="189"/>
-      <c r="D54" s="189"/>
-      <c r="E54" s="189"/>
-    </row>
-    <row r="55" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="189" t="s">
-        <v>707</v>
-      </c>
-      <c r="B55" s="189"/>
-      <c r="C55" s="189"/>
-      <c r="D55" s="189"/>
-      <c r="E55" s="189"/>
-    </row>
-    <row r="56" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="189" t="s">
-        <v>706</v>
-      </c>
-      <c r="B56" s="189"/>
-      <c r="C56" s="189"/>
-      <c r="D56" s="189"/>
-      <c r="E56" s="189"/>
-    </row>
-    <row r="57" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="189" t="s">
-        <v>705</v>
-      </c>
-      <c r="B57" s="189"/>
-      <c r="C57" s="189"/>
-      <c r="D57" s="189"/>
-      <c r="E57" s="189"/>
-    </row>
-    <row r="60" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A60" s="100" t="s">
-        <v>746</v>
-      </c>
-      <c r="B60" s="193" t="s">
-        <v>745</v>
-      </c>
-      <c r="C60" s="100" t="s">
-        <v>744</v>
-      </c>
-      <c r="D60" s="193"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
-      <c r="G60" s="196" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="100" t="s">
-        <v>743</v>
-      </c>
-      <c r="B61" s="100" t="s">
-        <v>742</v>
-      </c>
-      <c r="C61" s="193"/>
-      <c r="D61" s="193"/>
-      <c r="E61" s="193"/>
-      <c r="F61" s="193"/>
-      <c r="G61" s="193"/>
-    </row>
-    <row r="62" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="193"/>
-      <c r="B62" s="193"/>
-      <c r="C62" s="193"/>
-      <c r="D62" s="193"/>
-      <c r="E62" s="193"/>
-      <c r="F62" s="193"/>
-      <c r="G62" s="195" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="193"/>
-      <c r="B63" s="193"/>
-      <c r="C63" s="193"/>
-      <c r="D63" s="193"/>
-      <c r="E63" s="193"/>
-      <c r="F63" s="193"/>
-      <c r="G63" s="193"/>
-    </row>
-    <row r="64" spans="1:7" ht="58.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="194" t="s">
-        <v>740</v>
-      </c>
-      <c r="B64" s="193" t="s">
-        <v>739</v>
-      </c>
-      <c r="C64" s="100" t="s">
-        <v>738</v>
-      </c>
-      <c r="D64" s="100" t="s">
-        <v>737</v>
-      </c>
-      <c r="E64" s="100" t="s">
-        <v>736</v>
-      </c>
-      <c r="F64" s="193"/>
-      <c r="G64" s="193"/>
-    </row>
-    <row r="65" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="100" t="s">
-        <v>735</v>
-      </c>
-      <c r="B65" s="193"/>
-      <c r="C65" s="193"/>
-      <c r="D65" s="193"/>
-      <c r="E65" s="193"/>
-      <c r="F65" s="193"/>
-      <c r="G65" s="193"/>
-    </row>
-    <row r="66" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="193"/>
-      <c r="B66" s="193"/>
-      <c r="C66" s="193"/>
-      <c r="D66" s="193"/>
-      <c r="E66" s="193"/>
-      <c r="F66" s="193"/>
-      <c r="G66" s="193"/>
-    </row>
-    <row r="67" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="193"/>
-      <c r="B67" s="193"/>
-      <c r="C67" s="193"/>
-      <c r="D67" s="193"/>
-      <c r="E67" s="193"/>
-      <c r="F67" s="193"/>
-      <c r="G67" s="193"/>
-    </row>
-    <row r="68" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="194" t="s">
-        <v>734</v>
-      </c>
-      <c r="B68" s="193" t="s">
-        <v>733</v>
-      </c>
-      <c r="C68" s="193" t="s">
-        <v>732</v>
-      </c>
-      <c r="D68" s="193" t="s">
-        <v>731</v>
-      </c>
-      <c r="E68" s="193" t="s">
-        <v>730</v>
-      </c>
-      <c r="F68" s="193"/>
-      <c r="G68" s="193"/>
-    </row>
-    <row r="69" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="193" t="s">
-        <v>729</v>
-      </c>
-      <c r="B69" s="193"/>
-      <c r="C69" s="193"/>
-      <c r="D69" s="193"/>
-      <c r="E69" s="193"/>
-      <c r="F69" s="193"/>
-      <c r="G69" s="193"/>
-    </row>
-    <row r="73" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A73" s="198" t="s">
-        <v>759</v>
-      </c>
-      <c r="B73" s="199" t="s">
-        <v>758</v>
-      </c>
-      <c r="C73" s="199" t="s">
-        <v>757</v>
-      </c>
-      <c r="D73" s="198" t="s">
-        <v>756</v>
-      </c>
-      <c r="E73" s="199" t="s">
-        <v>755</v>
-      </c>
-      <c r="F73" s="199" t="s">
-        <v>754</v>
-      </c>
-      <c r="G73" s="197"/>
-    </row>
-    <row r="74" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A74" s="198" t="s">
-        <v>753</v>
-      </c>
-      <c r="B74" s="198" t="s">
-        <v>752</v>
-      </c>
-      <c r="C74" s="199" t="s">
-        <v>751</v>
-      </c>
-      <c r="D74" s="198" t="s">
-        <v>750</v>
-      </c>
-      <c r="E74" s="198" t="s">
-        <v>749</v>
-      </c>
-      <c r="F74" s="198" t="s">
-        <v>748</v>
-      </c>
-      <c r="G74" s="197"/>
-    </row>
-    <row r="75" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A75" s="198" t="s">
-        <v>747</v>
-      </c>
-      <c r="B75" s="197"/>
-      <c r="C75" s="197"/>
-      <c r="D75" s="197"/>
-      <c r="E75" s="197"/>
-      <c r="F75" s="197"/>
-      <c r="G75" s="197"/>
+      <c r="B75" s="192"/>
+      <c r="C75" s="192"/>
+      <c r="D75" s="192"/>
+      <c r="E75" s="192"/>
+      <c r="F75" s="192"/>
+      <c r="G75" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8294,86 +7179,86 @@
     <hyperlink ref="B4" r:id="rId28" display="https://www.facebook.com/Jobeexjobs" xr:uid="{1C80701E-8D1F-415D-98EB-ADEE7EE9DB73}"/>
     <hyperlink ref="F3" r:id="rId29" display="freeejobs" xr:uid="{AF6E842B-278C-4DD9-96BD-4A98FEDC10F5}"/>
     <hyperlink ref="A6" r:id="rId30" display="Salsabeel Elsanhory" xr:uid="{DCA96FF7-D15B-4E7B-91C5-7022F4F3D4BF}"/>
-    <hyperlink ref="I1" r:id="rId31" xr:uid="{7AA4A900-3FDC-4FE6-AF18-195FCA813159}"/>
-    <hyperlink ref="G3" r:id="rId32" display="careerjet" xr:uid="{E6B44DCE-81B2-45FC-8C7D-E6DB120BBE24}"/>
-    <hyperlink ref="C5" r:id="rId33" xr:uid="{822D81DE-F845-46C9-BCDA-54535AED662B}"/>
-    <hyperlink ref="D6" r:id="rId34" xr:uid="{CD5BE00A-662A-482E-9BB2-00F7653F5AEE}"/>
-    <hyperlink ref="C6" r:id="rId35" xr:uid="{16332ECD-6AC9-4E60-9AB9-C8CDED7CB114}"/>
-    <hyperlink ref="E6" r:id="rId36" xr:uid="{497B7B28-C4B6-4DC8-A0DD-9CD174F3EA2C}"/>
-    <hyperlink ref="A5" r:id="rId37" display="iCareerEgy" xr:uid="{86CC2BAE-A0EF-4862-A2C2-60751E6F2A24}"/>
-    <hyperlink ref="G2" r:id="rId38" display="https://www.goodfirms.co/" xr:uid="{F7393069-7D33-46BB-A062-8F9359424D47}"/>
+    <hyperlink ref="I1" location="'0'!A1" display="Back" xr:uid="{7AA4A900-3FDC-4FE6-AF18-195FCA813159}"/>
+    <hyperlink ref="G3" r:id="rId31" display="careerjet" xr:uid="{E6B44DCE-81B2-45FC-8C7D-E6DB120BBE24}"/>
+    <hyperlink ref="C5" r:id="rId32" xr:uid="{822D81DE-F845-46C9-BCDA-54535AED662B}"/>
+    <hyperlink ref="D6" r:id="rId33" xr:uid="{CD5BE00A-662A-482E-9BB2-00F7653F5AEE}"/>
+    <hyperlink ref="C6" r:id="rId34" xr:uid="{16332ECD-6AC9-4E60-9AB9-C8CDED7CB114}"/>
+    <hyperlink ref="E6" r:id="rId35" xr:uid="{497B7B28-C4B6-4DC8-A0DD-9CD174F3EA2C}"/>
+    <hyperlink ref="A5" r:id="rId36" display="iCareerEgy" xr:uid="{86CC2BAE-A0EF-4862-A2C2-60751E6F2A24}"/>
+    <hyperlink ref="G2" r:id="rId37" display="https://www.goodfirms.co/" xr:uid="{F7393069-7D33-46BB-A062-8F9359424D47}"/>
     <hyperlink ref="G6" location="Oth.Comp!A1" display="دليل شركات" xr:uid="{23170B6D-0052-45B2-97B4-AA1CB0CACFDB}"/>
-    <hyperlink ref="A33" r:id="rId39" display="https://egfwd.com/" xr:uid="{5B7FE5DC-C5AD-4094-8331-25AC95C2055F}"/>
-    <hyperlink ref="G33" r:id="rId40" display="https://www.facebook.com/AMIT.Learning" xr:uid="{59F5BBAD-16A4-4726-B749-0D5FF7D6DBB3}"/>
-    <hyperlink ref="B34" r:id="rId41" display="https://www.facebook.com/groups/402958410979164" xr:uid="{B268C425-417E-43D3-864D-EA712BAD71A7}"/>
-    <hyperlink ref="C33" r:id="rId42" display="https://millionrowad.com/" xr:uid="{F94ABC4C-6D4C-4667-9BBD-0C015C153110}"/>
-    <hyperlink ref="E33" r:id="rId43" display="https://eduhub21.com/" xr:uid="{97F5A4FD-093A-4C1A-89B9-66BA73056522}"/>
-    <hyperlink ref="D33" r:id="rId44" display="http://techleaders.eg/" xr:uid="{4E63B5C4-59E9-4869-BD19-1E8088830769}"/>
-    <hyperlink ref="A34" r:id="rId45" display="http://techleaders.eg/aal" xr:uid="{1C099C0C-BBEE-4C89-9BCA-17BB27D1EB04}"/>
-    <hyperlink ref="F33" r:id="rId46" display="https://assess.sovaonline.com/hub/?ar=eNoBsABP_84CZZsEw2cT_eL0lv9k67svWuYqmMx7QEXe4QtavJXfTRtkVX3sz1uXETWS-hYGbqvqhEmJxIP-5-RQ1_1O5HP7hLlCvmupEhLUZqR1lOkWAUHtu2pEZojcq4uTL71lnMKG6MshdwSs7nJ2DpnelCBRKBuOrGej7dKpCseMXOwZ-vQXfCwhnMOVwiIHxweiWV_sJA7XovenneiJnZceBTUUFoGrD6Az47UIIP2FU1KMUJZaTQ==" xr:uid="{0C1058FE-BAB9-4C41-BDF8-3BEE8BBF3141}"/>
-    <hyperlink ref="D32" r:id="rId47" display="https://www.egyincs.me/" xr:uid="{7B93414B-9E2F-43E4-9550-5FDAE1DC8B92}"/>
-    <hyperlink ref="A32" r:id="rId48" display="https://www.facebook.com/groups/cseknowledgeexchange" xr:uid="{2222AF30-0A43-4280-A8A6-2D79D96D134E}"/>
-    <hyperlink ref="C32" r:id="rId49" display="https://www.facebook.com/groups/463038787444078" xr:uid="{18024996-8770-4DF3-8677-81710D152970}"/>
-    <hyperlink ref="E32" r:id="rId50" display="https://www.facebook.com/internmenow2020" xr:uid="{00EA00CA-7B4C-4EE4-822A-3680BB4BFD16}"/>
-    <hyperlink ref="G32" r:id="rId51" xr:uid="{8D288077-281C-4C5C-82C0-2E3D58D3AC59}"/>
-    <hyperlink ref="F32" r:id="rId52" xr:uid="{C0D8C43E-0366-4773-9D6C-1CFEDF801A8A}"/>
-    <hyperlink ref="B32" r:id="rId53" display="https://www.facebook.com/groups/314004286793745" xr:uid="{96D96201-75A9-4749-AB55-969BB5F2ED0C}"/>
-    <hyperlink ref="B33" r:id="rId54" display="https://www.facebook.com/groups/FCISGraduateGroup" xr:uid="{5684784C-F2E4-475B-ACBD-5BBC1B99FDFF}"/>
-    <hyperlink ref="F36" r:id="rId55" display="https://www.egycompanies.com/" xr:uid="{324D4F45-7920-4D95-9FD9-5ECB0288C622}"/>
-    <hyperlink ref="A39" r:id="rId56" display="https://www.sts-egypt.com/" xr:uid="{C972BF91-C523-4965-96E8-2428D62F334F}"/>
-    <hyperlink ref="C39" r:id="rId57" display="mailto:info@sts-egypt.com" xr:uid="{34E9691A-2913-4026-BC3C-8AA7520CAB68}"/>
-    <hyperlink ref="A40" r:id="rId58" display="https://inovaeg.com/jobs" xr:uid="{78D3F8FA-22D8-4A75-82DD-903989586DD7}"/>
-    <hyperlink ref="A41" r:id="rId59" display="https://www.gizasystemscareers.com/en" xr:uid="{74361B15-AFC9-47EE-B3AC-F2FCCCA7FD5C}"/>
-    <hyperlink ref="A42" r:id="rId60" display="https://valeo.taleo.net/careersection/link/default.ftl?lang=en" xr:uid="{340EBC9A-321C-499B-8D1A-BE158A146414}"/>
-    <hyperlink ref="A43" r:id="rId61" display="https://dell.wd1.myworkdayjobs.com/en-US/External" xr:uid="{0A364A1F-5AF3-483E-B965-68D19F146312}"/>
-    <hyperlink ref="A44" r:id="rId62" display="https://jobs.dell.com/location/egypt-jobs/375/357994/2" xr:uid="{B5CBFBD0-1156-4C27-B514-4F3C14E65E5B}"/>
-    <hyperlink ref="A45" r:id="rId63" display="https://www.ibm.com/careers/us-en/search/?filters=primary_country:EG" xr:uid="{F413F53F-909D-4285-82C2-630DF0BF760A}"/>
-    <hyperlink ref="A46" r:id="rId64" location="/" display="https://e.huawei.com/en/talent/portal/ - /" xr:uid="{0392AD1C-D6C5-4107-9242-C1684B6E83A0}"/>
-    <hyperlink ref="A52" r:id="rId65" display="https://www.facebook.com/web.Developers.Jobs.Egypt" xr:uid="{C74B164C-0ED4-4573-B6E1-4C6DB757C371}"/>
-    <hyperlink ref="A56" r:id="rId66" display="https://itida.gov.eg/Arabic/Pages/default.aspx" xr:uid="{38CBB516-842A-4164-9C05-C6D535196E29}"/>
-    <hyperlink ref="A54" r:id="rId67" display="https://secc.org.eg/arabic/pages/default.aspx" xr:uid="{AE240F5D-438A-4A28-8E2B-CB424FE6643C}"/>
-    <hyperlink ref="A55" r:id="rId68" display="https://tiec.gov.eg/Arabic/Pages/default.aspx" xr:uid="{90974C4C-5B3B-47A0-BF91-C3E6A98CA2B6}"/>
-    <hyperlink ref="A57" r:id="rId69" display="https://www.facebook.com/Instabug" xr:uid="{A5775D45-923F-4B17-966D-81D1FB0B5303}"/>
-    <hyperlink ref="A47" r:id="rId70" xr:uid="{01679DDF-83AA-4319-BE5A-8E9862C78D74}"/>
-    <hyperlink ref="A60" r:id="rId71" display="https://www.javatpoint.com/interview-questions-and-answers" xr:uid="{2BA43989-E785-44F7-B86D-D586B2594E83}"/>
-    <hyperlink ref="B60" r:id="rId72" display="https://www.facebook.com/sou2el3amal" xr:uid="{48D706C8-3D79-437E-869B-8904F1A38EDF}"/>
+    <hyperlink ref="A33" r:id="rId38" display="https://egfwd.com/" xr:uid="{5B7FE5DC-C5AD-4094-8331-25AC95C2055F}"/>
+    <hyperlink ref="G33" r:id="rId39" display="https://www.facebook.com/AMIT.Learning" xr:uid="{59F5BBAD-16A4-4726-B749-0D5FF7D6DBB3}"/>
+    <hyperlink ref="B34" r:id="rId40" display="https://www.facebook.com/groups/402958410979164" xr:uid="{B268C425-417E-43D3-864D-EA712BAD71A7}"/>
+    <hyperlink ref="C33" r:id="rId41" display="https://millionrowad.com/" xr:uid="{F94ABC4C-6D4C-4667-9BBD-0C015C153110}"/>
+    <hyperlink ref="E33" r:id="rId42" display="https://eduhub21.com/" xr:uid="{97F5A4FD-093A-4C1A-89B9-66BA73056522}"/>
+    <hyperlink ref="D33" r:id="rId43" display="http://techleaders.eg/" xr:uid="{4E63B5C4-59E9-4869-BD19-1E8088830769}"/>
+    <hyperlink ref="A34" r:id="rId44" display="http://techleaders.eg/aal" xr:uid="{1C099C0C-BBEE-4C89-9BCA-17BB27D1EB04}"/>
+    <hyperlink ref="F33" r:id="rId45" display="https://assess.sovaonline.com/hub/?ar=eNoBsABP_84CZZsEw2cT_eL0lv9k67svWuYqmMx7QEXe4QtavJXfTRtkVX3sz1uXETWS-hYGbqvqhEmJxIP-5-RQ1_1O5HP7hLlCvmupEhLUZqR1lOkWAUHtu2pEZojcq4uTL71lnMKG6MshdwSs7nJ2DpnelCBRKBuOrGej7dKpCseMXOwZ-vQXfCwhnMOVwiIHxweiWV_sJA7XovenneiJnZceBTUUFoGrD6Az47UIIP2FU1KMUJZaTQ==" xr:uid="{0C1058FE-BAB9-4C41-BDF8-3BEE8BBF3141}"/>
+    <hyperlink ref="D32" r:id="rId46" display="https://www.egyincs.me/" xr:uid="{7B93414B-9E2F-43E4-9550-5FDAE1DC8B92}"/>
+    <hyperlink ref="A32" r:id="rId47" display="https://www.facebook.com/groups/cseknowledgeexchange" xr:uid="{2222AF30-0A43-4280-A8A6-2D79D96D134E}"/>
+    <hyperlink ref="C32" r:id="rId48" display="https://www.facebook.com/groups/463038787444078" xr:uid="{18024996-8770-4DF3-8677-81710D152970}"/>
+    <hyperlink ref="E32" r:id="rId49" display="https://www.facebook.com/internmenow2020" xr:uid="{00EA00CA-7B4C-4EE4-822A-3680BB4BFD16}"/>
+    <hyperlink ref="G32" r:id="rId50" xr:uid="{8D288077-281C-4C5C-82C0-2E3D58D3AC59}"/>
+    <hyperlink ref="F32" r:id="rId51" xr:uid="{C0D8C43E-0366-4773-9D6C-1CFEDF801A8A}"/>
+    <hyperlink ref="B32" r:id="rId52" display="https://www.facebook.com/groups/314004286793745" xr:uid="{96D96201-75A9-4749-AB55-969BB5F2ED0C}"/>
+    <hyperlink ref="B33" r:id="rId53" display="https://www.facebook.com/groups/FCISGraduateGroup" xr:uid="{5684784C-F2E4-475B-ACBD-5BBC1B99FDFF}"/>
+    <hyperlink ref="F36" r:id="rId54" display="https://www.egycompanies.com/" xr:uid="{324D4F45-7920-4D95-9FD9-5ECB0288C622}"/>
+    <hyperlink ref="A39" r:id="rId55" display="https://www.sts-egypt.com/" xr:uid="{C972BF91-C523-4965-96E8-2428D62F334F}"/>
+    <hyperlink ref="C39" r:id="rId56" display="mailto:info@sts-egypt.com" xr:uid="{34E9691A-2913-4026-BC3C-8AA7520CAB68}"/>
+    <hyperlink ref="A40" r:id="rId57" display="https://inovaeg.com/jobs" xr:uid="{78D3F8FA-22D8-4A75-82DD-903989586DD7}"/>
+    <hyperlink ref="A41" r:id="rId58" display="https://www.gizasystemscareers.com/en" xr:uid="{74361B15-AFC9-47EE-B3AC-F2FCCCA7FD5C}"/>
+    <hyperlink ref="A42" r:id="rId59" display="https://valeo.taleo.net/careersection/link/default.ftl?lang=en" xr:uid="{340EBC9A-321C-499B-8D1A-BE158A146414}"/>
+    <hyperlink ref="A43" r:id="rId60" display="https://dell.wd1.myworkdayjobs.com/en-US/External" xr:uid="{0A364A1F-5AF3-483E-B965-68D19F146312}"/>
+    <hyperlink ref="A44" r:id="rId61" display="https://jobs.dell.com/location/egypt-jobs/375/357994/2" xr:uid="{B5CBFBD0-1156-4C27-B514-4F3C14E65E5B}"/>
+    <hyperlink ref="A45" r:id="rId62" display="https://www.ibm.com/careers/us-en/search/?filters=primary_country:EG" xr:uid="{F413F53F-909D-4285-82C2-630DF0BF760A}"/>
+    <hyperlink ref="A46" r:id="rId63" location="/" display="https://e.huawei.com/en/talent/portal/ - /" xr:uid="{0392AD1C-D6C5-4107-9242-C1684B6E83A0}"/>
+    <hyperlink ref="A52" r:id="rId64" display="https://www.facebook.com/web.Developers.Jobs.Egypt" xr:uid="{C74B164C-0ED4-4573-B6E1-4C6DB757C371}"/>
+    <hyperlink ref="A56" r:id="rId65" display="https://itida.gov.eg/Arabic/Pages/default.aspx" xr:uid="{38CBB516-842A-4164-9C05-C6D535196E29}"/>
+    <hyperlink ref="A54" r:id="rId66" display="https://secc.org.eg/arabic/pages/default.aspx" xr:uid="{AE240F5D-438A-4A28-8E2B-CB424FE6643C}"/>
+    <hyperlink ref="A55" r:id="rId67" display="https://tiec.gov.eg/Arabic/Pages/default.aspx" xr:uid="{90974C4C-5B3B-47A0-BF91-C3E6A98CA2B6}"/>
+    <hyperlink ref="A57" r:id="rId68" display="https://www.facebook.com/Instabug" xr:uid="{A5775D45-923F-4B17-966D-81D1FB0B5303}"/>
+    <hyperlink ref="A47" r:id="rId69" xr:uid="{01679DDF-83AA-4319-BE5A-8E9862C78D74}"/>
+    <hyperlink ref="A60" r:id="rId70" display="https://www.javatpoint.com/interview-questions-and-answers" xr:uid="{2BA43989-E785-44F7-B86D-D586B2594E83}"/>
+    <hyperlink ref="B60" r:id="rId71" display="https://www.facebook.com/sou2el3amal" xr:uid="{48D706C8-3D79-437E-869B-8904F1A38EDF}"/>
     <hyperlink ref="G60" location="Jobs!A1" display="Back &lt;--" xr:uid="{910A0D80-B5DC-464F-92D8-BD35C571B6AD}"/>
-    <hyperlink ref="C60" r:id="rId73" display="https://www.thebalancecareers.com/sample-email-job-application-letter-2061608" xr:uid="{45CA1540-4F3F-491B-A863-458D827ED6D8}"/>
-    <hyperlink ref="B64" r:id="rId74" display="https://www.facebook.com/groups/402958410979164" xr:uid="{9E98DCFA-E6BA-4A05-AA25-452543EAAE39}"/>
-    <hyperlink ref="C64" r:id="rId75" display="https://www.facebook.com/groups/Dont.Work.Here" xr:uid="{2D0CC0E8-FA3A-48C9-8FCD-709201DDA6AC}"/>
-    <hyperlink ref="A65" r:id="rId76" display="https://www.facebook.com/groups/767725120055206" xr:uid="{71F71AFF-405C-4DC2-A0FF-A87D7917788C}"/>
-    <hyperlink ref="B61" r:id="rId77" xr:uid="{2E9C545B-F645-4A24-8E91-7BFE59466C1E}"/>
-    <hyperlink ref="D64" r:id="rId78" display="بلغ عن شركات النصب" xr:uid="{B74E46DD-F205-45CF-9F67-AA0E16883327}"/>
-    <hyperlink ref="E64" r:id="rId79" display="https://www.facebook.com/groups/253221952434585/" xr:uid="{79EB9432-7EFA-49DA-B9B5-2B6CB3FFEAF8}"/>
-    <hyperlink ref="A73" r:id="rId80" display="https://www.carrefouregypt.com/mafegy/ar" xr:uid="{5B55F5D2-E138-4E16-A6D3-EB5A57825CC8}"/>
-    <hyperlink ref="B73" r:id="rId81" display="https://www.jumia.com.eg/ar" xr:uid="{7D18826D-C5DE-402D-BE73-694958E65A77}"/>
-    <hyperlink ref="C73" r:id="rId82" display="https://www.raneen.com/ar" xr:uid="{A7D6AD86-B5AB-4B12-BFAA-D407089499FB}"/>
-    <hyperlink ref="D73" r:id="rId83" display="https://ar.aliexpress.com/" xr:uid="{7B29632D-E4A5-4990-993C-0F54BBE4657C}"/>
-    <hyperlink ref="E73" r:id="rId84" display="https://riz.shop/" xr:uid="{EC02BF4F-24E4-4F76-8A44-B73FC82B2C8E}"/>
-    <hyperlink ref="F73" r:id="rId85" display="https://ehabcenter.com/" xr:uid="{04985C63-238D-48C5-9959-57F080E55C63}"/>
-    <hyperlink ref="A74" r:id="rId86" display="https://noon.com/egypt-ar" xr:uid="{3BC21AE9-6120-471B-B649-DA95F10DB512}"/>
-    <hyperlink ref="B74" r:id="rId87" display="https://www.valu.com.eg/home" xr:uid="{0CB3E5D6-0D05-4CE2-8F09-1A90697DBF14}"/>
-    <hyperlink ref="C74" r:id="rId88" display="https://www.facebook.com/Al.morshedy" xr:uid="{95EEF36C-7511-461B-A94B-0F31B53C2736}"/>
-    <hyperlink ref="D74" r:id="rId89" display="https://homzmart.com/" xr:uid="{6834D860-33DC-4268-B3FC-E46D363F8C14}"/>
-    <hyperlink ref="E74" r:id="rId90" display="https://lacasa-egy.com/" xr:uid="{6026C1E5-CD3E-4D67-A23C-B21BE1C342A6}"/>
-    <hyperlink ref="F74" r:id="rId91" display="https://www.facebook.com/MilanStore4phones" xr:uid="{E5B00E6B-1831-4533-B473-B39346B00B9F}"/>
-    <hyperlink ref="A75" r:id="rId92" display="https://www.elarabygroup.com/ar" xr:uid="{D10B500F-04F2-43C4-9C51-39507CB3B198}"/>
-    <hyperlink ref="I2" r:id="rId93" xr:uid="{20B081CA-F7B0-4F03-99E8-2067D713D17D}"/>
-    <hyperlink ref="I3" r:id="rId94" xr:uid="{0BC5FE96-E9E3-4CB1-A671-353401F191D5}"/>
-    <hyperlink ref="G42" r:id="rId95" display="https://www.jumia.com.eg/ar" xr:uid="{496432C7-DA45-4A8E-A84C-8885C7FB005C}"/>
-    <hyperlink ref="H41" r:id="rId96" display="https://www.amazon.eg/" xr:uid="{8C57597A-C388-4AD3-8703-79DD842D535F}"/>
-    <hyperlink ref="G41" r:id="rId97" display="https://www.bezaat.com/egypt/cairo" xr:uid="{FE15EB89-7C4E-4477-82F3-09A3341DD129}"/>
-    <hyperlink ref="H40" r:id="rId98" display="https://eg.waseet.net/ar" xr:uid="{8D32B0A1-D400-417B-B7CE-6BD3137D7569}"/>
-    <hyperlink ref="G40" r:id="rId99" display="https://www.dubizzle.com.eg/" xr:uid="{4BECE79C-4CB5-46F1-8B23-016BB1369371}"/>
-    <hyperlink ref="H39" r:id="rId100" display="https://my.opensooq.com/" xr:uid="{FEB2963B-9392-436E-A10D-EDEE996C0D4E}"/>
-    <hyperlink ref="G39" r:id="rId101" display="https://www.facebook.com/marketplace" xr:uid="{1F1B89DB-72E8-4B08-956B-481A326E8718}"/>
+    <hyperlink ref="C60" r:id="rId72" display="https://www.thebalancecareers.com/sample-email-job-application-letter-2061608" xr:uid="{45CA1540-4F3F-491B-A863-458D827ED6D8}"/>
+    <hyperlink ref="B64" r:id="rId73" display="https://www.facebook.com/groups/402958410979164" xr:uid="{9E98DCFA-E6BA-4A05-AA25-452543EAAE39}"/>
+    <hyperlink ref="C64" r:id="rId74" display="https://www.facebook.com/groups/Dont.Work.Here" xr:uid="{2D0CC0E8-FA3A-48C9-8FCD-709201DDA6AC}"/>
+    <hyperlink ref="A65" r:id="rId75" display="https://www.facebook.com/groups/767725120055206" xr:uid="{71F71AFF-405C-4DC2-A0FF-A87D7917788C}"/>
+    <hyperlink ref="B61" r:id="rId76" xr:uid="{2E9C545B-F645-4A24-8E91-7BFE59466C1E}"/>
+    <hyperlink ref="D64" r:id="rId77" display="بلغ عن شركات النصب" xr:uid="{B74E46DD-F205-45CF-9F67-AA0E16883327}"/>
+    <hyperlink ref="E64" r:id="rId78" display="https://www.facebook.com/groups/253221952434585/" xr:uid="{79EB9432-7EFA-49DA-B9B5-2B6CB3FFEAF8}"/>
+    <hyperlink ref="A73" r:id="rId79" display="https://www.carrefouregypt.com/mafegy/ar" xr:uid="{5B55F5D2-E138-4E16-A6D3-EB5A57825CC8}"/>
+    <hyperlink ref="B73" r:id="rId80" display="https://www.jumia.com.eg/ar" xr:uid="{7D18826D-C5DE-402D-BE73-694958E65A77}"/>
+    <hyperlink ref="C73" r:id="rId81" display="https://www.raneen.com/ar" xr:uid="{A7D6AD86-B5AB-4B12-BFAA-D407089499FB}"/>
+    <hyperlink ref="D73" r:id="rId82" display="https://ar.aliexpress.com/" xr:uid="{7B29632D-E4A5-4990-993C-0F54BBE4657C}"/>
+    <hyperlink ref="E73" r:id="rId83" display="https://riz.shop/" xr:uid="{EC02BF4F-24E4-4F76-8A44-B73FC82B2C8E}"/>
+    <hyperlink ref="F73" r:id="rId84" display="https://ehabcenter.com/" xr:uid="{04985C63-238D-48C5-9959-57F080E55C63}"/>
+    <hyperlink ref="A74" r:id="rId85" display="https://noon.com/egypt-ar" xr:uid="{3BC21AE9-6120-471B-B649-DA95F10DB512}"/>
+    <hyperlink ref="B74" r:id="rId86" display="https://www.valu.com.eg/home" xr:uid="{0CB3E5D6-0D05-4CE2-8F09-1A90697DBF14}"/>
+    <hyperlink ref="C74" r:id="rId87" display="https://www.facebook.com/Al.morshedy" xr:uid="{95EEF36C-7511-461B-A94B-0F31B53C2736}"/>
+    <hyperlink ref="D74" r:id="rId88" display="https://homzmart.com/" xr:uid="{6834D860-33DC-4268-B3FC-E46D363F8C14}"/>
+    <hyperlink ref="E74" r:id="rId89" display="https://lacasa-egy.com/" xr:uid="{6026C1E5-CD3E-4D67-A23C-B21BE1C342A6}"/>
+    <hyperlink ref="F74" r:id="rId90" display="https://www.facebook.com/MilanStore4phones" xr:uid="{E5B00E6B-1831-4533-B473-B39346B00B9F}"/>
+    <hyperlink ref="A75" r:id="rId91" display="https://www.elarabygroup.com/ar" xr:uid="{D10B500F-04F2-43C4-9C51-39507CB3B198}"/>
+    <hyperlink ref="I2" r:id="rId92" xr:uid="{20B081CA-F7B0-4F03-99E8-2067D713D17D}"/>
+    <hyperlink ref="I3" r:id="rId93" xr:uid="{0BC5FE96-E9E3-4CB1-A671-353401F191D5}"/>
+    <hyperlink ref="G42" r:id="rId94" display="https://www.jumia.com.eg/ar" xr:uid="{496432C7-DA45-4A8E-A84C-8885C7FB005C}"/>
+    <hyperlink ref="H41" r:id="rId95" display="https://www.amazon.eg/" xr:uid="{8C57597A-C388-4AD3-8703-79DD842D535F}"/>
+    <hyperlink ref="G41" r:id="rId96" display="https://www.bezaat.com/egypt/cairo" xr:uid="{FE15EB89-7C4E-4477-82F3-09A3341DD129}"/>
+    <hyperlink ref="H40" r:id="rId97" display="https://eg.waseet.net/ar" xr:uid="{8D32B0A1-D400-417B-B7CE-6BD3137D7569}"/>
+    <hyperlink ref="G40" r:id="rId98" display="https://www.dubizzle.com.eg/" xr:uid="{4BECE79C-4CB5-46F1-8B23-016BB1369371}"/>
+    <hyperlink ref="H39" r:id="rId99" display="https://my.opensooq.com/" xr:uid="{FEB2963B-9392-436E-A10D-EDEE996C0D4E}"/>
+    <hyperlink ref="G39" r:id="rId100" display="https://www.facebook.com/marketplace" xr:uid="{1F1B89DB-72E8-4B08-956B-481A326E8718}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId102"/>
+  <pageSetup orientation="portrait" r:id="rId101"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5549999C-E578-4234-8F52-C87BE36B46AE}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="74.7109375" defaultRowHeight="72" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8382,82 +7267,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="175" t="s">
-        <v>645</v>
-      </c>
-      <c r="B1" s="175" t="s">
-        <v>644</v>
-      </c>
-      <c r="C1" s="171" t="s">
-        <v>643</v>
+      <c r="A1" s="170" t="s">
+        <v>564</v>
+      </c>
+      <c r="B1" s="170" t="s">
+        <v>563</v>
+      </c>
+      <c r="C1" s="166" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="174" t="s">
-        <v>642</v>
-      </c>
-      <c r="B2" s="172" t="s">
-        <v>641</v>
-      </c>
-      <c r="C2" s="171"/>
+      <c r="A2" s="169" t="s">
+        <v>561</v>
+      </c>
+      <c r="B2" s="167" t="s">
+        <v>560</v>
+      </c>
+      <c r="C2" s="166"/>
     </row>
     <row r="3" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="172" t="s">
-        <v>640</v>
-      </c>
-      <c r="B3" s="172" t="s">
-        <v>639</v>
-      </c>
-      <c r="C3" s="173" t="s">
-        <v>638</v>
+      <c r="A3" s="167" t="s">
+        <v>559</v>
+      </c>
+      <c r="B3" s="167" t="s">
+        <v>558</v>
+      </c>
+      <c r="C3" s="168" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="172" t="s">
-        <v>637</v>
-      </c>
-      <c r="B4" s="172" t="s">
-        <v>636</v>
-      </c>
-      <c r="C4" s="173" t="s">
-        <v>635</v>
+      <c r="A4" s="167" t="s">
+        <v>556</v>
+      </c>
+      <c r="B4" s="167" t="s">
+        <v>555</v>
+      </c>
+      <c r="C4" s="168" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="172" t="s">
-        <v>634</v>
-      </c>
-      <c r="B5" s="172" t="s">
-        <v>633</v>
-      </c>
-      <c r="C5" s="171"/>
+      <c r="A5" s="167" t="s">
+        <v>553</v>
+      </c>
+      <c r="B5" s="167" t="s">
+        <v>552</v>
+      </c>
+      <c r="C5" s="166"/>
     </row>
     <row r="6" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="172" t="s">
-        <v>632</v>
-      </c>
-      <c r="B6" s="172" t="s">
-        <v>631</v>
-      </c>
-      <c r="C6" s="171" t="s">
-        <v>630</v>
+      <c r="A6" s="167" t="s">
+        <v>551</v>
+      </c>
+      <c r="B6" s="167" t="s">
+        <v>550</v>
+      </c>
+      <c r="C6" s="166" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="172" t="s">
-        <v>629</v>
-      </c>
-      <c r="B7" s="172" t="s">
-        <v>628</v>
-      </c>
-      <c r="C7" s="171"/>
+      <c r="A7" s="167" t="s">
+        <v>548</v>
+      </c>
+      <c r="B7" s="167" t="s">
+        <v>547</v>
+      </c>
+      <c r="C7" s="166"/>
     </row>
     <row r="8" spans="1:3" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="262" t="s">
-        <v>627</v>
-      </c>
-      <c r="B8" s="263"/>
-      <c r="C8" s="171"/>
+      <c r="A8" s="256" t="s">
+        <v>546</v>
+      </c>
+      <c r="B8" s="257"/>
+      <c r="C8" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8471,7 +7356,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E94C25B2-BD25-4D56-89FD-7E7E1C826C18}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="56" defaultRowHeight="35.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8480,167 +7365,167 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="203" t="s">
-        <v>765</v>
-      </c>
-      <c r="B1" s="203" t="s">
-        <v>766</v>
-      </c>
-      <c r="C1" s="203" t="s">
-        <v>767</v>
+      <c r="A1" s="198" t="s">
+        <v>684</v>
+      </c>
+      <c r="B1" s="198" t="s">
+        <v>685</v>
+      </c>
+      <c r="C1" s="198" t="s">
+        <v>686</v>
       </c>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="203" t="s">
-        <v>768</v>
-      </c>
-      <c r="B2" s="203" t="s">
-        <v>769</v>
-      </c>
-      <c r="C2" s="203" t="s">
-        <v>770</v>
+      <c r="A2" s="198" t="s">
+        <v>687</v>
+      </c>
+      <c r="B2" s="198" t="s">
+        <v>688</v>
+      </c>
+      <c r="C2" s="198" t="s">
+        <v>689</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="204" t="s">
-        <v>771</v>
-      </c>
-      <c r="B3" s="203" t="s">
-        <v>772</v>
-      </c>
-      <c r="C3" s="203" t="s">
-        <v>767</v>
+      <c r="A3" s="199" t="s">
+        <v>690</v>
+      </c>
+      <c r="B3" s="198" t="s">
+        <v>691</v>
+      </c>
+      <c r="C3" s="198" t="s">
+        <v>686</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="203" t="s">
-        <v>773</v>
-      </c>
-      <c r="B4" s="203" t="s">
-        <v>774</v>
-      </c>
-      <c r="C4" s="204" t="s">
-        <v>777</v>
+      <c r="A4" s="198" t="s">
+        <v>692</v>
+      </c>
+      <c r="B4" s="198" t="s">
+        <v>693</v>
+      </c>
+      <c r="C4" s="199" t="s">
+        <v>696</v>
       </c>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="203" t="s">
-        <v>775</v>
-      </c>
-      <c r="B5" s="203" t="s">
-        <v>776</v>
-      </c>
-      <c r="C5" s="203" t="s">
-        <v>778</v>
+      <c r="A5" s="198" t="s">
+        <v>694</v>
+      </c>
+      <c r="B5" s="198" t="s">
+        <v>695</v>
+      </c>
+      <c r="C5" s="198" t="s">
+        <v>697</v>
       </c>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="203" t="s">
-        <v>779</v>
-      </c>
-      <c r="B6" s="203" t="s">
-        <v>780</v>
-      </c>
-      <c r="C6" s="203" t="s">
-        <v>781</v>
+      <c r="A6" s="198" t="s">
+        <v>698</v>
+      </c>
+      <c r="B6" s="198" t="s">
+        <v>699</v>
+      </c>
+      <c r="C6" s="198" t="s">
+        <v>700</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="203" t="s">
-        <v>782</v>
-      </c>
-      <c r="B7" s="203" t="s">
-        <v>783</v>
-      </c>
-      <c r="C7" s="203" t="s">
-        <v>784</v>
+      <c r="A7" s="198" t="s">
+        <v>701</v>
+      </c>
+      <c r="B7" s="198" t="s">
+        <v>702</v>
+      </c>
+      <c r="C7" s="198" t="s">
+        <v>703</v>
       </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="204" t="s">
-        <v>785</v>
-      </c>
-      <c r="B8" s="203" t="s">
-        <v>792</v>
-      </c>
-      <c r="C8" s="203" t="s">
-        <v>786</v>
+      <c r="A8" s="199" t="s">
+        <v>704</v>
+      </c>
+      <c r="B8" s="198" t="s">
+        <v>711</v>
+      </c>
+      <c r="C8" s="198" t="s">
+        <v>705</v>
       </c>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="203" t="s">
-        <v>787</v>
-      </c>
-      <c r="B9" s="203" t="s">
-        <v>788</v>
-      </c>
-      <c r="C9" s="203" t="s">
-        <v>789</v>
+      <c r="A9" s="198" t="s">
+        <v>706</v>
+      </c>
+      <c r="B9" s="198" t="s">
+        <v>707</v>
+      </c>
+      <c r="C9" s="198" t="s">
+        <v>708</v>
       </c>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="203" t="s">
-        <v>790</v>
-      </c>
-      <c r="B10" s="203" t="s">
-        <v>791</v>
-      </c>
-      <c r="C10" s="203" t="s">
-        <v>792</v>
+      <c r="A10" s="198" t="s">
+        <v>709</v>
+      </c>
+      <c r="B10" s="198" t="s">
+        <v>710</v>
+      </c>
+      <c r="C10" s="198" t="s">
+        <v>711</v>
       </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="204" t="s">
-        <v>793</v>
-      </c>
-      <c r="B11" s="203" t="s">
-        <v>796</v>
-      </c>
-      <c r="C11" s="203" t="s">
-        <v>794</v>
+      <c r="A11" s="199" t="s">
+        <v>712</v>
+      </c>
+      <c r="B11" s="198" t="s">
+        <v>715</v>
+      </c>
+      <c r="C11" s="198" t="s">
+        <v>713</v>
       </c>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="203" t="s">
-        <v>795</v>
-      </c>
-      <c r="B12" s="203" t="s">
-        <v>791</v>
-      </c>
-      <c r="C12" s="203" t="s">
-        <v>797</v>
+      <c r="A12" s="198" t="s">
+        <v>714</v>
+      </c>
+      <c r="B12" s="198" t="s">
+        <v>710</v>
+      </c>
+      <c r="C12" s="198" t="s">
+        <v>716</v>
       </c>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="203" t="s">
-        <v>790</v>
-      </c>
-      <c r="B13" s="203" t="s">
-        <v>794</v>
-      </c>
-      <c r="C13" s="12"/>
+      <c r="A13" s="198" t="s">
+        <v>709</v>
+      </c>
+      <c r="B13" s="198" t="s">
+        <v>713</v>
+      </c>
+      <c r="C13" s="10"/>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="203" t="s">
-        <v>793</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
+      <c r="A14" s="198" t="s">
+        <v>712</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
       <c r="D14" s="1"/>
     </row>
   </sheetData>
@@ -8652,112 +7537,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EABE8F6-4A32-498B-B882-928553FE5363}">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="66.75" customHeight="1" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>806</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>807</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>804</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>805</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>809</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>810</v>
-      </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-    </row>
-    <row r="2" spans="1:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-    </row>
-    <row r="3" spans="1:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="205" t="s">
-        <v>817</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C1" r:id="rId1" xr:uid="{67D9A7D7-13E8-4CBB-AB6B-496CD8B2A24A}"/>
-    <hyperlink ref="D1" r:id="rId2" xr:uid="{85A498E3-BF2D-4555-BA26-8984512F2849}"/>
-    <hyperlink ref="A1" r:id="rId3" xr:uid="{7F96FF10-E0A4-4296-9746-8497F280E6A9}"/>
-    <hyperlink ref="B1" r:id="rId4" xr:uid="{04A596D0-C798-4281-A4B2-B0CC6351F864}"/>
-    <hyperlink ref="E1" r:id="rId5" display="lumalabs" xr:uid="{6F636338-DC00-4072-8F05-938FC38DCE6D}"/>
-    <hyperlink ref="F1" r:id="rId6" xr:uid="{A7DB4B4A-6F74-42AD-83F8-0AAB6C08A6D3}"/>
-    <hyperlink ref="A3" r:id="rId7" xr:uid="{3300B61F-C9A8-4E0B-AC4A-26EC93A72999}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId8"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{351CB7F5-0732-4C7D-AB4A-38AEE92C8DA0}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="35.5703125" defaultRowHeight="69.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8861,7 +7640,7 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="6" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8906,7 +7685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7EBAE04-CE5D-484A-B110-BB80EB69EBB2}">
   <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="40.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8925,22 +7704,22 @@
         <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -8952,22 +7731,22 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -9081,10 +7860,10 @@
     </row>
     <row r="17" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>476</v>
+        <v>396</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>482</v>
+        <v>402</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -9095,22 +7874,22 @@
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="117" t="s">
-        <v>477</v>
+      <c r="B18" s="115" t="s">
+        <v>397</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="6" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="117" t="s">
-        <v>481</v>
+      <c r="B19" s="115" t="s">
+        <v>401</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -9119,10 +7898,10 @@
     </row>
     <row r="20" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="B20" s="117" t="s">
-        <v>478</v>
+        <v>395</v>
+      </c>
+      <c r="B20" s="115" t="s">
+        <v>398</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -9131,10 +7910,10 @@
     </row>
     <row r="21" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="B21" s="117" t="s">
-        <v>479</v>
+        <v>400</v>
+      </c>
+      <c r="B21" s="115" t="s">
+        <v>399</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -9143,10 +7922,10 @@
     </row>
     <row r="22" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="B22" s="117" t="s">
-        <v>486</v>
+        <v>405</v>
+      </c>
+      <c r="B22" s="115" t="s">
+        <v>406</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -9154,16 +7933,16 @@
       <c r="F22" s="1"/>
     </row>
     <row r="23" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="117"/>
-      <c r="B23" s="117"/>
+      <c r="A23" s="115"/>
+      <c r="B23" s="115"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
     <row r="24" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="117"/>
-      <c r="B24" s="117"/>
+      <c r="A24" s="115"/>
+      <c r="B24" s="115"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -9171,7 +7950,7 @@
     </row>
     <row r="25" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="117"/>
+      <c r="B25" s="115"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -9179,7 +7958,7 @@
     </row>
     <row r="26" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="117"/>
+      <c r="B26" s="115"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -9187,7 +7966,7 @@
     </row>
     <row r="27" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="117"/>
+      <c r="B27" s="115"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -9195,7 +7974,7 @@
     </row>
     <row r="28" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="117"/>
+      <c r="B28" s="115"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -9203,10 +7982,10 @@
     </row>
     <row r="29" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B29" s="117" t="s">
-        <v>483</v>
+        <v>111</v>
+      </c>
+      <c r="B29" s="115" t="s">
+        <v>403</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -9215,7 +7994,7 @@
     </row>
     <row r="30" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="117"/>
+      <c r="B30" s="115"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -9351,107 +8130,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{131FDDF8-672D-481C-98BD-73BCE07A5B98}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="29.85546875" defaultRowHeight="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" customWidth="1"/>
-    <col min="3" max="3" width="26.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="120" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="120" t="s">
-        <v>143</v>
-      </c>
-      <c r="C1" s="120" t="s">
-        <v>144</v>
-      </c>
-      <c r="D1" s="120" t="s">
-        <v>150</v>
-      </c>
-      <c r="E1" s="120" t="s">
-        <v>154</v>
-      </c>
-      <c r="F1" s="120" t="s">
-        <v>152</v>
-      </c>
-      <c r="G1" s="122" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="120" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="120" t="s">
-        <v>148</v>
-      </c>
-      <c r="C2" s="120" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" s="120" t="s">
-        <v>153</v>
-      </c>
-      <c r="E2" s="120" t="s">
-        <v>149</v>
-      </c>
-      <c r="F2" s="120" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="120" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120"/>
-    </row>
-    <row r="5" spans="1:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-    </row>
-    <row r="6" spans="1:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" display="https://www.facebook.com/MOHESREGYPT" xr:uid="{98DD0BDC-C936-4B1A-901F-A18FE02B3461}"/>
-    <hyperlink ref="C2" r:id="rId2" display="https://www.capmas.gov.eg/" xr:uid="{5E7DD485-7A5D-4696-A798-45931B453776}"/>
-    <hyperlink ref="B1" r:id="rId3" display="https://www.msme.eg/ar/Pages/default.aspx" xr:uid="{97A34A31-AE21-4D3E-A585-C86389EFEC91}"/>
-    <hyperlink ref="C1" r:id="rId4" display="https://digital.gov.eg/" xr:uid="{C526A501-C848-42E0-A2A3-78E0960E9764}"/>
-    <hyperlink ref="B3" r:id="rId5" display="https://www.cpa.gov.eg/ar-eg" xr:uid="{9780D227-FE05-4F1C-9C01-531B8E2842C0}"/>
-    <hyperlink ref="A2" r:id="rId6" display="https://mcit.gov.eg/ar" xr:uid="{578854D3-9485-4EA4-AF62-298A1C0DB9CA}"/>
-    <hyperlink ref="A3" r:id="rId7" display="http://issr.cu.edu.eg/ar" xr:uid="{F29E3E4E-5207-44B0-882E-9989F2217982}"/>
-    <hyperlink ref="B2" r:id="rId8" display="https://asa.gov.eg/page.aspx" xr:uid="{BBC57A1A-15C2-42C7-A716-D04F008A8950}"/>
-    <hyperlink ref="D1" r:id="rId9" display="https://www.shakwa.eg/GCP/Default.aspx" xr:uid="{D2D5AB12-9F65-4713-8F9B-4E3A4F0C2073}"/>
-    <hyperlink ref="F2" r:id="rId10" display="https://www.mof.gov.eg/ar" xr:uid="{3E2CC13A-E577-4E40-91AB-88D77411999B}"/>
-    <hyperlink ref="F1" r:id="rId11" display="http://www.gcwc.com.eg/Services/bill" xr:uid="{6524CEA9-BFD5-464A-963D-BB37C867099F}"/>
-    <hyperlink ref="D2" r:id="rId12" display="https://rern.gov.eg/" xr:uid="{2FFC4958-989B-40D7-9C31-123867917BA4}"/>
-    <hyperlink ref="E1" r:id="rId13" display="https://nosi.gov.eg/ar/Pages/HomePage/Home.aspx" xr:uid="{219AA9A2-EB3F-44C3-B470-19AA35F7C93A}"/>
-    <hyperlink ref="G1" location="'0'!A1" display="Back" xr:uid="{2B0FCC00-3444-4D83-8465-B618ADF38DC7}"/>
-    <hyperlink ref="E2" r:id="rId14" display="https://www.customs.gov.eg/" xr:uid="{EAA0AE80-7E58-485F-930E-5BEFAF1FD711}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF34A33-1541-472F-8CDA-F0757201BC40}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="24.7109375" defaultRowHeight="50.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.7109375" style="8" customWidth="1"/>
@@ -9468,1091 +8149,857 @@
   <sheetData>
     <row r="1" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>160</v>
+        <v>717</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>162</v>
+        <v>120</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="206"/>
+      <c r="B3" s="207"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="207"/>
+      <c r="H3" s="207"/>
+      <c r="I3" s="208"/>
+    </row>
+    <row r="4" spans="1:9" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>216</v>
+        <v>127</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>217</v>
+        <v>128</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>218</v>
+        <v>129</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>219</v>
+        <v>130</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>221</v>
+        <v>132</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>798</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="212"/>
-      <c r="B5" s="213"/>
-      <c r="C5" s="213"/>
-      <c r="D5" s="213"/>
-      <c r="E5" s="213"/>
-      <c r="F5" s="213"/>
-      <c r="G5" s="213"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="214"/>
-    </row>
-    <row r="6" spans="1:9" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="212"/>
-      <c r="B8" s="213"/>
-      <c r="C8" s="213"/>
-      <c r="D8" s="213"/>
-      <c r="E8" s="213"/>
-      <c r="F8" s="213"/>
-      <c r="G8" s="213"/>
-      <c r="H8" s="213"/>
-      <c r="I8" s="214"/>
-    </row>
-    <row r="9" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="212"/>
-      <c r="B11" s="213"/>
-      <c r="C11" s="213"/>
-      <c r="D11" s="213"/>
-      <c r="E11" s="213"/>
-      <c r="F11" s="213"/>
-      <c r="G11" s="213"/>
-      <c r="H11" s="213"/>
-      <c r="I11" s="214"/>
-    </row>
-    <row r="12" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E15" s="11"/>
-    </row>
-    <row r="16" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="E16" s="11"/>
-    </row>
-    <row r="18" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="12"/>
-    </row>
-    <row r="19" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
-      <c r="D19" s="12"/>
-    </row>
-    <row r="20" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="12"/>
-    </row>
-    <row r="21" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-    </row>
-    <row r="24" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
-      <c r="B24" s="7"/>
-    </row>
-    <row r="25" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-    </row>
-    <row r="26" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-    </row>
-    <row r="27" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-    </row>
-    <row r="28" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-    </row>
-    <row r="29" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-    </row>
-    <row r="30" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="7"/>
-    </row>
-    <row r="31" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="11"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="206"/>
+      <c r="B6" s="207"/>
+      <c r="C6" s="207"/>
+      <c r="D6" s="207"/>
+      <c r="E6" s="207"/>
+      <c r="F6" s="207"/>
+      <c r="G6" s="207"/>
+      <c r="H6" s="207"/>
+      <c r="I6" s="208"/>
+    </row>
+    <row r="7" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="206"/>
+      <c r="B8" s="207"/>
+      <c r="C8" s="207"/>
+      <c r="D8" s="207"/>
+      <c r="E8" s="207"/>
+      <c r="F8" s="207"/>
+      <c r="G8" s="207"/>
+      <c r="H8" s="207"/>
+      <c r="I8" s="208"/>
+    </row>
+    <row r="9" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="1:9" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A6:I6"/>
     <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" display="https://www.youtube.com/@MokhbirEqtisadi/videos" xr:uid="{CF28F272-6A39-4FEA-AC59-296E6D0C348C}"/>
-    <hyperlink ref="A3" r:id="rId2" display="https://www.youtube.com/@alfayda-3463/videos" xr:uid="{3B7DE227-CCF3-42BF-99EC-1E318F1B798F}"/>
+    <hyperlink ref="A2" r:id="rId2" display="https://www.youtube.com/@alfayda-3463/videos" xr:uid="{3B7DE227-CCF3-42BF-99EC-1E318F1B798F}"/>
     <hyperlink ref="E1" r:id="rId3" display="https://www.youtube.com/channel/UCSTPH3s5vBdblQR7CP85GWw/videos" xr:uid="{E39D3550-07CB-46E2-9B3A-7F804B199771}"/>
-    <hyperlink ref="G1" r:id="rId4" display="https://www.youtube.com/@hanyshkshk1976/videos" xr:uid="{91AAFA65-C52A-4E7E-A8D4-0A48007EB4CD}"/>
-    <hyperlink ref="G2" r:id="rId5" display="https://www.youtube.com/channel/UCrqt7_3HH__0pE3UTUDxdvA/videos" xr:uid="{D8384400-4A35-4B89-A402-64B6AD6007C3}"/>
-    <hyperlink ref="C2" r:id="rId6" display="https://www.youtube.com/@mohamedabdelfattah9178/videos" xr:uid="{E4240878-4B90-45F9-83F8-AD51AF3F8D5B}"/>
-    <hyperlink ref="A2" r:id="rId7" display="https://www.youtube.com/c/GrowUpYourMind/videos" xr:uid="{C10370D1-6AFE-43E6-BE8B-9D5F55017B1E}"/>
-    <hyperlink ref="B2" r:id="rId8" display="https://www.youtube.com/@el-bankeer/videos" xr:uid="{66130B53-04F4-411C-B93E-5EC8C1083D78}"/>
-    <hyperlink ref="F1" r:id="rId9" display="https://www.youtube.com/@Khamsint_ektesad/videos" xr:uid="{6006E0BB-AF34-400E-8C92-21A757E27F51}"/>
-    <hyperlink ref="D2" r:id="rId10" display="https://www.youtube.com/@investwithmahmood1/videos" xr:uid="{414F89E3-8972-4C4E-AC99-A222A36F9558}"/>
-    <hyperlink ref="E2" r:id="rId11" display="https://www.youtube.com/@user-wi1ur9xw3i/videos" xr:uid="{F3723356-904E-439E-9F19-98F959F66C35}"/>
-    <hyperlink ref="I3" r:id="rId12" display="https://www.facebook.com/groups/841535960276202" xr:uid="{638B4B0B-2DAD-449A-B1E1-D6F7C8228C78}"/>
-    <hyperlink ref="B1" r:id="rId13" display="https://www.youtube.com/@SharkTankEgypt/videos" xr:uid="{06DFCB78-2B6A-4A3B-B820-068445B49F59}"/>
-    <hyperlink ref="F2" r:id="rId14" display="https://www.youtube.com/@user-lm7yr8pq3c/videos" xr:uid="{0F0FE219-686D-410A-B0DB-883EE613DEE4}"/>
-    <hyperlink ref="I4" r:id="rId15" display="https://www.marketwatch.com/" xr:uid="{C9E5F377-E6B5-4D2A-82A7-3EE4787FC5E5}"/>
-    <hyperlink ref="C1" r:id="rId16" display="https://sa.investing.com/" xr:uid="{073C51EE-FF20-4990-863F-41446BD6D016}"/>
-    <hyperlink ref="D1" r:id="rId17" display="https://www.mubasher.info/countries/eg" xr:uid="{6EA1CE65-6C61-4AB2-8ABD-4C3136AD347F}"/>
-    <hyperlink ref="C3" r:id="rId18" display="https://www.facebook.com/mmali83" xr:uid="{FC65A7C2-DCF9-40BC-A737-51248CB2C75F}"/>
-    <hyperlink ref="D3" r:id="rId19" display="https://www.facebook.com/groups/qeyser.soze" xr:uid="{F288C44B-835D-419F-971B-7AF8B74B8DCD}"/>
-    <hyperlink ref="A6" r:id="rId20" display="https://www.youtube.com/c/FinBeeAcademy/videos" xr:uid="{04FEDE1C-9371-4A63-B7BB-690C91FFF41E}"/>
-    <hyperlink ref="B6" r:id="rId21" display="https://www.youtube.com/c/GrowthEngine100/videos" xr:uid="{B42D8D61-F943-4915-AFD3-E75E8FA67281}"/>
-    <hyperlink ref="C6" r:id="rId22" display="https://www.youtube.com/c/ehabmes/videos" xr:uid="{4270842D-CCB5-4A7F-A9AA-6BF64215E5A6}"/>
-    <hyperlink ref="D6" r:id="rId23" display="https://www.youtube.com/c/E3melBusinessArabic/videos" xr:uid="{A0D0C151-7D0F-4F20-B179-D7F68D2F39B3}"/>
-    <hyperlink ref="E6" r:id="rId24" display="https://www.youtube.com/channel/UCCEn3Vf1_QDBVTuz9EXrDtw/videos" xr:uid="{4F5120FC-00C6-4264-ABA4-83AB14576630}"/>
-    <hyperlink ref="F6" r:id="rId25" display="https://www.youtube.com/user/samatawy/videos" xr:uid="{01FEAEB2-16EC-432E-83C6-353CFC1F82D3}"/>
-    <hyperlink ref="G6" r:id="rId26" display="https://www.youtube.com/channel/UCZ4C_uCzDQYXOqwfDfzfRhQ/videos" xr:uid="{BD46B400-698A-4AAB-9FC9-F509ACFF3A3E}"/>
-    <hyperlink ref="G7" r:id="rId27" display="https://www.youtube.com/channel/UCeR2z-G7ncZSWHIv3pOcegA/videos" xr:uid="{563F96F1-0EEE-4496-84BD-561D92E1F932}"/>
-    <hyperlink ref="A7" r:id="rId28" display="https://corporatefinanceinstitute.com/" xr:uid="{B02201BE-6A52-493A-8598-806F4E52475E}"/>
-    <hyperlink ref="B7" r:id="rId29" display="https://www.facebook.com/Accounting.office.hatem/posts/719488698235998/" xr:uid="{261FA6B6-1CE4-428C-AB4E-DD3C454ADA1B}"/>
-    <hyperlink ref="C7" r:id="rId30" display="https://drive.google.com/drive/folders/0BzSN-W9vv152SHBaUF9UekdUNXM?fbclid=IwAR2aH0ObzqVzouPewjUUAEWq_6lz4ZJpWQoE41WRnhYo7pJWEV0qc4pEJrY&amp;resourcekey=0-20oUDhCfamMKTlXHvkSt7A" xr:uid="{725D467C-F65E-4720-93CA-193411E25778}"/>
-    <hyperlink ref="D7" r:id="rId31" display="https://www.youtube.com/@user-qg8tu7xk6l/videos" xr:uid="{FE1FB635-C9B1-485D-820C-C6836182A568}"/>
-    <hyperlink ref="E7" r:id="rId32" display="https://www.youtube.com/@AbdullahGalal/videos" xr:uid="{FC9EC340-1F68-49F0-A341-63589DFAB123}"/>
-    <hyperlink ref="F7" r:id="rId33" display="https://www.youtube.com/@Accountingforever/videos" xr:uid="{CA7E4B51-F323-43D8-A5D1-24FC7A419397}"/>
-    <hyperlink ref="E3" r:id="rId34" display="https://www.ebi.gov.eg/?lang=ar" xr:uid="{1E4834E0-5B30-4F81-90CE-07BA9F69CE1A}"/>
-    <hyperlink ref="A16" r:id="rId35" display="https://www.incometax.gov.eg/" xr:uid="{205E0792-4E3D-48FC-BF33-164AF88E869E}"/>
-    <hyperlink ref="B16" r:id="rId36" display="https://www.eta.gov.eg/ar/news" xr:uid="{A658FBAD-9D54-4692-B03D-0A524340A8D2}"/>
-    <hyperlink ref="I2" r:id="rId37" display="https://www.paypal.com/eg/home" xr:uid="{AB849500-2F5C-4150-943B-A7945120FB23}"/>
-    <hyperlink ref="B3" r:id="rId38" display="https://www.youtube.com/@ektesadmanzly/videos" xr:uid="{3D614DCA-E896-4F18-AA91-967619C30180}"/>
+    <hyperlink ref="F1" r:id="rId4" display="https://www.facebook.com/groups/841535960276202" xr:uid="{638B4B0B-2DAD-449A-B1E1-D6F7C8228C78}"/>
+    <hyperlink ref="B1" r:id="rId5" display="https://www.youtube.com/@SharkTankEgypt/videos" xr:uid="{06DFCB78-2B6A-4A3B-B820-068445B49F59}"/>
+    <hyperlink ref="C1" r:id="rId6" display="https://sa.investing.com/" xr:uid="{073C51EE-FF20-4990-863F-41446BD6D016}"/>
+    <hyperlink ref="D1" r:id="rId7" display="https://www.mubasher.info/countries/eg" xr:uid="{6EA1CE65-6C61-4AB2-8ABD-4C3136AD347F}"/>
+    <hyperlink ref="A4" r:id="rId8" display="https://www.youtube.com/c/FinBeeAcademy/videos" xr:uid="{04FEDE1C-9371-4A63-B7BB-690C91FFF41E}"/>
+    <hyperlink ref="B4" r:id="rId9" display="https://www.youtube.com/c/GrowthEngine100/videos" xr:uid="{B42D8D61-F943-4915-AFD3-E75E8FA67281}"/>
+    <hyperlink ref="C4" r:id="rId10" display="https://www.youtube.com/c/ehabmes/videos" xr:uid="{4270842D-CCB5-4A7F-A9AA-6BF64215E5A6}"/>
+    <hyperlink ref="D4" r:id="rId11" display="https://www.youtube.com/c/E3melBusinessArabic/videos" xr:uid="{A0D0C151-7D0F-4F20-B179-D7F68D2F39B3}"/>
+    <hyperlink ref="E4" r:id="rId12" display="https://www.youtube.com/channel/UCCEn3Vf1_QDBVTuz9EXrDtw/videos" xr:uid="{4F5120FC-00C6-4264-ABA4-83AB14576630}"/>
+    <hyperlink ref="F4" r:id="rId13" display="https://www.youtube.com/user/samatawy/videos" xr:uid="{01FEAEB2-16EC-432E-83C6-353CFC1F82D3}"/>
+    <hyperlink ref="G4" r:id="rId14" display="https://www.youtube.com/channel/UCZ4C_uCzDQYXOqwfDfzfRhQ/videos" xr:uid="{BD46B400-698A-4AAB-9FC9-F509ACFF3A3E}"/>
+    <hyperlink ref="D5" r:id="rId15" display="https://www.youtube.com/channel/UCeR2z-G7ncZSWHIv3pOcegA/videos" xr:uid="{563F96F1-0EEE-4496-84BD-561D92E1F932}"/>
+    <hyperlink ref="A5" r:id="rId16" display="https://corporatefinanceinstitute.com/" xr:uid="{B02201BE-6A52-493A-8598-806F4E52475E}"/>
+    <hyperlink ref="B5" r:id="rId17" display="https://www.facebook.com/Accounting.office.hatem/posts/719488698235998/" xr:uid="{261FA6B6-1CE4-428C-AB4E-DD3C454ADA1B}"/>
+    <hyperlink ref="C5" r:id="rId18" display="https://drive.google.com/drive/folders/0BzSN-W9vv152SHBaUF9UekdUNXM?fbclid=IwAR2aH0ObzqVzouPewjUUAEWq_6lz4ZJpWQoE41WRnhYo7pJWEV0qc4pEJrY&amp;resourcekey=0-20oUDhCfamMKTlXHvkSt7A" xr:uid="{725D467C-F65E-4720-93CA-193411E25778}"/>
+    <hyperlink ref="E5" r:id="rId19" display="https://www.youtube.com/@AbdullahGalal/videos" xr:uid="{FC9EC340-1F68-49F0-A341-63589DFAB123}"/>
+    <hyperlink ref="F5" r:id="rId20" display="https://www.youtube.com/@Accountingforever/videos" xr:uid="{CA7E4B51-F323-43D8-A5D1-24FC7A419397}"/>
+    <hyperlink ref="C2" r:id="rId21" display="https://www.ebi.gov.eg/?lang=ar" xr:uid="{1E4834E0-5B30-4F81-90CE-07BA9F69CE1A}"/>
+    <hyperlink ref="B2" r:id="rId22" display="https://www.youtube.com/@ektesadmanzly/videos" xr:uid="{3D614DCA-E896-4F18-AA91-967619C30180}"/>
     <hyperlink ref="I1" location="'0'!A1" display="Back" xr:uid="{844FB339-1F46-4D66-985D-2E18BC7BD043}"/>
-    <hyperlink ref="F3" r:id="rId39" display="https://www.egyptpost.org/enpo/ar/joinUs" xr:uid="{947FEBCC-E805-4BCD-AA9D-79545B164979}"/>
-    <hyperlink ref="B9" r:id="rId40" display="https://egypt.gold-price-today.com/" xr:uid="{F08D6B97-38CC-420C-8C81-296E06A30FDE}"/>
-    <hyperlink ref="C9" r:id="rId41" display="https://market.isagha.com/" xr:uid="{92F870A3-4CC7-45F6-8EDC-903CBAB32047}"/>
-    <hyperlink ref="D9" r:id="rId42" display="https://shop.btcegyptgold.com/" xr:uid="{E65AB057-A93C-4FF9-A095-76F410CC5816}"/>
-    <hyperlink ref="E9" r:id="rId43" display="https://selemagold.com/" xr:uid="{D2F12558-B7A6-403A-9BB4-58C41B38463B}"/>
-    <hyperlink ref="F9" r:id="rId44" display="https://lazurde.com/eg_ar" xr:uid="{8B3CAD7E-B09B-4B6F-A1AC-9F7CC9FA4140}"/>
-    <hyperlink ref="A10" r:id="rId45" display="https://www.facebook.com/kirmenajewelry" xr:uid="{7951D62D-C982-4A9D-80FF-93915776A844}"/>
-    <hyperlink ref="D10" r:id="rId46" display="https://swissgold.com.eg/" xr:uid="{94347AC1-14FD-4D79-B461-A878CE160CB4}"/>
-    <hyperlink ref="E10" r:id="rId47" display="https://bajocchi.com/" xr:uid="{D136EFB3-A969-4714-BE39-0F6F4D8B4EE0}"/>
-    <hyperlink ref="A12" r:id="rId48" display="https://egx.com.eg/ar/homepage.aspx" xr:uid="{C794035C-E4A9-430D-90DC-EE0D98F467BE}"/>
-    <hyperlink ref="B12" r:id="rId49" display="https://www.facebook.com/EgyptianExchangeEGX" xr:uid="{83AF1A5F-B20C-4EEE-9308-11B4517CD376}"/>
-    <hyperlink ref="C12" r:id="rId50" display="https://www.facebook.com/AzimutEgypt" xr:uid="{255ADFDD-E082-4A6C-B285-FD204FA22496}"/>
-    <hyperlink ref="D12" r:id="rId51" display="https://www.efghermesone.com/" xr:uid="{EE9CC173-D4EF-4987-818E-8441D914974C}"/>
-    <hyperlink ref="E12" r:id="rId52" display="https://www.facebook.com/thndrapp" xr:uid="{F5D67088-68A1-40B9-9E27-3180A4A372EB}"/>
-    <hyperlink ref="A13" r:id="rId53" display="https://www.facebook.com/groups/496551342015919" xr:uid="{288C7F5F-26C2-4334-BCB3-907BE29FDCAE}"/>
-    <hyperlink ref="B13" r:id="rId54" display="https://www.youtube.com/@Dr.TarekAtef/videos" xr:uid="{16571216-BFAE-4BF2-A90B-6517475ECA28}"/>
-    <hyperlink ref="C13" r:id="rId55" display="https://www.youtube.com/c/Arabicbroker1/videos" xr:uid="{C8C8E623-4F61-45CB-9F9E-56A07E9697A6}"/>
-    <hyperlink ref="D13" r:id="rId56" display="https://www.youtube.com/c/%D8%A7%D9%84%D8%A8%D9%88%D8%B1%D8%B5%D9%87%D9%85%D8%B9%D9%81%D8%A7%D8%B1%D9%88%D9%82/videos" xr:uid="{551FFB75-2F48-4D02-8E56-634114A455E1}"/>
-    <hyperlink ref="I12" r:id="rId57" display="https://ipf.eg/" xr:uid="{F36B460D-0DC0-470E-AEC6-F251290A8517}"/>
-    <hyperlink ref="F13" r:id="rId58" display="https://www.youtube.com/@elborsagia/videos" xr:uid="{8B4FB0C4-932C-4EA4-9679-C5E3C0FCBC84}"/>
-    <hyperlink ref="G12" r:id="rId59" display="https://www.facebook.com/borsacourses" xr:uid="{25C235D8-C419-45D6-8305-98EC5E70DDD0}"/>
-    <hyperlink ref="C10" r:id="rId60" xr:uid="{A36BA9B2-2D0B-4A83-87D4-CC82FDB5007B}"/>
-    <hyperlink ref="F12" r:id="rId61" xr:uid="{631468F6-55DE-4445-BE6F-92BAE8880A51}"/>
-    <hyperlink ref="B10" r:id="rId62" xr:uid="{8C965775-1F81-4624-85BC-854B09310360}"/>
-    <hyperlink ref="A9" r:id="rId63" xr:uid="{82F462F8-E15D-456A-A2AD-900377C55343}"/>
-    <hyperlink ref="C16" r:id="rId64" display="https://www.facebook.com/TheEgyptianCreditBureau" xr:uid="{B8FFBC01-44A6-4B77-9606-E001C356E329}"/>
-    <hyperlink ref="D16" r:id="rId65" display="https://www.imf.org/ar/Home" xr:uid="{48521203-7423-4B7E-91C0-9B02BFE7BE62}"/>
-    <hyperlink ref="A4" r:id="rId66" display="https://www.facebook.com/hany.genena.9" xr:uid="{7674A5EB-3383-498F-9B13-9AD6CA57D279}"/>
-    <hyperlink ref="C4" r:id="rId67" display="https://www.facebook.com/DrMahmoudWahba" xr:uid="{1B3FC995-64F1-4BF6-AA81-B9689FCA507F}"/>
-    <hyperlink ref="B4" r:id="rId68" display="https://www.facebook.com/hany.tawfik2" xr:uid="{83661365-57C3-4CCA-B540-FA329C88C7AD}"/>
-    <hyperlink ref="D4" r:id="rId69" display="https://www.facebook.com/mamdouh.hamza.77" xr:uid="{E69CD0E1-9855-43ED-94AA-651937597757}"/>
-    <hyperlink ref="E4" r:id="rId70" display="https://www.facebook.com/khedrwbusiness" xr:uid="{996D19DF-C9A8-4DC0-96AB-D6B82BA5FB68}"/>
-    <hyperlink ref="F4" r:id="rId71" display="https://www.facebook.com/mohamedhossamkhedr" xr:uid="{58848501-967B-4D89-9B59-BC7D74C5F36F}"/>
-    <hyperlink ref="G3" r:id="rId72" display="https://www.facebook.com/profile.php?id=1062738043" xr:uid="{41B6D081-FB47-4825-B9D5-EF4D37F18953}"/>
-    <hyperlink ref="E13" r:id="rId73" display="https://www.facebook.com/kareem.doghim" xr:uid="{47ECFB6A-4070-42DD-B673-9653666C303E}"/>
-    <hyperlink ref="A14" r:id="rId74" xr:uid="{B678A694-27D8-4441-838E-C53D8B0F4DFE}"/>
-    <hyperlink ref="G13" r:id="rId75" xr:uid="{6E91C3D6-2BF1-443F-AC1D-5240EFC88972}"/>
-    <hyperlink ref="G9" r:id="rId76" display="https://egyptgold-eg.com/" xr:uid="{3D0FBA57-91F3-403F-B893-E34F74A07AB1}"/>
-    <hyperlink ref="G4" r:id="rId77" xr:uid="{28EED527-3D39-4545-B669-D072096E57FE}"/>
+    <hyperlink ref="B7" r:id="rId23" display="https://egypt.gold-price-today.com/" xr:uid="{F08D6B97-38CC-420C-8C81-296E06A30FDE}"/>
+    <hyperlink ref="C7" r:id="rId24" display="https://market.isagha.com/" xr:uid="{92F870A3-4CC7-45F6-8EDC-903CBAB32047}"/>
+    <hyperlink ref="F7" r:id="rId25" display="https://swissgold.com.eg/" xr:uid="{94347AC1-14FD-4D79-B461-A878CE160CB4}"/>
+    <hyperlink ref="E7" r:id="rId26" xr:uid="{A36BA9B2-2D0B-4A83-87D4-CC82FDB5007B}"/>
+    <hyperlink ref="G7" r:id="rId27" xr:uid="{8C965775-1F81-4624-85BC-854B09310360}"/>
+    <hyperlink ref="A7" r:id="rId28" xr:uid="{82F462F8-E15D-456A-A2AD-900377C55343}"/>
+    <hyperlink ref="D2" r:id="rId29" display="https://www.facebook.com/hany.tawfik2" xr:uid="{83661365-57C3-4CCA-B540-FA329C88C7AD}"/>
+    <hyperlink ref="E2" r:id="rId30" display="https://www.facebook.com/khedrwbusiness" xr:uid="{996D19DF-C9A8-4DC0-96AB-D6B82BA5FB68}"/>
+    <hyperlink ref="F2" r:id="rId31" display="https://www.facebook.com/mohamedhossamkhedr" xr:uid="{58848501-967B-4D89-9B59-BC7D74C5F36F}"/>
+    <hyperlink ref="D7" r:id="rId32" display="https://egyptgold-eg.com/" xr:uid="{3D0FBA57-91F3-403F-B893-E34F74A07AB1}"/>
+    <hyperlink ref="G1" r:id="rId33" xr:uid="{28EED527-3D39-4545-B669-D072096E57FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId78"/>
+  <pageSetup orientation="portrait" r:id="rId34"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9977A93-9C4A-4E25-9D64-A0FBE0508D58}">
   <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="1.42578125" style="13" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="13" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="1.5703125" style="13" customWidth="1"/>
-    <col min="7" max="7" width="19" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.5703125" style="13" customWidth="1"/>
-    <col min="9" max="9" width="1.85546875" style="13" customWidth="1"/>
-    <col min="10" max="10" width="22.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" style="13" customWidth="1"/>
-    <col min="12" max="12" width="1.7109375" style="13" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="28.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="1.42578125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="11" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="1.5703125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="19" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.5703125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="1.85546875" style="11" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" style="11" customWidth="1"/>
+    <col min="12" max="12" width="1.7109375" style="11" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="146" t="s">
-        <v>227</v>
-      </c>
-      <c r="B1" s="147" t="s">
-        <v>228</v>
-      </c>
-      <c r="D1" s="229" t="s">
-        <v>229</v>
-      </c>
-      <c r="E1" s="230"/>
-      <c r="F1" s="217"/>
-      <c r="G1" s="221" t="s">
-        <v>515</v>
-      </c>
-      <c r="H1" s="222"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="225" t="s">
-        <v>231</v>
-      </c>
-      <c r="K1" s="226"/>
-      <c r="M1" s="223" t="s">
-        <v>70</v>
+      <c r="A1" s="142" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="143" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1" s="223" t="s">
+        <v>150</v>
+      </c>
+      <c r="E1" s="224"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="215" t="s">
+        <v>434</v>
+      </c>
+      <c r="H1" s="216"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="219" t="s">
+        <v>152</v>
+      </c>
+      <c r="K1" s="220"/>
+      <c r="M1" s="217" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
-        <v>516</v>
-      </c>
-      <c r="B2" s="127">
+      <c r="A2" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="B2" s="123">
         <v>77.5</v>
       </c>
-      <c r="D2" s="126" t="s">
-        <v>233</v>
-      </c>
-      <c r="E2" s="125" t="s">
-        <v>228</v>
-      </c>
-      <c r="F2" s="217"/>
-      <c r="G2" s="144" t="s">
-        <v>232</v>
-      </c>
-      <c r="H2" s="145">
+      <c r="D2" s="122" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" s="211"/>
+      <c r="G2" s="140" t="s">
+        <v>153</v>
+      </c>
+      <c r="H2" s="141">
         <v>18</v>
       </c>
-      <c r="I2" s="217"/>
-      <c r="J2" s="139" t="s">
+      <c r="I2" s="211"/>
+      <c r="J2" s="135" t="s">
+        <v>409</v>
+      </c>
+      <c r="K2" s="136" t="s">
+        <v>158</v>
+      </c>
+      <c r="M2" s="218"/>
+    </row>
+    <row r="3" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="B3" s="123">
+        <v>98</v>
+      </c>
+      <c r="D3" s="125" t="s">
+        <v>438</v>
+      </c>
+      <c r="E3" s="12">
+        <v>132</v>
+      </c>
+      <c r="F3" s="211"/>
+      <c r="G3" s="140" t="s">
+        <v>156</v>
+      </c>
+      <c r="H3" s="141">
+        <v>22</v>
+      </c>
+      <c r="I3" s="211"/>
+      <c r="J3" s="135" t="s">
+        <v>163</v>
+      </c>
+      <c r="K3" s="136" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="123">
+        <v>76</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="12">
+        <v>120</v>
+      </c>
+      <c r="F4" s="211"/>
+      <c r="G4" s="140" t="s">
+        <v>160</v>
+      </c>
+      <c r="H4" s="141">
+        <v>22</v>
+      </c>
+      <c r="I4" s="211"/>
+      <c r="J4" s="135" t="s">
+        <v>486</v>
+      </c>
+      <c r="K4" s="136" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="123">
+        <v>61</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="E5" s="13">
+        <v>128</v>
+      </c>
+      <c r="F5" s="211"/>
+      <c r="G5" s="140" t="s">
+        <v>168</v>
+      </c>
+      <c r="H5" s="141">
+        <v>40</v>
+      </c>
+      <c r="I5" s="211"/>
+      <c r="J5" s="135" t="s">
+        <v>171</v>
+      </c>
+      <c r="K5" s="136" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
+        <v>456</v>
+      </c>
+      <c r="B6" s="123"/>
+      <c r="D6" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="E6" s="13">
+        <v>100</v>
+      </c>
+      <c r="F6" s="211"/>
+      <c r="G6" s="140" t="s">
+        <v>169</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>170</v>
+      </c>
+      <c r="I6" s="211"/>
+      <c r="J6" s="137" t="s">
+        <v>453</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="B7" s="123"/>
+      <c r="D7" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="211"/>
+      <c r="G7" s="140" t="s">
+        <v>443</v>
+      </c>
+      <c r="H7" s="141" t="s">
+        <v>500</v>
+      </c>
+      <c r="I7" s="211"/>
+    </row>
+    <row r="8" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="B8" s="109" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="211"/>
+      <c r="G8" s="140" t="s">
+        <v>451</v>
+      </c>
+      <c r="H8" s="141"/>
+      <c r="I8" s="211"/>
+      <c r="J8" s="212" t="s">
+        <v>458</v>
+      </c>
+      <c r="K8" s="212"/>
+    </row>
+    <row r="9" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="144" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="E9" s="16"/>
+      <c r="F9" s="211"/>
+      <c r="G9" s="140" t="s">
+        <v>452</v>
+      </c>
+      <c r="H9" s="141" t="s">
+        <v>499</v>
+      </c>
+      <c r="I9" s="211"/>
+      <c r="J9" s="127" t="s">
+        <v>165</v>
+      </c>
+      <c r="K9" s="127" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="122" t="s">
+        <v>172</v>
+      </c>
+      <c r="E10" s="121" t="s">
+        <v>149</v>
+      </c>
+      <c r="F10" s="211"/>
+      <c r="G10" s="140" t="s">
+        <v>501</v>
+      </c>
+      <c r="H10" s="141" t="s">
+        <v>502</v>
+      </c>
+      <c r="I10" s="211"/>
+      <c r="J10" s="127" t="s">
+        <v>449</v>
+      </c>
+      <c r="K10" s="127" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="145" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" s="146" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="E11" s="12">
+        <v>143</v>
+      </c>
+      <c r="F11" s="211"/>
+      <c r="I11" s="211"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="127"/>
+    </row>
+    <row r="12" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="135" t="s">
+        <v>444</v>
+      </c>
+      <c r="B12" s="147"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="211"/>
+      <c r="G12" s="221" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" s="222"/>
+      <c r="I12" s="211"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="127"/>
+    </row>
+    <row r="13" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="135" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" s="147">
+        <v>69</v>
+      </c>
+      <c r="D13" s="122" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="121" t="s">
+        <v>149</v>
+      </c>
+      <c r="F13" s="211"/>
+      <c r="G13" s="132" t="s">
+        <v>155</v>
+      </c>
+      <c r="H13" s="132" t="s">
+        <v>157</v>
+      </c>
+      <c r="I13" s="211"/>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="135" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" s="148">
+        <v>23</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="E14" s="12">
+        <v>120</v>
+      </c>
+      <c r="F14" s="211"/>
+      <c r="G14" s="132" t="s">
+        <v>162</v>
+      </c>
+      <c r="H14" s="132" t="s">
+        <v>447</v>
+      </c>
+      <c r="I14" s="211"/>
+    </row>
+    <row r="15" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="150" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" s="151" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" s="15"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="211"/>
+      <c r="G15" s="132" t="s">
+        <v>484</v>
+      </c>
+      <c r="H15" s="133" t="s">
+        <v>454</v>
+      </c>
+      <c r="I15" s="211"/>
+      <c r="J15" s="105" t="s">
+        <v>441</v>
+      </c>
+      <c r="K15" s="105" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" s="149" t="s">
+        <v>176</v>
+      </c>
+      <c r="F16" s="211"/>
+      <c r="G16" s="132" t="s">
+        <v>485</v>
+      </c>
+      <c r="H16" s="132" t="s">
+        <v>482</v>
+      </c>
+      <c r="I16" s="211"/>
+      <c r="J16" s="105"/>
+      <c r="K16" s="105"/>
+    </row>
+    <row r="17" spans="1:11" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="B17" s="149" t="s">
+        <v>176</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="F17" s="211"/>
+      <c r="G17" s="134" t="s">
+        <v>487</v>
+      </c>
+      <c r="H17" s="134" t="s">
+        <v>483</v>
+      </c>
+      <c r="I17" s="211"/>
+      <c r="J17" s="105"/>
+      <c r="K17" s="105"/>
+    </row>
+    <row r="18" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="F18" s="211"/>
+      <c r="I18" s="211"/>
+    </row>
+    <row r="19" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="B19" s="124" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="F19" s="211"/>
+      <c r="G19" s="213" t="s">
+        <v>433</v>
+      </c>
+      <c r="H19" s="214"/>
+      <c r="I19" s="211"/>
+    </row>
+    <row r="20" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="123" t="s">
+        <v>488</v>
+      </c>
+      <c r="B20" s="78"/>
+      <c r="D20" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="F20" s="211"/>
+      <c r="G20" s="120" t="s">
+        <v>178</v>
+      </c>
+      <c r="H20" s="68" t="s">
+        <v>179</v>
+      </c>
+      <c r="I20" s="211"/>
+    </row>
+    <row r="21" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="123" t="s">
+        <v>490</v>
+      </c>
+      <c r="B21" s="78"/>
+      <c r="D21" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="E21" s="28"/>
+      <c r="F21" s="211"/>
+      <c r="G21" s="120" t="s">
+        <v>437</v>
+      </c>
+      <c r="H21" s="68" t="s">
+        <v>179</v>
+      </c>
+      <c r="I21" s="211"/>
+      <c r="J21" s="160"/>
+    </row>
+    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="123" t="s">
         <v>489</v>
       </c>
-      <c r="K2" s="140" t="s">
-        <v>237</v>
-      </c>
-      <c r="M2" s="224"/>
-    </row>
-    <row r="3" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>536</v>
-      </c>
-      <c r="B3" s="127">
-        <v>98</v>
-      </c>
-      <c r="D3" s="129" t="s">
-        <v>519</v>
-      </c>
-      <c r="E3" s="14">
-        <v>132</v>
-      </c>
-      <c r="F3" s="217"/>
-      <c r="G3" s="144" t="s">
-        <v>235</v>
-      </c>
-      <c r="H3" s="145">
-        <v>22</v>
-      </c>
-      <c r="I3" s="217"/>
-      <c r="J3" s="139" t="s">
-        <v>242</v>
-      </c>
-      <c r="K3" s="140" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="B4" s="127">
-        <v>76</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="E4" s="14">
-        <v>120</v>
-      </c>
-      <c r="F4" s="217"/>
-      <c r="G4" s="144" t="s">
-        <v>239</v>
-      </c>
-      <c r="H4" s="145">
-        <v>22</v>
-      </c>
-      <c r="I4" s="217"/>
-      <c r="J4" s="139" t="s">
-        <v>567</v>
-      </c>
-      <c r="K4" s="140" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="B5" s="127">
-        <v>61</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="E5" s="15">
-        <v>128</v>
-      </c>
-      <c r="F5" s="217"/>
-      <c r="G5" s="144" t="s">
-        <v>247</v>
-      </c>
-      <c r="H5" s="145">
-        <v>40</v>
-      </c>
-      <c r="I5" s="217"/>
-      <c r="J5" s="139" t="s">
-        <v>250</v>
-      </c>
-      <c r="K5" s="140" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
-        <v>537</v>
-      </c>
-      <c r="B6" s="127"/>
-      <c r="D6" s="16" t="s">
-        <v>574</v>
-      </c>
-      <c r="E6" s="15">
-        <v>100</v>
-      </c>
-      <c r="F6" s="217"/>
-      <c r="G6" s="144" t="s">
-        <v>248</v>
-      </c>
-      <c r="H6" s="145" t="s">
-        <v>249</v>
-      </c>
-      <c r="I6" s="217"/>
-      <c r="J6" s="141" t="s">
-        <v>534</v>
-      </c>
-      <c r="K6" s="142" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>538</v>
-      </c>
-      <c r="B7" s="127"/>
-      <c r="D7" s="16" t="s">
-        <v>520</v>
-      </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="217"/>
-      <c r="G7" s="144" t="s">
-        <v>524</v>
-      </c>
-      <c r="H7" s="145" t="s">
-        <v>581</v>
-      </c>
-      <c r="I7" s="217"/>
-    </row>
-    <row r="8" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>517</v>
-      </c>
-      <c r="B8" s="111" t="s">
-        <v>255</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>521</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="217"/>
-      <c r="G8" s="144" t="s">
-        <v>532</v>
-      </c>
-      <c r="H8" s="145"/>
-      <c r="I8" s="217"/>
-      <c r="J8" s="218" t="s">
-        <v>539</v>
-      </c>
-      <c r="K8" s="218"/>
-    </row>
-    <row r="9" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="B9" s="148" t="s">
-        <v>255</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>573</v>
-      </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="217"/>
-      <c r="G9" s="144" t="s">
-        <v>533</v>
-      </c>
-      <c r="H9" s="145" t="s">
-        <v>580</v>
-      </c>
-      <c r="I9" s="217"/>
-      <c r="J9" s="131" t="s">
-        <v>244</v>
-      </c>
-      <c r="K9" s="131" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D10" s="126" t="s">
-        <v>251</v>
-      </c>
-      <c r="E10" s="125" t="s">
-        <v>228</v>
-      </c>
-      <c r="F10" s="217"/>
-      <c r="G10" s="144" t="s">
-        <v>582</v>
-      </c>
-      <c r="H10" s="145" t="s">
-        <v>583</v>
-      </c>
-      <c r="I10" s="217"/>
-      <c r="J10" s="131" t="s">
-        <v>530</v>
-      </c>
-      <c r="K10" s="131" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="149" t="s">
-        <v>260</v>
-      </c>
-      <c r="B11" s="150" t="s">
-        <v>228</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E11" s="14">
-        <v>143</v>
-      </c>
-      <c r="F11" s="217"/>
-      <c r="I11" s="217"/>
-      <c r="J11" s="131"/>
-      <c r="K11" s="131"/>
-    </row>
-    <row r="12" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="139" t="s">
-        <v>525</v>
-      </c>
-      <c r="B12" s="151"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="217"/>
-      <c r="G12" s="227" t="s">
-        <v>230</v>
-      </c>
-      <c r="H12" s="228"/>
-      <c r="I12" s="217"/>
-      <c r="J12" s="131"/>
-      <c r="K12" s="131"/>
-    </row>
-    <row r="13" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="139" t="s">
-        <v>262</v>
-      </c>
-      <c r="B13" s="151">
-        <v>69</v>
-      </c>
-      <c r="D13" s="126" t="s">
-        <v>266</v>
-      </c>
-      <c r="E13" s="125" t="s">
-        <v>228</v>
-      </c>
-      <c r="F13" s="217"/>
-      <c r="G13" s="136" t="s">
-        <v>234</v>
-      </c>
-      <c r="H13" s="136" t="s">
-        <v>236</v>
-      </c>
-      <c r="I13" s="217"/>
-    </row>
-    <row r="14" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="139" t="s">
-        <v>265</v>
-      </c>
-      <c r="B14" s="152">
-        <v>23</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="E14" s="14">
-        <v>120</v>
-      </c>
-      <c r="F14" s="217"/>
-      <c r="G14" s="136" t="s">
-        <v>241</v>
-      </c>
-      <c r="H14" s="136" t="s">
-        <v>528</v>
-      </c>
-      <c r="I14" s="217"/>
-    </row>
-    <row r="15" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="154" t="s">
-        <v>229</v>
-      </c>
-      <c r="B15" s="155" t="s">
-        <v>255</v>
-      </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="217"/>
-      <c r="G15" s="136" t="s">
-        <v>565</v>
-      </c>
-      <c r="H15" s="137" t="s">
-        <v>535</v>
-      </c>
-      <c r="I15" s="217"/>
-      <c r="J15" s="107" t="s">
-        <v>522</v>
-      </c>
-      <c r="K15" s="107" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="B16" s="153" t="s">
-        <v>255</v>
-      </c>
-      <c r="F16" s="217"/>
-      <c r="G16" s="136" t="s">
-        <v>566</v>
-      </c>
-      <c r="H16" s="136" t="s">
-        <v>563</v>
-      </c>
-      <c r="I16" s="217"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="107"/>
-    </row>
-    <row r="17" spans="1:11" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="B17" s="153" t="s">
-        <v>255</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="F17" s="217"/>
-      <c r="G17" s="138" t="s">
-        <v>568</v>
-      </c>
-      <c r="H17" s="138" t="s">
-        <v>564</v>
-      </c>
-      <c r="I17" s="217"/>
-      <c r="J17" s="107"/>
-      <c r="K17" s="107"/>
-    </row>
-    <row r="18" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D18" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>277</v>
-      </c>
-      <c r="F18" s="217"/>
-      <c r="I18" s="217"/>
-    </row>
-    <row r="19" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
-        <v>517</v>
-      </c>
-      <c r="B19" s="128" t="s">
-        <v>228</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="F19" s="217"/>
-      <c r="G19" s="219" t="s">
-        <v>514</v>
-      </c>
-      <c r="H19" s="220"/>
-      <c r="I19" s="217"/>
-    </row>
-    <row r="20" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="127" t="s">
-        <v>569</v>
-      </c>
-      <c r="B20" s="80"/>
-      <c r="D20" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="E20" s="30" t="s">
-        <v>283</v>
-      </c>
-      <c r="F20" s="217"/>
-      <c r="G20" s="124" t="s">
-        <v>257</v>
-      </c>
-      <c r="H20" s="70" t="s">
-        <v>258</v>
-      </c>
-      <c r="I20" s="217"/>
-    </row>
-    <row r="21" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="127" t="s">
-        <v>571</v>
-      </c>
-      <c r="B21" s="80"/>
-      <c r="D21" s="21" t="s">
-        <v>578</v>
-      </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="217"/>
-      <c r="G21" s="124" t="s">
-        <v>518</v>
-      </c>
-      <c r="H21" s="70" t="s">
-        <v>258</v>
-      </c>
-      <c r="I21" s="217"/>
-      <c r="J21" s="164"/>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="127" t="s">
-        <v>570</v>
-      </c>
-      <c r="B22" s="80"/>
-      <c r="D22" s="21" t="s">
-        <v>579</v>
-      </c>
-      <c r="E22" s="30"/>
-      <c r="F22" s="217"/>
-      <c r="G22" s="124"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="217"/>
+      <c r="B22" s="78"/>
+      <c r="D22" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="E22" s="28"/>
+      <c r="F22" s="211"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="211"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="127" t="s">
-        <v>572</v>
-      </c>
-      <c r="B23" s="80"/>
-      <c r="D23" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="E23" s="30"/>
-      <c r="F23" s="217"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="217"/>
+      <c r="A23" s="123" t="s">
+        <v>491</v>
+      </c>
+      <c r="B23" s="78"/>
+      <c r="D23" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="E23" s="28"/>
+      <c r="F23" s="211"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="211"/>
     </row>
     <row r="24" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="127" t="s">
-        <v>575</v>
-      </c>
-      <c r="B24" s="80"/>
-      <c r="D24" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="F24" s="217"/>
-      <c r="G24" s="143" t="s">
-        <v>526</v>
-      </c>
-      <c r="H24" s="67"/>
-      <c r="I24" s="217"/>
+      <c r="A24" s="123" t="s">
+        <v>494</v>
+      </c>
+      <c r="B24" s="78"/>
+      <c r="D24" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="F24" s="211"/>
+      <c r="G24" s="139" t="s">
+        <v>445</v>
+      </c>
+      <c r="H24" s="65"/>
+      <c r="I24" s="211"/>
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="127" t="s">
-        <v>576</v>
-      </c>
-      <c r="B25" s="80"/>
+      <c r="A25" s="123" t="s">
+        <v>495</v>
+      </c>
+      <c r="B25" s="78"/>
     </row>
     <row r="26" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="127" t="s">
-        <v>577</v>
-      </c>
-      <c r="B26" s="80"/>
+      <c r="A26" s="123" t="s">
+        <v>496</v>
+      </c>
+      <c r="B26" s="78"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="127"/>
-      <c r="B27" s="30"/>
+      <c r="A27" s="123"/>
+      <c r="B27" s="28"/>
     </row>
     <row r="28" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="130"/>
-      <c r="B28" s="31"/>
+      <c r="A28" s="126"/>
+      <c r="B28" s="29"/>
     </row>
     <row r="29" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="133"/>
-      <c r="D29" s="132" t="s">
-        <v>287</v>
-      </c>
-      <c r="F29" s="133"/>
-      <c r="G29" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H29" s="132" t="s">
-        <v>285</v>
+      <c r="C29" s="129"/>
+      <c r="D29" s="128" t="s">
+        <v>208</v>
+      </c>
+      <c r="F29" s="129"/>
+      <c r="G29" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="H29" s="128" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="231" t="s">
-        <v>259</v>
-      </c>
-      <c r="B30" s="232"/>
-      <c r="G30" s="135" t="s">
-        <v>286</v>
-      </c>
-      <c r="H30" s="134" t="s">
-        <v>288</v>
+      <c r="A30" s="225" t="s">
+        <v>180</v>
+      </c>
+      <c r="B30" s="226"/>
+      <c r="G30" s="131" t="s">
+        <v>207</v>
+      </c>
+      <c r="H30" s="130" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="B31" s="22">
+      <c r="A31" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B31" s="20">
         <v>1.5</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="B32" s="22">
+      <c r="A32" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32" s="20">
         <v>1.5</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="B33" s="118" t="s">
-        <v>268</v>
+      <c r="A33" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" s="116" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="B34" s="22">
+      <c r="A34" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" s="20">
         <v>4.7</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="B35" s="22">
+      <c r="A35" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="B35" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="B36" s="22">
+      <c r="A36" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B36" s="20">
         <v>0.4</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="B37" s="22"/>
+      <c r="A37" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" spans="1:2" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="B38" s="29"/>
+      <c r="A38" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="B38" s="27"/>
     </row>
     <row r="39" spans="1:2" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="215" t="s">
-        <v>281</v>
-      </c>
-      <c r="B39" s="216"/>
+      <c r="A39" s="209" t="s">
+        <v>202</v>
+      </c>
+      <c r="B39" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -10581,118 +9028,118 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{407928FC-3F3D-40A9-A482-DAE5DC3CE4C9}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="23.42578125" defaultRowHeight="104.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="156" t="s">
-        <v>540</v>
-      </c>
-      <c r="B1" s="156" t="s">
-        <v>541</v>
-      </c>
-      <c r="C1" s="156" t="s">
-        <v>542</v>
-      </c>
-      <c r="D1" s="156" t="s">
-        <v>543</v>
-      </c>
-      <c r="E1" s="156" t="s">
-        <v>544</v>
-      </c>
-      <c r="F1" s="156" t="s">
-        <v>545</v>
-      </c>
-      <c r="G1" s="156" t="s">
-        <v>546</v>
+      <c r="A1" s="152" t="s">
+        <v>459</v>
+      </c>
+      <c r="B1" s="152" t="s">
+        <v>460</v>
+      </c>
+      <c r="C1" s="152" t="s">
+        <v>461</v>
+      </c>
+      <c r="D1" s="152" t="s">
+        <v>462</v>
+      </c>
+      <c r="E1" s="152" t="s">
+        <v>463</v>
+      </c>
+      <c r="F1" s="152" t="s">
+        <v>464</v>
+      </c>
+      <c r="G1" s="152" t="s">
+        <v>465</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="156" t="s">
-        <v>547</v>
-      </c>
-      <c r="B2" s="156" t="s">
-        <v>548</v>
-      </c>
-      <c r="C2" s="156" t="s">
-        <v>549</v>
-      </c>
-      <c r="D2" s="157"/>
-      <c r="E2" s="156" t="s">
-        <v>550</v>
-      </c>
-      <c r="F2" s="158"/>
-      <c r="G2" s="159" t="s">
-        <v>551</v>
+      <c r="A2" s="152" t="s">
+        <v>466</v>
+      </c>
+      <c r="B2" s="152" t="s">
+        <v>467</v>
+      </c>
+      <c r="C2" s="152" t="s">
+        <v>468</v>
+      </c>
+      <c r="D2" s="153"/>
+      <c r="E2" s="152" t="s">
+        <v>469</v>
+      </c>
+      <c r="F2" s="154"/>
+      <c r="G2" s="155" t="s">
+        <v>470</v>
       </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="156" t="s">
-        <v>552</v>
-      </c>
-      <c r="B3" s="156" t="s">
-        <v>553</v>
-      </c>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="156" t="s">
-        <v>554</v>
-      </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="160"/>
+      <c r="A3" s="152" t="s">
+        <v>471</v>
+      </c>
+      <c r="B3" s="152" t="s">
+        <v>472</v>
+      </c>
+      <c r="C3" s="153"/>
+      <c r="D3" s="153"/>
+      <c r="E3" s="152" t="s">
+        <v>473</v>
+      </c>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="156"/>
     </row>
     <row r="4" spans="1:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="233" t="s">
-        <v>555</v>
-      </c>
-      <c r="B4" s="233"/>
-      <c r="C4" s="233"/>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="158"/>
-      <c r="G4" s="158"/>
-      <c r="H4" s="160"/>
+      <c r="A4" s="227" t="s">
+        <v>474</v>
+      </c>
+      <c r="B4" s="227"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="227"/>
+      <c r="E4" s="227"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="156"/>
     </row>
     <row r="5" spans="1:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="161" t="s">
-        <v>556</v>
-      </c>
-      <c r="B5" s="161" t="s">
-        <v>557</v>
-      </c>
-      <c r="C5" s="161" t="s">
-        <v>558</v>
-      </c>
-      <c r="D5" s="162" t="s">
-        <v>131</v>
-      </c>
-      <c r="E5" s="163"/>
-      <c r="F5" s="158"/>
-      <c r="G5" s="158"/>
-      <c r="H5" s="160"/>
+      <c r="A5" s="157" t="s">
+        <v>475</v>
+      </c>
+      <c r="B5" s="157" t="s">
+        <v>476</v>
+      </c>
+      <c r="C5" s="157" t="s">
+        <v>477</v>
+      </c>
+      <c r="D5" s="158" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="159"/>
+      <c r="F5" s="154"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="156"/>
     </row>
     <row r="6" spans="1:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="161" t="s">
-        <v>559</v>
-      </c>
-      <c r="B6" s="163" t="s">
-        <v>560</v>
-      </c>
-      <c r="C6" s="163"/>
-      <c r="D6" s="163"/>
-      <c r="E6" s="162" t="s">
-        <v>561</v>
-      </c>
-      <c r="F6" s="158"/>
-      <c r="G6" s="158"/>
-      <c r="H6" s="160"/>
+      <c r="A6" s="157" t="s">
+        <v>478</v>
+      </c>
+      <c r="B6" s="159" t="s">
+        <v>479</v>
+      </c>
+      <c r="C6" s="159"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="158" t="s">
+        <v>480</v>
+      </c>
+      <c r="F6" s="154"/>
+      <c r="G6" s="154"/>
+      <c r="H6" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10727,228 +9174,228 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866B73DE-53F2-44B5-9617-ECC017AFCAD6}">
   <dimension ref="B1:N23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="33" customWidth="1"/>
-    <col min="2" max="2" width="49.140625" style="33" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="58.42578125" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="33"/>
-    <col min="8" max="8" width="32.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.140625" style="33"/>
-    <col min="11" max="11" width="8.28515625" style="33" customWidth="1"/>
-    <col min="12" max="13" width="9.140625" style="33"/>
-    <col min="14" max="14" width="10" style="33" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="33"/>
+    <col min="1" max="1" width="2.7109375" style="31" customWidth="1"/>
+    <col min="2" max="2" width="49.140625" style="31" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.42578125" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="31"/>
+    <col min="8" max="8" width="32.85546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.140625" style="31"/>
+    <col min="11" max="11" width="8.28515625" style="31" customWidth="1"/>
+    <col min="12" max="13" width="9.140625" style="31"/>
+    <col min="14" max="14" width="10" style="31" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="39" t="s">
-        <v>302</v>
-      </c>
-      <c r="D1" s="39" t="s">
-        <v>301</v>
-      </c>
-      <c r="F1" s="234" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="13"/>
-      <c r="L1" s="13"/>
+      <c r="B1" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="F1" s="228" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" s="11"/>
+      <c r="L1" s="11"/>
     </row>
     <row r="2" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F2" s="235"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
+      <c r="F2" s="229"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
     </row>
     <row r="3" spans="2:14" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="D3" s="38" t="s">
-        <v>299</v>
-      </c>
-      <c r="I3" s="13"/>
-      <c r="L3" s="13"/>
+      <c r="B3" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="L3" s="11"/>
     </row>
     <row r="4" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:14" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="34" t="s">
-        <v>298</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>297</v>
-      </c>
-      <c r="H5" s="37" t="s">
-        <v>296</v>
+      <c r="B5" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="H5" s="35" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:14" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>294</v>
+      <c r="B7" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:14" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="34" t="s">
-        <v>293</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>292</v>
+      <c r="B9" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="2:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="34" t="s">
-        <v>291</v>
-      </c>
-      <c r="E11" s="13"/>
+      <c r="D11" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" spans="2:14" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D13" s="34" t="s">
-        <v>290</v>
+      <c r="D13" s="32" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="237" t="s">
-        <v>648</v>
-      </c>
-      <c r="C15" s="237"/>
-      <c r="D15" s="237"/>
-      <c r="E15" s="237"/>
-      <c r="F15" s="237"/>
+      <c r="B15" s="231" t="s">
+        <v>567</v>
+      </c>
+      <c r="C15" s="231"/>
+      <c r="D15" s="231"/>
+      <c r="E15" s="231"/>
+      <c r="F15" s="231"/>
     </row>
     <row r="16" spans="2:14" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="B16" s="42" t="s">
-        <v>647</v>
-      </c>
-      <c r="C16" s="42" t="s">
+      <c r="B16" s="40" t="s">
+        <v>566</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="E16" s="230" t="s">
+        <v>249</v>
+      </c>
+      <c r="F16" s="230"/>
+    </row>
+    <row r="17" spans="2:6" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="B18" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>241</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="B19" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>235</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="B20" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="D20" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="D16" s="42" t="s">
-        <v>329</v>
-      </c>
-      <c r="E16" s="236" t="s">
-        <v>328</v>
-      </c>
-      <c r="F16" s="236"/>
-    </row>
-    <row r="17" spans="2:6" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="B17" s="40" t="s">
-        <v>327</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>326</v>
-      </c>
-      <c r="D17" s="40" t="s">
-        <v>325</v>
-      </c>
-      <c r="E17" s="40" t="s">
-        <v>324</v>
-      </c>
-      <c r="F17" s="40" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="B18" s="40" t="s">
-        <v>322</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>321</v>
-      </c>
-      <c r="D18" s="40" t="s">
-        <v>320</v>
-      </c>
-      <c r="E18" s="40" t="s">
-        <v>319</v>
-      </c>
-      <c r="F18" s="40" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="B19" s="40" t="s">
-        <v>317</v>
-      </c>
-      <c r="C19" s="40" t="s">
-        <v>316</v>
-      </c>
-      <c r="D19" s="40" t="s">
-        <v>315</v>
-      </c>
-      <c r="E19" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="F19" s="40" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="B20" s="40" t="s">
-        <v>312</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>311</v>
-      </c>
-      <c r="D20" s="40" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="40" t="s">
-        <v>309</v>
-      </c>
-      <c r="F20" s="40" t="s">
-        <v>308</v>
+      <c r="E20" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="52.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="40" t="s">
-        <v>307</v>
-      </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="41" t="s">
-        <v>306</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>305</v>
-      </c>
-      <c r="F21" s="40"/>
+      <c r="B21" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="C21" s="38"/>
+      <c r="D21" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="F21" s="38"/>
     </row>
     <row r="22" spans="2:6" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40" t="s">
-        <v>304</v>
-      </c>
-      <c r="F22" s="40"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="F22" s="38"/>
     </row>
     <row r="23" spans="2:6" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40" t="s">
-        <v>303</v>
-      </c>
-      <c r="F23" s="40"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="F23" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -10963,4 +9410,654 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73EAC2E5-A839-4CFE-81CB-B3D389005C51}">
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.140625" style="42" customWidth="1"/>
+    <col min="2" max="2" width="25" style="42" customWidth="1"/>
+    <col min="3" max="3" width="46.42578125" style="42" customWidth="1"/>
+    <col min="4" max="4" width="1.85546875" style="42" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="42" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="42" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" style="42" customWidth="1"/>
+    <col min="9" max="9" width="24" style="42" customWidth="1"/>
+    <col min="10" max="10" width="1.5703125" style="42" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="42" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="42"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="91" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" s="90" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" s="89" t="s">
+        <v>299</v>
+      </c>
+      <c r="E1" s="88" t="s">
+        <v>298</v>
+      </c>
+      <c r="F1" s="87" t="s">
+        <v>297</v>
+      </c>
+      <c r="G1" s="86" t="s">
+        <v>296</v>
+      </c>
+      <c r="H1" s="86" t="s">
+        <v>295</v>
+      </c>
+      <c r="I1" s="85" t="s">
+        <v>294</v>
+      </c>
+      <c r="K1" s="228" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="235" t="s">
+        <v>293</v>
+      </c>
+      <c r="B2" s="84" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="51" t="s">
+        <v>291</v>
+      </c>
+      <c r="E2" s="249" t="s">
+        <v>290</v>
+      </c>
+      <c r="F2" s="83" t="s">
+        <v>289</v>
+      </c>
+      <c r="G2" s="82" t="s">
+        <v>288</v>
+      </c>
+      <c r="H2" s="82" t="s">
+        <v>287</v>
+      </c>
+      <c r="I2" s="81"/>
+      <c r="K2" s="229"/>
+    </row>
+    <row r="3" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="235"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="E3" s="250"/>
+      <c r="F3" s="80" t="s">
+        <v>285</v>
+      </c>
+      <c r="G3" s="79" t="s">
+        <v>284</v>
+      </c>
+      <c r="H3" s="79"/>
+      <c r="I3" s="78"/>
+    </row>
+    <row r="4" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="235"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="51"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="77" t="s">
+        <v>283</v>
+      </c>
+      <c r="G4" s="76">
+        <v>44</v>
+      </c>
+      <c r="H4" s="76" t="s">
+        <v>282</v>
+      </c>
+      <c r="I4" s="75" t="s">
+        <v>251</v>
+      </c>
+      <c r="K4" s="237" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="235"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="51"/>
+      <c r="E5" s="240" t="s">
+        <v>280</v>
+      </c>
+      <c r="F5" s="74" t="s">
+        <v>276</v>
+      </c>
+      <c r="G5" s="73" t="s">
+        <v>279</v>
+      </c>
+      <c r="H5" s="73"/>
+      <c r="I5" s="72" t="s">
+        <v>278</v>
+      </c>
+      <c r="K5" s="238"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="235"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="51"/>
+      <c r="E6" s="241"/>
+      <c r="F6" s="70" t="s">
+        <v>277</v>
+      </c>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="68"/>
+    </row>
+    <row r="7" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="235" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>274</v>
+      </c>
+      <c r="E7" s="242"/>
+      <c r="F7" s="67" t="s">
+        <v>273</v>
+      </c>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="65"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="235"/>
+      <c r="B8" s="246" t="s">
+        <v>272</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>271</v>
+      </c>
+      <c r="E8" s="243" t="s">
+        <v>270</v>
+      </c>
+      <c r="F8" s="64" t="s">
+        <v>269</v>
+      </c>
+      <c r="G8" s="247">
+        <v>1.8229166666666667</v>
+      </c>
+      <c r="H8" s="63"/>
+      <c r="I8" s="62"/>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="235"/>
+      <c r="B9" s="246"/>
+      <c r="C9" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="E9" s="244"/>
+      <c r="F9" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="G9" s="248"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="59"/>
+    </row>
+    <row r="10" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="235"/>
+      <c r="B10" s="41" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="51"/>
+    </row>
+    <row r="11" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="235" t="s">
+        <v>265</v>
+      </c>
+      <c r="B11" s="58" t="s">
+        <v>264</v>
+      </c>
+      <c r="C11" s="51"/>
+      <c r="E11" s="245" t="s">
+        <v>263</v>
+      </c>
+      <c r="F11" s="57" t="s">
+        <v>262</v>
+      </c>
+      <c r="I11" s="236" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="235"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="51"/>
+      <c r="E12" s="235"/>
+      <c r="F12" s="56" t="s">
+        <v>260</v>
+      </c>
+      <c r="I12" s="236"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="235"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="51"/>
+      <c r="E13" s="235"/>
+      <c r="F13" s="55"/>
+      <c r="I13" s="236"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="235"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="51"/>
+      <c r="E14" s="235"/>
+      <c r="F14" s="55"/>
+      <c r="I14" s="53" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="235"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="51"/>
+      <c r="E15" s="239"/>
+      <c r="F15" s="54"/>
+      <c r="I15" s="53" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="235"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="51"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="235" t="s">
+        <v>257</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>256</v>
+      </c>
+      <c r="C17" s="51"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="235"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="51"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="235"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="51"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="239"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="49"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="232" t="s">
+        <v>255</v>
+      </c>
+      <c r="B22" s="233"/>
+      <c r="C22" s="234"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="48" t="s">
+        <v>253</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>254</v>
+      </c>
+      <c r="C23" s="46" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="45" t="s">
+        <v>253</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>252</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>251</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E11:E15"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="E2:E4"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{B988A63C-7553-41F6-967C-BC88E6F5E3DD}"/>
+    <hyperlink ref="B8:B9" r:id="rId2" display="الحفاظ علي البنطلون الجينس" xr:uid="{880237D1-1B91-4C64-A6CC-22BC2270CA94}"/>
+    <hyperlink ref="B11" r:id="rId3" display="انواع الريحة لازم في الخطوبة" xr:uid="{B7F74BA0-EC89-4678-95F7-816C16AFC981}"/>
+    <hyperlink ref="B17" r:id="rId4" xr:uid="{31AFDD69-1797-4DAD-8122-5ED1B8D405D5}"/>
+    <hyperlink ref="K1" location="Food!A1" display="رجوع" xr:uid="{6CB8AB43-919C-4D43-A984-3DA84D1F460C}"/>
+    <hyperlink ref="B2" r:id="rId5" xr:uid="{6B4AFA1A-2287-47DD-875E-678BCED22632}"/>
+    <hyperlink ref="F12" r:id="rId6" xr:uid="{698456EB-C81D-445D-9CE2-1B1D1C262E82}"/>
+    <hyperlink ref="F11" r:id="rId7" xr:uid="{C73669CA-12C8-4426-9434-BBBFFBC26F01}"/>
+    <hyperlink ref="K4:K5" location="Suit!A1" display="Good Suit" xr:uid="{7F379537-317A-44E4-8081-EAD6202FE71E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
+  <drawing r:id="rId9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E6618AA-AE09-4C49-A204-1817CC12D7FC}">
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="96" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1" s="96" t="s">
+        <v>322</v>
+      </c>
+      <c r="C1" s="96" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1" s="96" t="s">
+        <v>320</v>
+      </c>
+      <c r="E1" s="96" t="s">
+        <v>319</v>
+      </c>
+      <c r="F1" s="96" t="s">
+        <v>318</v>
+      </c>
+      <c r="H1" s="228" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="94" t="s">
+        <v>317</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>316</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="E2" s="41">
+        <v>2</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="H2" s="229"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="94" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="D3" s="41">
+        <v>15</v>
+      </c>
+      <c r="E3" s="41">
+        <v>3</v>
+      </c>
+      <c r="F3" s="95" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="94" t="s">
+        <v>314</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="41">
+        <v>15</v>
+      </c>
+      <c r="E4" s="41">
+        <v>3</v>
+      </c>
+      <c r="F4" s="95" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="94" t="s">
+        <v>312</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>311</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>311</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="94" t="s">
+        <v>310</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="D6" s="41">
+        <v>15</v>
+      </c>
+      <c r="E6" s="41">
+        <v>3</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="94" t="s">
+        <v>309</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="D7" s="41">
+        <v>15</v>
+      </c>
+      <c r="E7" s="41">
+        <v>3</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="94" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="D8" s="41">
+        <v>50</v>
+      </c>
+      <c r="E8" s="41">
+        <v>2</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="94"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="94"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="94"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="94"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="94"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="94"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="94"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="94"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="94"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="94"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="93" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="93" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="93" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="93" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="92" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="92"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:H2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="H1" location="Food!A1" display="رجوع" xr:uid="{B51BC1D8-BE8F-4685-B797-B33661E6AC7E}"/>
+    <hyperlink ref="B20" r:id="rId1" xr:uid="{D0CD5B75-8B58-4EF0-A785-5AD62082792B}"/>
+    <hyperlink ref="B22" r:id="rId2" xr:uid="{C5E299F2-4960-4620-AB15-17E8CAB7DD92}"/>
+    <hyperlink ref="B23" r:id="rId3" xr:uid="{CF66D09A-5242-470B-A8B0-98F885522A00}"/>
+    <hyperlink ref="B21" r:id="rId4" xr:uid="{BBD8B956-1626-45FB-96C8-F75C27E7B01C}"/>
+    <hyperlink ref="B24" r:id="rId5" xr:uid="{75EA1F4B-79B3-48D3-8124-7958DF345360}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
+</worksheet>
 </file>
--- a/HTML/0 Excel SRC Files/Other E.xlsx
+++ b/HTML/0 Excel SRC Files/Other E.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Me\QuickAccessv2\HTML\0 Excel SRC Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A992883B-DD26-4AC5-A54C-B483FB9C8530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BFB1B9-DB57-4959-AC2F-958D836DE7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="899" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="733">
   <si>
     <t>البيت الكبير</t>
   </si>
@@ -2569,6 +2569,9 @@
 اي ال main rules بتاعتي
 اي الحاجات إللي تنصحني أركز عليها
 هل ف احتمال يبقي فيه تعامل مع ال. Cloud</t>
+  </si>
+  <si>
+    <t>Math Is Fun</t>
   </si>
 </sst>
 </file>
@@ -4344,6 +4347,36 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4366,36 +4399,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="21" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5271,7 +5274,9 @@
       <c r="B3" s="201" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="118"/>
+      <c r="C3" s="200" t="s">
+        <v>732</v>
+      </c>
       <c r="D3" s="118"/>
       <c r="E3" s="200" t="s">
         <v>723</v>
@@ -5678,9 +5683,10 @@
     <hyperlink ref="H2" r:id="rId81" xr:uid="{969AC396-5B59-481C-A83A-7CF2FB12E437}"/>
     <hyperlink ref="G3" r:id="rId82" display="Quran" xr:uid="{1A09DF84-C826-4E70-AF94-16C57942C718}"/>
     <hyperlink ref="I5" r:id="rId83" xr:uid="{AE6A0070-D481-4725-8D96-23887A6B2F88}"/>
+    <hyperlink ref="C3" r:id="rId84" display="MathIsFun" xr:uid="{B35DD295-83A0-4BEF-85D2-E498D6EE24C0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId84"/>
+  <pageSetup orientation="portrait" r:id="rId85"/>
 </worksheet>
 </file>
 
@@ -8386,21 +8392,21 @@
       <c r="B1" s="143" t="s">
         <v>149</v>
       </c>
-      <c r="D1" s="223" t="s">
+      <c r="D1" s="215" t="s">
         <v>150</v>
       </c>
-      <c r="E1" s="224"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="215" t="s">
+      <c r="E1" s="216"/>
+      <c r="F1" s="221"/>
+      <c r="G1" s="225" t="s">
         <v>434</v>
       </c>
-      <c r="H1" s="216"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="219" t="s">
+      <c r="H1" s="226"/>
+      <c r="I1" s="221"/>
+      <c r="J1" s="211" t="s">
         <v>152</v>
       </c>
-      <c r="K1" s="220"/>
-      <c r="M1" s="217" t="s">
+      <c r="K1" s="212"/>
+      <c r="M1" s="209" t="s">
         <v>53</v>
       </c>
     </row>
@@ -8417,21 +8423,21 @@
       <c r="E2" s="121" t="s">
         <v>149</v>
       </c>
-      <c r="F2" s="211"/>
+      <c r="F2" s="221"/>
       <c r="G2" s="140" t="s">
         <v>153</v>
       </c>
       <c r="H2" s="141">
         <v>18</v>
       </c>
-      <c r="I2" s="211"/>
+      <c r="I2" s="221"/>
       <c r="J2" s="135" t="s">
         <v>409</v>
       </c>
       <c r="K2" s="136" t="s">
         <v>158</v>
       </c>
-      <c r="M2" s="218"/>
+      <c r="M2" s="210"/>
     </row>
     <row r="3" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
@@ -8446,14 +8452,14 @@
       <c r="E3" s="12">
         <v>132</v>
       </c>
-      <c r="F3" s="211"/>
+      <c r="F3" s="221"/>
       <c r="G3" s="140" t="s">
         <v>156</v>
       </c>
       <c r="H3" s="141">
         <v>22</v>
       </c>
-      <c r="I3" s="211"/>
+      <c r="I3" s="221"/>
       <c r="J3" s="135" t="s">
         <v>163</v>
       </c>
@@ -8474,14 +8480,14 @@
       <c r="E4" s="12">
         <v>120</v>
       </c>
-      <c r="F4" s="211"/>
+      <c r="F4" s="221"/>
       <c r="G4" s="140" t="s">
         <v>160</v>
       </c>
       <c r="H4" s="141">
         <v>22</v>
       </c>
-      <c r="I4" s="211"/>
+      <c r="I4" s="221"/>
       <c r="J4" s="135" t="s">
         <v>486</v>
       </c>
@@ -8502,14 +8508,14 @@
       <c r="E5" s="13">
         <v>128</v>
       </c>
-      <c r="F5" s="211"/>
+      <c r="F5" s="221"/>
       <c r="G5" s="140" t="s">
         <v>168</v>
       </c>
       <c r="H5" s="141">
         <v>40</v>
       </c>
-      <c r="I5" s="211"/>
+      <c r="I5" s="221"/>
       <c r="J5" s="135" t="s">
         <v>171</v>
       </c>
@@ -8528,14 +8534,14 @@
       <c r="E6" s="13">
         <v>100</v>
       </c>
-      <c r="F6" s="211"/>
+      <c r="F6" s="221"/>
       <c r="G6" s="140" t="s">
         <v>169</v>
       </c>
       <c r="H6" s="141" t="s">
         <v>170</v>
       </c>
-      <c r="I6" s="211"/>
+      <c r="I6" s="221"/>
       <c r="J6" s="137" t="s">
         <v>453</v>
       </c>
@@ -8552,14 +8558,14 @@
         <v>439</v>
       </c>
       <c r="E7" s="13"/>
-      <c r="F7" s="211"/>
+      <c r="F7" s="221"/>
       <c r="G7" s="140" t="s">
         <v>443</v>
       </c>
       <c r="H7" s="141" t="s">
         <v>500</v>
       </c>
-      <c r="I7" s="211"/>
+      <c r="I7" s="221"/>
     </row>
     <row r="8" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
@@ -8572,16 +8578,16 @@
         <v>440</v>
       </c>
       <c r="E8" s="13"/>
-      <c r="F8" s="211"/>
+      <c r="F8" s="221"/>
       <c r="G8" s="140" t="s">
         <v>451</v>
       </c>
       <c r="H8" s="141"/>
-      <c r="I8" s="211"/>
-      <c r="J8" s="212" t="s">
+      <c r="I8" s="221"/>
+      <c r="J8" s="222" t="s">
         <v>458</v>
       </c>
-      <c r="K8" s="212"/>
+      <c r="K8" s="222"/>
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
@@ -8594,14 +8600,14 @@
         <v>492</v>
       </c>
       <c r="E9" s="16"/>
-      <c r="F9" s="211"/>
+      <c r="F9" s="221"/>
       <c r="G9" s="140" t="s">
         <v>452</v>
       </c>
       <c r="H9" s="141" t="s">
         <v>499</v>
       </c>
-      <c r="I9" s="211"/>
+      <c r="I9" s="221"/>
       <c r="J9" s="127" t="s">
         <v>165</v>
       </c>
@@ -8616,14 +8622,14 @@
       <c r="E10" s="121" t="s">
         <v>149</v>
       </c>
-      <c r="F10" s="211"/>
+      <c r="F10" s="221"/>
       <c r="G10" s="140" t="s">
         <v>501</v>
       </c>
       <c r="H10" s="141" t="s">
         <v>502</v>
       </c>
-      <c r="I10" s="211"/>
+      <c r="I10" s="221"/>
       <c r="J10" s="127" t="s">
         <v>449</v>
       </c>
@@ -8644,8 +8650,8 @@
       <c r="E11" s="12">
         <v>143</v>
       </c>
-      <c r="F11" s="211"/>
-      <c r="I11" s="211"/>
+      <c r="F11" s="221"/>
+      <c r="I11" s="221"/>
       <c r="J11" s="127"/>
       <c r="K11" s="127"/>
     </row>
@@ -8656,12 +8662,12 @@
       <c r="B12" s="147"/>
       <c r="D12" s="15"/>
       <c r="E12" s="16"/>
-      <c r="F12" s="211"/>
-      <c r="G12" s="221" t="s">
+      <c r="F12" s="221"/>
+      <c r="G12" s="213" t="s">
         <v>151</v>
       </c>
-      <c r="H12" s="222"/>
-      <c r="I12" s="211"/>
+      <c r="H12" s="214"/>
+      <c r="I12" s="221"/>
       <c r="J12" s="127"/>
       <c r="K12" s="127"/>
     </row>
@@ -8678,14 +8684,14 @@
       <c r="E13" s="121" t="s">
         <v>149</v>
       </c>
-      <c r="F13" s="211"/>
+      <c r="F13" s="221"/>
       <c r="G13" s="132" t="s">
         <v>155</v>
       </c>
       <c r="H13" s="132" t="s">
         <v>157</v>
       </c>
-      <c r="I13" s="211"/>
+      <c r="I13" s="221"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="135" t="s">
@@ -8700,14 +8706,14 @@
       <c r="E14" s="12">
         <v>120</v>
       </c>
-      <c r="F14" s="211"/>
+      <c r="F14" s="221"/>
       <c r="G14" s="132" t="s">
         <v>162</v>
       </c>
       <c r="H14" s="132" t="s">
         <v>447</v>
       </c>
-      <c r="I14" s="211"/>
+      <c r="I14" s="221"/>
     </row>
     <row r="15" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="150" t="s">
@@ -8718,14 +8724,14 @@
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="16"/>
-      <c r="F15" s="211"/>
+      <c r="F15" s="221"/>
       <c r="G15" s="132" t="s">
         <v>484</v>
       </c>
       <c r="H15" s="133" t="s">
         <v>454</v>
       </c>
-      <c r="I15" s="211"/>
+      <c r="I15" s="221"/>
       <c r="J15" s="105" t="s">
         <v>441</v>
       </c>
@@ -8740,14 +8746,14 @@
       <c r="B16" s="149" t="s">
         <v>176</v>
       </c>
-      <c r="F16" s="211"/>
+      <c r="F16" s="221"/>
       <c r="G16" s="132" t="s">
         <v>485</v>
       </c>
       <c r="H16" s="132" t="s">
         <v>482</v>
       </c>
-      <c r="I16" s="211"/>
+      <c r="I16" s="221"/>
       <c r="J16" s="105"/>
       <c r="K16" s="105"/>
     </row>
@@ -8764,14 +8770,14 @@
       <c r="E17" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="F17" s="211"/>
+      <c r="F17" s="221"/>
       <c r="G17" s="134" t="s">
         <v>487</v>
       </c>
       <c r="H17" s="134" t="s">
         <v>483</v>
       </c>
-      <c r="I17" s="211"/>
+      <c r="I17" s="221"/>
       <c r="J17" s="105"/>
       <c r="K17" s="105"/>
     </row>
@@ -8782,8 +8788,8 @@
       <c r="E18" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="F18" s="211"/>
-      <c r="I18" s="211"/>
+      <c r="F18" s="221"/>
+      <c r="I18" s="221"/>
     </row>
     <row r="19" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
@@ -8798,12 +8804,12 @@
       <c r="E19" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="F19" s="211"/>
-      <c r="G19" s="213" t="s">
+      <c r="F19" s="221"/>
+      <c r="G19" s="223" t="s">
         <v>433</v>
       </c>
-      <c r="H19" s="214"/>
-      <c r="I19" s="211"/>
+      <c r="H19" s="224"/>
+      <c r="I19" s="221"/>
     </row>
     <row r="20" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="123" t="s">
@@ -8816,14 +8822,14 @@
       <c r="E20" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="F20" s="211"/>
+      <c r="F20" s="221"/>
       <c r="G20" s="120" t="s">
         <v>178</v>
       </c>
       <c r="H20" s="68" t="s">
         <v>179</v>
       </c>
-      <c r="I20" s="211"/>
+      <c r="I20" s="221"/>
     </row>
     <row r="21" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="123" t="s">
@@ -8834,14 +8840,14 @@
         <v>497</v>
       </c>
       <c r="E21" s="28"/>
-      <c r="F21" s="211"/>
+      <c r="F21" s="221"/>
       <c r="G21" s="120" t="s">
         <v>437</v>
       </c>
       <c r="H21" s="68" t="s">
         <v>179</v>
       </c>
-      <c r="I21" s="211"/>
+      <c r="I21" s="221"/>
       <c r="J21" s="160"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -8853,10 +8859,10 @@
         <v>498</v>
       </c>
       <c r="E22" s="28"/>
-      <c r="F22" s="211"/>
+      <c r="F22" s="221"/>
       <c r="G22" s="120"/>
       <c r="H22" s="68"/>
-      <c r="I22" s="211"/>
+      <c r="I22" s="221"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="123" t="s">
@@ -8867,10 +8873,10 @@
         <v>190</v>
       </c>
       <c r="E23" s="28"/>
-      <c r="F23" s="211"/>
+      <c r="F23" s="221"/>
       <c r="G23" s="120"/>
       <c r="H23" s="68"/>
-      <c r="I23" s="211"/>
+      <c r="I23" s="221"/>
     </row>
     <row r="24" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="123" t="s">
@@ -8883,12 +8889,12 @@
       <c r="E24" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="F24" s="211"/>
+      <c r="F24" s="221"/>
       <c r="G24" s="139" t="s">
         <v>445</v>
       </c>
       <c r="H24" s="65"/>
-      <c r="I24" s="211"/>
+      <c r="I24" s="221"/>
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="123" t="s">
@@ -8924,10 +8930,10 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="225" t="s">
+      <c r="A30" s="217" t="s">
         <v>180</v>
       </c>
-      <c r="B30" s="226"/>
+      <c r="B30" s="218"/>
       <c r="G30" s="131" t="s">
         <v>207</v>
       </c>
@@ -8996,24 +9002,24 @@
       <c r="B38" s="27"/>
     </row>
     <row r="39" spans="1:2" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="209" t="s">
+      <c r="A39" s="219" t="s">
         <v>202</v>
       </c>
-      <c r="B39" s="210"/>
+      <c r="B39" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A30:B30"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="I1:I24"/>
     <mergeCell ref="F1:F24"/>
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A30:B30"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H30" location="Sports!A1" display="Sport" xr:uid="{0E60B1D8-A03B-425B-B677-F574292DD411}"/>
